--- a/school_lublino/vor_lublino_floors.xlsx
+++ b/school_lublino/vor_lublino_floors.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14190" windowHeight="6840" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14190" windowHeight="6840"/>
   </bookViews>
   <sheets>
     <sheet name="ВОР 2 эт" sheetId="2" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="97">
   <si>
     <t>№ п.п.</t>
   </si>
@@ -322,6 +322,13 @@
   </si>
   <si>
     <t>3.077.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Типы 8.3
+</t>
+  </si>
+  <si>
+    <t>Типы 6.1, 7.2, 9.2</t>
   </si>
 </sst>
 </file>
@@ -439,7 +446,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -594,11 +601,14 @@
     <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -934,7 +944,7 @@
         <v>25</v>
       </c>
       <c r="C3" s="52" t="s">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="D3" s="51" t="s">
         <v>7</v>
@@ -1074,7 +1084,7 @@
         <v>-94.93</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="39" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A8" s="29">
         <v>2</v>
       </c>
@@ -1082,7 +1092,7 @@
         <v>26</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="D8" s="29" t="s">
         <v>7</v>
@@ -1228,15 +1238,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="10"/>
@@ -2154,7 +2164,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="39" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A3" s="29">
         <v>1</v>
       </c>
@@ -2162,7 +2172,7 @@
         <v>25</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="D3" s="29" t="s">
         <v>7</v>
@@ -2290,15 +2300,15 @@
         <v>-96.33</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="39" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A8" s="29">
         <v>2</v>
       </c>
       <c r="B8" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="28" t="s">
-        <v>43</v>
+      <c r="C8" s="56" t="s">
+        <v>96</v>
       </c>
       <c r="D8" s="29" t="s">
         <v>7</v>
@@ -2444,15 +2454,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="10"/>
@@ -2511,7 +2521,7 @@
       <c r="A4" s="10">
         <v>1</v>
       </c>
-      <c r="B4" s="55">
+      <c r="B4" s="54">
         <v>3.0059999999999998</v>
       </c>
       <c r="C4" s="50">
@@ -2521,7 +2531,7 @@
       <c r="E4" s="41"/>
       <c r="F4" s="47"/>
       <c r="G4" s="25">
-        <f>SUM(C4:F4)</f>
+        <f t="shared" ref="G4:G27" si="0">SUM(C4:F4)</f>
         <v>13.62</v>
       </c>
       <c r="K4">
@@ -2532,7 +2542,7 @@
       <c r="A5" s="10">
         <v>2</v>
       </c>
-      <c r="B5" s="55">
+      <c r="B5" s="54">
         <v>3.0939999999999999</v>
       </c>
       <c r="C5" s="50">
@@ -2542,7 +2552,7 @@
       <c r="E5" s="41"/>
       <c r="F5" s="47"/>
       <c r="G5" s="25">
-        <f>SUM(C5:F5)</f>
+        <f t="shared" si="0"/>
         <v>15.07</v>
       </c>
       <c r="K5">
@@ -2553,7 +2563,7 @@
       <c r="A6" s="10">
         <v>3</v>
       </c>
-      <c r="B6" s="55">
+      <c r="B6" s="54">
         <v>3.0150000000000001</v>
       </c>
       <c r="C6" s="50"/>
@@ -2563,7 +2573,7 @@
       <c r="E6" s="41"/>
       <c r="F6" s="47"/>
       <c r="G6" s="25">
-        <f>SUM(C6:F6)</f>
+        <f t="shared" si="0"/>
         <v>17.21</v>
       </c>
       <c r="K6">
@@ -2574,7 +2584,7 @@
       <c r="A7" s="10">
         <v>4</v>
       </c>
-      <c r="B7" s="55">
+      <c r="B7" s="54">
         <v>3.016</v>
       </c>
       <c r="C7" s="50"/>
@@ -2584,7 +2594,7 @@
       <c r="E7" s="41"/>
       <c r="F7" s="47"/>
       <c r="G7" s="25">
-        <f>SUM(C7:F7)</f>
+        <f t="shared" si="0"/>
         <v>21.12</v>
       </c>
       <c r="K7">
@@ -2595,7 +2605,7 @@
       <c r="A8" s="10">
         <v>5</v>
       </c>
-      <c r="B8" s="55">
+      <c r="B8" s="54">
         <v>3.0169999999999999</v>
       </c>
       <c r="C8" s="50"/>
@@ -2605,7 +2615,7 @@
       <c r="E8" s="41"/>
       <c r="F8" s="47"/>
       <c r="G8" s="25">
-        <f>SUM(C8:F8)</f>
+        <f t="shared" si="0"/>
         <v>5.0599999999999996</v>
       </c>
       <c r="K8">
@@ -2616,7 +2626,7 @@
       <c r="A9" s="10">
         <v>6</v>
       </c>
-      <c r="B9" s="55">
+      <c r="B9" s="54">
         <v>3.0179999999999998</v>
       </c>
       <c r="C9" s="50"/>
@@ -2626,7 +2636,7 @@
       </c>
       <c r="F9" s="47"/>
       <c r="G9" s="25">
-        <f>SUM(C9:F9)</f>
+        <f t="shared" si="0"/>
         <v>5.0599999999999996</v>
       </c>
       <c r="K9">
@@ -2637,7 +2647,7 @@
       <c r="A10" s="10">
         <v>7</v>
       </c>
-      <c r="B10" s="55">
+      <c r="B10" s="54">
         <v>3.0920000000000001</v>
       </c>
       <c r="C10" s="50"/>
@@ -2647,7 +2657,7 @@
       </c>
       <c r="F10" s="47"/>
       <c r="G10" s="25">
-        <f>SUM(C10:F10)</f>
+        <f t="shared" si="0"/>
         <v>5.24</v>
       </c>
       <c r="K10">
@@ -2658,7 +2668,7 @@
       <c r="A11" s="10">
         <v>8</v>
       </c>
-      <c r="B11" s="55">
+      <c r="B11" s="54">
         <v>3.0209999999999999</v>
       </c>
       <c r="C11" s="50"/>
@@ -2668,7 +2678,7 @@
       </c>
       <c r="F11" s="47"/>
       <c r="G11" s="25">
-        <f>SUM(C11:F11)</f>
+        <f t="shared" si="0"/>
         <v>15.62</v>
       </c>
       <c r="K11">
@@ -2679,7 +2689,7 @@
       <c r="A12" s="10">
         <v>9</v>
       </c>
-      <c r="B12" s="55">
+      <c r="B12" s="54">
         <v>3.0009999999999999</v>
       </c>
       <c r="C12" s="50"/>
@@ -2689,7 +2699,7 @@
         <v>129.68</v>
       </c>
       <c r="G12" s="25">
-        <f>SUM(C12:F12)</f>
+        <f t="shared" si="0"/>
         <v>129.68</v>
       </c>
       <c r="K12">
@@ -2700,7 +2710,7 @@
       <c r="A13" s="10">
         <v>10</v>
       </c>
-      <c r="B13" s="55">
+      <c r="B13" s="54">
         <v>3.0019999999999998</v>
       </c>
       <c r="C13" s="50"/>
@@ -2710,7 +2720,7 @@
         <v>73.05</v>
       </c>
       <c r="G13" s="25">
-        <f>SUM(C13:F13)</f>
+        <f t="shared" si="0"/>
         <v>73.05</v>
       </c>
       <c r="K13">
@@ -2721,7 +2731,7 @@
       <c r="A14" s="10">
         <v>11</v>
       </c>
-      <c r="B14" s="55">
+      <c r="B14" s="54">
         <v>3.0030000000000001</v>
       </c>
       <c r="C14" s="50"/>
@@ -2731,7 +2741,7 @@
         <v>71.709999999999994</v>
       </c>
       <c r="G14" s="25">
-        <f>SUM(C14:F14)</f>
+        <f t="shared" si="0"/>
         <v>71.709999999999994</v>
       </c>
       <c r="K14">
@@ -2742,7 +2752,7 @@
       <c r="A15" s="10">
         <v>12</v>
       </c>
-      <c r="B15" s="55">
+      <c r="B15" s="54">
         <v>3.004</v>
       </c>
       <c r="C15" s="50"/>
@@ -2752,7 +2762,7 @@
         <v>67.59</v>
       </c>
       <c r="G15" s="25">
-        <f>SUM(C15:F15)</f>
+        <f t="shared" si="0"/>
         <v>67.59</v>
       </c>
       <c r="K15">
@@ -2763,7 +2773,7 @@
       <c r="A16" s="10">
         <v>13</v>
       </c>
-      <c r="B16" s="55">
+      <c r="B16" s="54">
         <v>3.0049999999999999</v>
       </c>
       <c r="C16" s="50"/>
@@ -2773,7 +2783,7 @@
         <v>239.62</v>
       </c>
       <c r="G16" s="25">
-        <f>SUM(C16:F16)</f>
+        <f t="shared" si="0"/>
         <v>239.62</v>
       </c>
       <c r="K16">
@@ -2784,7 +2794,7 @@
       <c r="A17" s="10">
         <v>14</v>
       </c>
-      <c r="B17" s="55">
+      <c r="B17" s="54">
         <v>3.008</v>
       </c>
       <c r="C17" s="50"/>
@@ -2794,7 +2804,7 @@
         <v>67.84</v>
       </c>
       <c r="G17" s="25">
-        <f>SUM(C17:F17)</f>
+        <f t="shared" si="0"/>
         <v>67.84</v>
       </c>
       <c r="K17">
@@ -2805,7 +2815,7 @@
       <c r="A18" s="10">
         <v>15</v>
       </c>
-      <c r="B18" s="55">
+      <c r="B18" s="54">
         <v>3.0089999999999999</v>
       </c>
       <c r="C18" s="50"/>
@@ -2815,7 +2825,7 @@
         <v>68</v>
       </c>
       <c r="G18" s="25">
-        <f>SUM(C18:F18)</f>
+        <f t="shared" si="0"/>
         <v>68</v>
       </c>
       <c r="K18">
@@ -2826,7 +2836,7 @@
       <c r="A19" s="10">
         <v>16</v>
       </c>
-      <c r="B19" s="55">
+      <c r="B19" s="54">
         <v>3.01</v>
       </c>
       <c r="C19" s="50"/>
@@ -2836,7 +2846,7 @@
         <v>68</v>
       </c>
       <c r="G19" s="25">
-        <f>SUM(C19:F19)</f>
+        <f t="shared" si="0"/>
         <v>68</v>
       </c>
       <c r="K19">
@@ -2847,7 +2857,7 @@
       <c r="A20" s="10">
         <v>17</v>
       </c>
-      <c r="B20" s="55">
+      <c r="B20" s="54">
         <v>3.0110000000000001</v>
       </c>
       <c r="C20" s="50"/>
@@ -2857,7 +2867,7 @@
         <v>67.14</v>
       </c>
       <c r="G20" s="25">
-        <f>SUM(C20:F20)</f>
+        <f t="shared" si="0"/>
         <v>67.14</v>
       </c>
       <c r="K20">
@@ -2868,7 +2878,7 @@
       <c r="A21" s="10">
         <v>18</v>
       </c>
-      <c r="B21" s="55">
+      <c r="B21" s="54">
         <v>3.012</v>
       </c>
       <c r="C21" s="50"/>
@@ -2878,7 +2888,7 @@
         <v>68</v>
       </c>
       <c r="G21" s="25">
-        <f>SUM(C21:F21)</f>
+        <f t="shared" si="0"/>
         <v>68</v>
       </c>
       <c r="K21">
@@ -2889,7 +2899,7 @@
       <c r="A22" s="10">
         <v>19</v>
       </c>
-      <c r="B22" s="55">
+      <c r="B22" s="54">
         <v>3.0129999999999999</v>
       </c>
       <c r="C22" s="50"/>
@@ -2899,7 +2909,7 @@
         <v>68</v>
       </c>
       <c r="G22" s="25">
-        <f>SUM(C22:F22)</f>
+        <f t="shared" si="0"/>
         <v>68</v>
       </c>
       <c r="K22">
@@ -2910,7 +2920,7 @@
       <c r="A23" s="10">
         <v>20</v>
       </c>
-      <c r="B23" s="55">
+      <c r="B23" s="54">
         <v>3.0139999999999998</v>
       </c>
       <c r="C23" s="50"/>
@@ -2920,7 +2930,7 @@
         <v>148.61000000000001</v>
       </c>
       <c r="G23" s="25">
-        <f>SUM(C23:F23)</f>
+        <f t="shared" si="0"/>
         <v>148.61000000000001</v>
       </c>
       <c r="K23">
@@ -2941,7 +2951,7 @@
         <v>244.28</v>
       </c>
       <c r="G24" s="25">
-        <f>SUM(C24:F24)</f>
+        <f t="shared" si="0"/>
         <v>244.28</v>
       </c>
       <c r="K24">
@@ -2952,7 +2962,7 @@
       <c r="A25" s="10">
         <v>22</v>
       </c>
-      <c r="B25" s="55">
+      <c r="B25" s="54">
         <v>3.02</v>
       </c>
       <c r="C25" s="50"/>
@@ -2962,7 +2972,7 @@
         <v>137.72999999999999</v>
       </c>
       <c r="G25" s="25">
-        <f>SUM(C25:F25)</f>
+        <f t="shared" si="0"/>
         <v>137.72999999999999</v>
       </c>
       <c r="K25">
@@ -2973,7 +2983,7 @@
       <c r="A26" s="10">
         <v>23</v>
       </c>
-      <c r="B26" s="55">
+      <c r="B26" s="54">
         <v>3.085</v>
       </c>
       <c r="C26" s="50"/>
@@ -2983,7 +2993,7 @@
         <v>13.16</v>
       </c>
       <c r="G26" s="25">
-        <f>SUM(C26:F26)</f>
+        <f t="shared" si="0"/>
         <v>13.16</v>
       </c>
       <c r="K26">
@@ -2994,7 +3004,7 @@
       <c r="A27" s="10">
         <v>24</v>
       </c>
-      <c r="B27" s="55" t="s">
+      <c r="B27" s="54" t="s">
         <v>94</v>
       </c>
       <c r="C27" s="50"/>
@@ -3004,7 +3014,7 @@
         <v>140.80000000000001</v>
       </c>
       <c r="G27" s="25">
-        <f>SUM(C27:F27)</f>
+        <f t="shared" si="0"/>
         <v>140.80000000000001</v>
       </c>
       <c r="K27">

--- a/school_lublino/vor_lublino_floors.xlsx
+++ b/school_lublino/vor_lublino_floors.xlsx
@@ -9,18 +9,30 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14190" windowHeight="6840"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14190" windowHeight="6840" firstSheet="13" activeTab="14"/>
   </bookViews>
   <sheets>
-    <sheet name="ВОР 2 эт" sheetId="2" r:id="rId1"/>
-    <sheet name="Спец 2 эт" sheetId="4" r:id="rId2"/>
-    <sheet name="ВОР 3 эт" sheetId="3" r:id="rId3"/>
-    <sheet name="Спец 3 эт" sheetId="6" r:id="rId4"/>
-    <sheet name="общий (2)" sheetId="5" r:id="rId5"/>
-    <sheet name="Лист1" sheetId="7" r:id="rId6"/>
+    <sheet name="АА" sheetId="16" state="hidden" r:id="rId1"/>
+    <sheet name="ВОР 2 эт" sheetId="2" r:id="rId2"/>
+    <sheet name="Спец 2 эт" sheetId="4" state="hidden" r:id="rId3"/>
+    <sheet name="ВОР 3 эт" sheetId="3" r:id="rId4"/>
+    <sheet name="Спец 3 эт" sheetId="6" state="hidden" r:id="rId5"/>
+    <sheet name="общий (2)" sheetId="5" state="hidden" r:id="rId6"/>
+    <sheet name="ВорИзол" sheetId="10" r:id="rId7"/>
+    <sheet name="Из1эт" sheetId="8" state="hidden" r:id="rId8"/>
+    <sheet name="Из2эт" sheetId="9" state="hidden" r:id="rId9"/>
+    <sheet name="ВорПленка" sheetId="12" r:id="rId10"/>
+    <sheet name="Плк1э" sheetId="13" state="hidden" r:id="rId11"/>
+    <sheet name="Плк2э" sheetId="14" state="hidden" r:id="rId12"/>
+    <sheet name="Плк3э" sheetId="15" state="hidden" r:id="rId13"/>
+    <sheet name="Общ" sheetId="7" r:id="rId14"/>
+    <sheet name="СКБ-1эт" sheetId="17" r:id="rId15"/>
+    <sheet name="1эт" sheetId="18" r:id="rId16"/>
+    <sheet name="2эт" sheetId="19" r:id="rId17"/>
+    <sheet name="3эт" sheetId="20" r:id="rId18"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Спец 3 эт'!$B$2:$K$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Спец 3 эт'!$B$2:$K$27</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -32,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="115">
   <si>
     <t>№ п.п.</t>
   </si>
@@ -329,6 +341,60 @@
   </si>
   <si>
     <t>Типы 6.1, 7.2, 9.2</t>
+  </si>
+  <si>
+    <t>Блок</t>
+  </si>
+  <si>
+    <t>№ пом.</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>4.1</t>
+  </si>
+  <si>
+    <t>7.2</t>
+  </si>
+  <si>
+    <t>Устройство тепло-звукоизоляции полов / минвата / в 1 слой</t>
+  </si>
+  <si>
+    <t>Плита минераловатная_ / Технолайт Экстра</t>
+  </si>
+  <si>
+    <t>Типы 5, 6, 7, 7.2, 8.1, 8.2, 9, 9.1</t>
+  </si>
+  <si>
+    <t>м3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">сумма: </t>
+  </si>
+  <si>
+    <t>Спецификация выполненных работ (2 этаж)</t>
+  </si>
+  <si>
+    <t>Спецификация выполненных работ (1 этаж)</t>
+  </si>
+  <si>
+    <t>Спецификация выполненных работ. 3 этаж.</t>
+  </si>
+  <si>
+    <t>Спецификация выполненных работ. 1 этаж.</t>
+  </si>
+  <si>
+    <t>Спецификация выполненных работ. 2 этаж.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.075; 2.080; </t>
+  </si>
+  <si>
+    <t>`-</t>
+  </si>
+  <si>
+    <t>сумма</t>
   </si>
 </sst>
 </file>
@@ -339,7 +405,7 @@
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -369,8 +435,15 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ГОСТ тип А"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -407,8 +480,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCCFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -442,11 +521,118 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -604,18 +790,851 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="27">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="ГОСТ тип А"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="ГОСТ тип А"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="ГОСТ тип А"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="ГОСТ тип А"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="ГОСТ тип А"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="ГОСТ тип А"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="ГОСТ тип А"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="ГОСТ тип А"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="ГОСТ тип А"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="ГОСТ тип А"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="ГОСТ тип А"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="ГОСТ тип А"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="ГОСТ тип А"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="ГОСТ тип А"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="ГОСТ тип А"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="0.000"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="ГОСТ тип А"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="ГОСТ тип А"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="ГОСТ тип А"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFCCFF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -625,6 +1644,81 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Таблица1" displayName="Таблица1" ref="A81:E105" totalsRowShown="0" dataDxfId="25" headerRowBorderDxfId="26" tableBorderDxfId="24" totalsRowBorderDxfId="23">
+  <autoFilter ref="A81:E105">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="6.1"/>
+        <filter val="7.2"/>
+        <filter val="9.2"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <sortState ref="A82:E105">
+    <sortCondition ref="D81:D105"/>
+  </sortState>
+  <tableColumns count="5">
+    <tableColumn id="1" name="№ п.п." dataDxfId="22"/>
+    <tableColumn id="2" name="Блок" dataDxfId="21"/>
+    <tableColumn id="3" name="№ пом." dataDxfId="20"/>
+    <tableColumn id="4" name="Типы" dataDxfId="19"/>
+    <tableColumn id="5" name="Объем, м²" dataDxfId="18"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Таблица2" displayName="Таблица2" ref="A32:E77" totalsRowShown="0" dataDxfId="16" headerRowBorderDxfId="17" tableBorderDxfId="15" totalsRowBorderDxfId="14">
+  <autoFilter ref="A32:E77">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="4.4"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <sortState ref="A34:E75">
+    <sortCondition ref="D32:D77"/>
+  </sortState>
+  <tableColumns count="5">
+    <tableColumn id="1" name="№ п.п." dataDxfId="13"/>
+    <tableColumn id="2" name="Блок" dataDxfId="12"/>
+    <tableColumn id="3" name="№ пом." dataDxfId="11"/>
+    <tableColumn id="4" name="Типы" dataDxfId="10"/>
+    <tableColumn id="5" name="Объем, м²" dataDxfId="9"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Таблица3" displayName="Таблица3" ref="A2:E29" totalsRowShown="0" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6" totalsRowBorderDxfId="5">
+  <autoFilter ref="A2:E29">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="6"/>
+        <filter val="7"/>
+        <filter val="8.1"/>
+        <filter val="8.2"/>
+        <filter val="9"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <sortState ref="A3:E29">
+    <sortCondition ref="D2:D29"/>
+  </sortState>
+  <tableColumns count="5">
+    <tableColumn id="1" name="№ п.п." dataDxfId="4"/>
+    <tableColumn id="2" name="Блок" dataDxfId="3"/>
+    <tableColumn id="3" name="№ пом." dataDxfId="2"/>
+    <tableColumn id="4" name="Типы" dataDxfId="1"/>
+    <tableColumn id="5" name="Объем, м²" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -890,6 +1984,5066 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor theme="5" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor theme="5" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="7.5703125" customWidth="1"/>
+    <col min="2" max="2" width="50.28515625" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" customWidth="1"/>
+    <col min="6" max="6" width="7.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="15"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="5"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="39" x14ac:dyDescent="0.25">
+      <c r="A3" s="67">
+        <v>1</v>
+      </c>
+      <c r="B3" s="73" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="69" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" s="67" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="70">
+        <v>1</v>
+      </c>
+      <c r="F3" s="60">
+        <f>Плк1э!E30+Плк2э!E23+Плк3э!E8</f>
+        <v>2708.8399999999997</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="57">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="9"/>
+      <c r="D4" s="57" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F4" s="25">
+        <f>F3*E4</f>
+        <v>2979.7239999999997</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor theme="5" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:E30"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="7.5703125" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" customWidth="1"/>
+    <col min="4" max="4" width="6.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="96" t="s">
+        <v>110</v>
+      </c>
+      <c r="B1" s="97"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="98"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="86" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="86" t="s">
+        <v>97</v>
+      </c>
+      <c r="C2" s="86" t="s">
+        <v>98</v>
+      </c>
+      <c r="D2" s="86" t="s">
+        <v>93</v>
+      </c>
+      <c r="E2" s="86" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="86">
+        <v>1</v>
+      </c>
+      <c r="B3" s="86">
+        <v>1</v>
+      </c>
+      <c r="C3" s="86">
+        <v>1.024</v>
+      </c>
+      <c r="D3" s="86">
+        <v>6</v>
+      </c>
+      <c r="E3" s="86">
+        <v>13.62</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="86">
+        <v>2</v>
+      </c>
+      <c r="B4" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C4" s="86">
+        <v>1.0449999999999999</v>
+      </c>
+      <c r="D4" s="86">
+        <v>6</v>
+      </c>
+      <c r="E4" s="86">
+        <v>161.78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="86">
+        <v>3</v>
+      </c>
+      <c r="B5" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C5" s="86">
+        <v>1.046</v>
+      </c>
+      <c r="D5" s="86">
+        <v>6</v>
+      </c>
+      <c r="E5" s="86">
+        <v>161.15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="86">
+        <v>4</v>
+      </c>
+      <c r="B6" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C6" s="86">
+        <v>1.0529999999999999</v>
+      </c>
+      <c r="D6" s="86">
+        <v>6</v>
+      </c>
+      <c r="E6" s="86">
+        <v>443.48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="86">
+        <v>5</v>
+      </c>
+      <c r="B7" s="86">
+        <v>1</v>
+      </c>
+      <c r="C7" s="86">
+        <v>1.034</v>
+      </c>
+      <c r="D7" s="86">
+        <v>7</v>
+      </c>
+      <c r="E7" s="86">
+        <v>17.22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="86">
+        <v>6</v>
+      </c>
+      <c r="B8" s="86">
+        <v>1</v>
+      </c>
+      <c r="C8" s="86">
+        <v>1.0349999999999999</v>
+      </c>
+      <c r="D8" s="86">
+        <v>7</v>
+      </c>
+      <c r="E8" s="86">
+        <v>21.63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="86">
+        <v>7</v>
+      </c>
+      <c r="B9" s="86">
+        <v>1</v>
+      </c>
+      <c r="C9" s="86">
+        <v>1.036</v>
+      </c>
+      <c r="D9" s="86">
+        <v>7</v>
+      </c>
+      <c r="E9" s="86">
+        <v>5.76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="86">
+        <v>8</v>
+      </c>
+      <c r="B10" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C10" s="86">
+        <v>1.054</v>
+      </c>
+      <c r="D10" s="86">
+        <v>7</v>
+      </c>
+      <c r="E10" s="86">
+        <v>14.54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="86">
+        <v>9</v>
+      </c>
+      <c r="B11" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C11" s="86">
+        <v>1.054</v>
+      </c>
+      <c r="D11" s="86">
+        <v>7.1</v>
+      </c>
+      <c r="E11" s="86">
+        <v>46.62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="86">
+        <v>10</v>
+      </c>
+      <c r="B12" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C12" s="86">
+        <v>1.048</v>
+      </c>
+      <c r="D12" s="86">
+        <v>8.1</v>
+      </c>
+      <c r="E12" s="86">
+        <v>23.92</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="86">
+        <v>11</v>
+      </c>
+      <c r="B13" s="86">
+        <v>1</v>
+      </c>
+      <c r="C13" s="86">
+        <v>1.0369999999999999</v>
+      </c>
+      <c r="D13" s="86">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="E13" s="86">
+        <v>3.34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="86">
+        <v>12</v>
+      </c>
+      <c r="B14" s="86">
+        <v>1</v>
+      </c>
+      <c r="C14" s="86">
+        <v>1.038</v>
+      </c>
+      <c r="D14" s="86">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="E14" s="86">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="86">
+        <v>13</v>
+      </c>
+      <c r="B15" s="86">
+        <v>1</v>
+      </c>
+      <c r="C15" s="86">
+        <v>1.026</v>
+      </c>
+      <c r="D15" s="86">
+        <v>9</v>
+      </c>
+      <c r="E15" s="86">
+        <v>191.68</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="86">
+        <v>14</v>
+      </c>
+      <c r="B16" s="86">
+        <v>1</v>
+      </c>
+      <c r="C16" s="86">
+        <v>1.0269999999999999</v>
+      </c>
+      <c r="D16" s="86">
+        <v>9</v>
+      </c>
+      <c r="E16" s="86">
+        <v>114.04</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="86">
+        <v>15</v>
+      </c>
+      <c r="B17" s="86">
+        <v>1</v>
+      </c>
+      <c r="C17" s="86">
+        <v>1.028</v>
+      </c>
+      <c r="D17" s="86">
+        <v>9</v>
+      </c>
+      <c r="E17" s="86">
+        <v>68.81</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="86">
+        <v>16</v>
+      </c>
+      <c r="B18" s="86">
+        <v>1</v>
+      </c>
+      <c r="C18" s="86">
+        <v>1.0289999999999999</v>
+      </c>
+      <c r="D18" s="86">
+        <v>9</v>
+      </c>
+      <c r="E18" s="86">
+        <v>68.81</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="86">
+        <v>17</v>
+      </c>
+      <c r="B19" s="86">
+        <v>1</v>
+      </c>
+      <c r="C19" s="86">
+        <v>1.03</v>
+      </c>
+      <c r="D19" s="86">
+        <v>9</v>
+      </c>
+      <c r="E19" s="86">
+        <v>68.89</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="86">
+        <v>18</v>
+      </c>
+      <c r="B20" s="86">
+        <v>1</v>
+      </c>
+      <c r="C20" s="86">
+        <v>1.0309999999999999</v>
+      </c>
+      <c r="D20" s="86">
+        <v>9</v>
+      </c>
+      <c r="E20" s="86">
+        <v>68.89</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="86">
+        <v>19</v>
+      </c>
+      <c r="B21" s="86">
+        <v>1</v>
+      </c>
+      <c r="C21" s="86">
+        <v>1.032</v>
+      </c>
+      <c r="D21" s="86">
+        <v>9</v>
+      </c>
+      <c r="E21" s="86">
+        <v>68.069999999999993</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="86">
+        <v>20</v>
+      </c>
+      <c r="B22" s="86">
+        <v>1</v>
+      </c>
+      <c r="C22" s="86">
+        <v>1.0329999999999999</v>
+      </c>
+      <c r="D22" s="86">
+        <v>9</v>
+      </c>
+      <c r="E22" s="86">
+        <v>139.1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="86">
+        <v>21</v>
+      </c>
+      <c r="B23" s="86">
+        <v>1</v>
+      </c>
+      <c r="C23" s="86">
+        <v>1.0389999999999999</v>
+      </c>
+      <c r="D23" s="86">
+        <v>9</v>
+      </c>
+      <c r="E23" s="86">
+        <v>149.69999999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="86">
+        <v>22</v>
+      </c>
+      <c r="B24" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C24" s="86">
+        <v>1.04</v>
+      </c>
+      <c r="D24" s="86">
+        <v>9</v>
+      </c>
+      <c r="E24" s="86">
+        <v>220.47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="86">
+        <v>23</v>
+      </c>
+      <c r="B25" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C25" s="86">
+        <v>1.0429999999999999</v>
+      </c>
+      <c r="D25" s="86">
+        <v>9</v>
+      </c>
+      <c r="E25" s="86">
+        <v>61.99</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="86">
+        <v>24</v>
+      </c>
+      <c r="B26" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C26" s="86">
+        <v>1.044</v>
+      </c>
+      <c r="D26" s="86">
+        <v>9</v>
+      </c>
+      <c r="E26" s="86">
+        <v>14.14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="86">
+        <v>25</v>
+      </c>
+      <c r="B27" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C27" s="86">
+        <v>1.0489999999999999</v>
+      </c>
+      <c r="D27" s="86">
+        <v>9</v>
+      </c>
+      <c r="E27" s="86">
+        <v>103.8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="86">
+        <v>26</v>
+      </c>
+      <c r="B28" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C28" s="86">
+        <v>1.05</v>
+      </c>
+      <c r="D28" s="86">
+        <v>9</v>
+      </c>
+      <c r="E28" s="86">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="86">
+        <v>27</v>
+      </c>
+      <c r="B29" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C29" s="86">
+        <v>1.0509999999999999</v>
+      </c>
+      <c r="D29" s="86">
+        <v>9</v>
+      </c>
+      <c r="E29" s="86">
+        <v>31.58</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="57"/>
+      <c r="B30" s="34"/>
+      <c r="C30" s="54"/>
+      <c r="D30" s="34" t="s">
+        <v>52</v>
+      </c>
+      <c r="E30" s="72">
+        <f>SUM(E1:E29)</f>
+        <v>2310.2799999999997</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor theme="5" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6.5703125" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="7.140625" customWidth="1"/>
+    <col min="4" max="4" width="6.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="96" t="s">
+        <v>111</v>
+      </c>
+      <c r="B1" s="97"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="98"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="86" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="86" t="s">
+        <v>97</v>
+      </c>
+      <c r="C2" s="86" t="s">
+        <v>98</v>
+      </c>
+      <c r="D2" s="86" t="s">
+        <v>93</v>
+      </c>
+      <c r="E2" s="86" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="86">
+        <v>1</v>
+      </c>
+      <c r="B3" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C3" s="89">
+        <v>2.16</v>
+      </c>
+      <c r="D3" s="86">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="E3" s="86">
+        <v>72.64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="86">
+        <v>2</v>
+      </c>
+      <c r="B4" s="86">
+        <v>1</v>
+      </c>
+      <c r="C4" s="89">
+        <v>2.0049999999999999</v>
+      </c>
+      <c r="D4" s="86">
+        <v>6.1</v>
+      </c>
+      <c r="E4" s="86">
+        <v>13.62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="86">
+        <v>3</v>
+      </c>
+      <c r="B5" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C5" s="89">
+        <v>2.0840000000000001</v>
+      </c>
+      <c r="D5" s="86">
+        <v>6.1</v>
+      </c>
+      <c r="E5" s="88">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="86">
+        <v>4</v>
+      </c>
+      <c r="B6" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C6" s="89">
+        <v>2.0870000000000002</v>
+      </c>
+      <c r="D6" s="86">
+        <v>6.1</v>
+      </c>
+      <c r="E6" s="86">
+        <v>19.46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="86">
+        <v>5</v>
+      </c>
+      <c r="B7" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C7" s="89">
+        <v>2.109</v>
+      </c>
+      <c r="D7" s="86">
+        <v>6.1</v>
+      </c>
+      <c r="E7" s="86">
+        <v>33.049999999999997</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="86">
+        <v>6</v>
+      </c>
+      <c r="B8" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C8" s="89">
+        <v>2.1680000000000001</v>
+      </c>
+      <c r="D8" s="86">
+        <v>6.1</v>
+      </c>
+      <c r="E8" s="86">
+        <v>8.02</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="86">
+        <v>7</v>
+      </c>
+      <c r="B9" s="86">
+        <v>1</v>
+      </c>
+      <c r="C9" s="89">
+        <v>2.0139999999999998</v>
+      </c>
+      <c r="D9" s="86">
+        <v>7.2</v>
+      </c>
+      <c r="E9" s="86">
+        <v>17.22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="86">
+        <v>8</v>
+      </c>
+      <c r="B10" s="86">
+        <v>1</v>
+      </c>
+      <c r="C10" s="89">
+        <v>2.0150000000000001</v>
+      </c>
+      <c r="D10" s="86">
+        <v>7.2</v>
+      </c>
+      <c r="E10" s="86">
+        <v>21.87</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="86">
+        <v>9</v>
+      </c>
+      <c r="B11" s="86">
+        <v>1</v>
+      </c>
+      <c r="C11" s="89">
+        <v>2.016</v>
+      </c>
+      <c r="D11" s="86">
+        <v>7.2</v>
+      </c>
+      <c r="E11" s="86">
+        <v>5.0599999999999996</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="86">
+        <v>10</v>
+      </c>
+      <c r="B12" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C12" s="89">
+        <v>2.089</v>
+      </c>
+      <c r="D12" s="86">
+        <v>7.2</v>
+      </c>
+      <c r="E12" s="86">
+        <v>6.05</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="86">
+        <v>11</v>
+      </c>
+      <c r="B13" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C13" s="89">
+        <v>2.09</v>
+      </c>
+      <c r="D13" s="86">
+        <v>7.2</v>
+      </c>
+      <c r="E13" s="86">
+        <v>12.15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="86">
+        <v>12</v>
+      </c>
+      <c r="B14" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C14" s="89">
+        <v>2.0910000000000002</v>
+      </c>
+      <c r="D14" s="86">
+        <v>7.2</v>
+      </c>
+      <c r="E14" s="86">
+        <v>10.63</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="86">
+        <v>13</v>
+      </c>
+      <c r="B15" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C15" s="89">
+        <v>2.0950000000000002</v>
+      </c>
+      <c r="D15" s="86">
+        <v>7.2</v>
+      </c>
+      <c r="E15" s="86">
+        <v>8.7899999999999991</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="86">
+        <v>14</v>
+      </c>
+      <c r="B16" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C16" s="89">
+        <v>2.0960000000000001</v>
+      </c>
+      <c r="D16" s="86">
+        <v>7.2</v>
+      </c>
+      <c r="E16" s="86">
+        <v>14.39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="86">
+        <v>15</v>
+      </c>
+      <c r="B17" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C17" s="89">
+        <v>2.1</v>
+      </c>
+      <c r="D17" s="86">
+        <v>7.2</v>
+      </c>
+      <c r="E17" s="86">
+        <v>8.19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="86">
+        <v>16</v>
+      </c>
+      <c r="B18" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C18" s="89">
+        <v>2.101</v>
+      </c>
+      <c r="D18" s="86">
+        <v>7.2</v>
+      </c>
+      <c r="E18" s="86">
+        <v>12.22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="86">
+        <v>17</v>
+      </c>
+      <c r="B19" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C19" s="89">
+        <v>2.1040000000000001</v>
+      </c>
+      <c r="D19" s="86">
+        <v>7.2</v>
+      </c>
+      <c r="E19" s="86">
+        <v>8.4499999999999993</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="86">
+        <v>18</v>
+      </c>
+      <c r="B20" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C20" s="89">
+        <v>2.105</v>
+      </c>
+      <c r="D20" s="86">
+        <v>7.2</v>
+      </c>
+      <c r="E20" s="86">
+        <v>14.25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="86">
+        <v>19</v>
+      </c>
+      <c r="B21" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C21" s="89">
+        <v>2.1070000000000002</v>
+      </c>
+      <c r="D21" s="86">
+        <v>7.2</v>
+      </c>
+      <c r="E21" s="86">
+        <v>8.14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="86">
+        <v>20</v>
+      </c>
+      <c r="B22" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C22" s="89">
+        <v>2.1080000000000001</v>
+      </c>
+      <c r="D22" s="86">
+        <v>7.2</v>
+      </c>
+      <c r="E22" s="86">
+        <v>16.28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="57"/>
+      <c r="B23" s="34"/>
+      <c r="C23" s="54"/>
+      <c r="D23" s="34" t="s">
+        <v>52</v>
+      </c>
+      <c r="E23" s="72">
+        <f>SUM(E3:E22)</f>
+        <v>326.48</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor theme="5" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="4" width="6.140625" customWidth="1"/>
+    <col min="5" max="5" width="8" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="93" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1" s="94"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="95"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="77" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="65" t="s">
+        <v>97</v>
+      </c>
+      <c r="C2" s="78" t="s">
+        <v>98</v>
+      </c>
+      <c r="D2" s="65" t="s">
+        <v>93</v>
+      </c>
+      <c r="E2" s="79" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="68">
+        <v>1</v>
+      </c>
+      <c r="B3" s="64">
+        <v>1</v>
+      </c>
+      <c r="C3" s="8">
+        <v>3.0059999999999998</v>
+      </c>
+      <c r="D3" s="64">
+        <v>6.1</v>
+      </c>
+      <c r="E3" s="76">
+        <v>13.62</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="68">
+        <v>2</v>
+      </c>
+      <c r="B4" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C4" s="8">
+        <v>3.0939999999999999</v>
+      </c>
+      <c r="D4" s="64">
+        <v>6.1</v>
+      </c>
+      <c r="E4" s="76">
+        <v>15.07</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="68">
+        <v>3</v>
+      </c>
+      <c r="B5" s="64">
+        <v>1</v>
+      </c>
+      <c r="C5" s="8">
+        <v>3.0150000000000001</v>
+      </c>
+      <c r="D5" s="64">
+        <v>7.2</v>
+      </c>
+      <c r="E5" s="76">
+        <v>17.21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="68">
+        <v>4</v>
+      </c>
+      <c r="B6" s="64">
+        <v>1</v>
+      </c>
+      <c r="C6" s="8">
+        <v>3.016</v>
+      </c>
+      <c r="D6" s="64">
+        <v>7.2</v>
+      </c>
+      <c r="E6" s="76">
+        <v>21.12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="68">
+        <v>5</v>
+      </c>
+      <c r="B7" s="64">
+        <v>1</v>
+      </c>
+      <c r="C7" s="8">
+        <v>3.0169999999999999</v>
+      </c>
+      <c r="D7" s="64">
+        <v>7.2</v>
+      </c>
+      <c r="E7" s="76">
+        <v>5.0599999999999996</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="57"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="34" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" s="72">
+        <f>SUM(E3:E7)</f>
+        <v>72.08</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF00B0F0"/>
+  </sheetPr>
+  <dimension ref="A1:I106"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="9.140625" style="63"/>
+    <col min="5" max="5" width="10.7109375" style="61" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="93" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="94"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="95"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="77" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="65" t="s">
+        <v>97</v>
+      </c>
+      <c r="C2" s="78" t="s">
+        <v>98</v>
+      </c>
+      <c r="D2" s="65" t="s">
+        <v>93</v>
+      </c>
+      <c r="E2" s="85" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="68">
+        <v>1</v>
+      </c>
+      <c r="B3" s="64">
+        <v>1</v>
+      </c>
+      <c r="C3" s="64">
+        <v>1.024</v>
+      </c>
+      <c r="D3" s="64">
+        <v>6</v>
+      </c>
+      <c r="E3" s="76">
+        <v>13.62</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="68">
+        <v>2</v>
+      </c>
+      <c r="B4" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C4" s="64">
+        <v>1.0449999999999999</v>
+      </c>
+      <c r="D4" s="64">
+        <v>6</v>
+      </c>
+      <c r="E4" s="76">
+        <v>161.78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="68">
+        <v>3</v>
+      </c>
+      <c r="B5" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C5" s="64">
+        <v>1.046</v>
+      </c>
+      <c r="D5" s="64">
+        <v>6</v>
+      </c>
+      <c r="E5" s="76">
+        <v>161.15</v>
+      </c>
+      <c r="G5">
+        <f t="shared" ref="G5:G18" si="0">--MID($G$62,IF(ROW(A2)=1,1,FIND("; ",$G$62,FIND("; ",$G$62,1)*(ROW(A2)-1))+2),FIND("; ",$G$62&amp;"; ",IF(ROW(A2)=1,1,FIND("; ",$G$62,FIND("; ",$G$62,1)*(ROW(A2)-1))+2))-IF(ROW(A2)=1,1,FIND("; ",$G$62,FIND("; ",$G$62,1)*(ROW(A2)-1))+2))</f>
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="68">
+        <v>4</v>
+      </c>
+      <c r="B6" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C6" s="64">
+        <v>1.0529999999999999</v>
+      </c>
+      <c r="D6" s="64">
+        <v>6</v>
+      </c>
+      <c r="E6" s="76">
+        <v>443.48</v>
+      </c>
+      <c r="G6" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="68">
+        <v>5</v>
+      </c>
+      <c r="B7" s="64">
+        <v>1</v>
+      </c>
+      <c r="C7" s="64">
+        <v>1.034</v>
+      </c>
+      <c r="D7" s="64">
+        <v>7</v>
+      </c>
+      <c r="E7" s="76">
+        <v>17.22</v>
+      </c>
+      <c r="G7" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="68">
+        <v>6</v>
+      </c>
+      <c r="B8" s="64">
+        <v>1</v>
+      </c>
+      <c r="C8" s="64">
+        <v>1.0349999999999999</v>
+      </c>
+      <c r="D8" s="64">
+        <v>7</v>
+      </c>
+      <c r="E8" s="76">
+        <v>21.63</v>
+      </c>
+      <c r="G8" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="68">
+        <v>7</v>
+      </c>
+      <c r="B9" s="64">
+        <v>1</v>
+      </c>
+      <c r="C9" s="64">
+        <v>1.036</v>
+      </c>
+      <c r="D9" s="64">
+        <v>7</v>
+      </c>
+      <c r="E9" s="76">
+        <v>5.76</v>
+      </c>
+      <c r="G9" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="68">
+        <v>8</v>
+      </c>
+      <c r="B10" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C10" s="64">
+        <v>1.054</v>
+      </c>
+      <c r="D10" s="64">
+        <v>7</v>
+      </c>
+      <c r="E10" s="76">
+        <v>14.54</v>
+      </c>
+      <c r="G10" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="68">
+        <v>9</v>
+      </c>
+      <c r="B11" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C11" s="64">
+        <v>1.054</v>
+      </c>
+      <c r="D11" s="64">
+        <v>7.1</v>
+      </c>
+      <c r="E11" s="76">
+        <v>46.62</v>
+      </c>
+      <c r="G11" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="68">
+        <v>10</v>
+      </c>
+      <c r="B12" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C12" s="64">
+        <v>1.048</v>
+      </c>
+      <c r="D12" s="64">
+        <v>8.1</v>
+      </c>
+      <c r="E12" s="76">
+        <v>23.92</v>
+      </c>
+      <c r="G12" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="68">
+        <v>11</v>
+      </c>
+      <c r="B13" s="64">
+        <v>1</v>
+      </c>
+      <c r="C13" s="64">
+        <v>1.0369999999999999</v>
+      </c>
+      <c r="D13" s="64">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="E13" s="76">
+        <v>3.34</v>
+      </c>
+      <c r="G13" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="68">
+        <v>12</v>
+      </c>
+      <c r="B14" s="64">
+        <v>1</v>
+      </c>
+      <c r="C14" s="64">
+        <v>1.038</v>
+      </c>
+      <c r="D14" s="64">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="E14" s="76">
+        <v>5.25</v>
+      </c>
+      <c r="G14" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="68">
+        <v>13</v>
+      </c>
+      <c r="B15" s="64">
+        <v>1</v>
+      </c>
+      <c r="C15" s="8">
+        <v>1.026</v>
+      </c>
+      <c r="D15" s="64">
+        <v>9</v>
+      </c>
+      <c r="E15" s="76">
+        <v>191.68</v>
+      </c>
+      <c r="G15" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="68">
+        <v>14</v>
+      </c>
+      <c r="B16" s="64">
+        <v>1</v>
+      </c>
+      <c r="C16" s="54">
+        <v>1.0269999999999999</v>
+      </c>
+      <c r="D16" s="64">
+        <v>9</v>
+      </c>
+      <c r="E16" s="76">
+        <v>114.04</v>
+      </c>
+      <c r="G16" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="68">
+        <v>15</v>
+      </c>
+      <c r="B17" s="64">
+        <v>1</v>
+      </c>
+      <c r="C17" s="54">
+        <v>1.028</v>
+      </c>
+      <c r="D17" s="64">
+        <v>9</v>
+      </c>
+      <c r="E17" s="76">
+        <v>68.81</v>
+      </c>
+      <c r="G17" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="68">
+        <v>16</v>
+      </c>
+      <c r="B18" s="64">
+        <v>1</v>
+      </c>
+      <c r="C18" s="54">
+        <v>1.0289999999999999</v>
+      </c>
+      <c r="D18" s="64">
+        <v>9</v>
+      </c>
+      <c r="E18" s="76">
+        <v>68.81</v>
+      </c>
+      <c r="G18" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="68">
+        <v>17</v>
+      </c>
+      <c r="B19" s="64">
+        <v>1</v>
+      </c>
+      <c r="C19" s="54">
+        <v>1.03</v>
+      </c>
+      <c r="D19" s="64">
+        <v>9</v>
+      </c>
+      <c r="E19" s="76">
+        <v>68.89</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="68">
+        <v>18</v>
+      </c>
+      <c r="B20" s="64">
+        <v>1</v>
+      </c>
+      <c r="C20" s="54">
+        <v>1.0309999999999999</v>
+      </c>
+      <c r="D20" s="64">
+        <v>9</v>
+      </c>
+      <c r="E20" s="76">
+        <v>68.89</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="68">
+        <v>19</v>
+      </c>
+      <c r="B21" s="64">
+        <v>1</v>
+      </c>
+      <c r="C21" s="54">
+        <v>1.032</v>
+      </c>
+      <c r="D21" s="64">
+        <v>9</v>
+      </c>
+      <c r="E21" s="76">
+        <v>68.069999999999993</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="68">
+        <v>20</v>
+      </c>
+      <c r="B22" s="64">
+        <v>1</v>
+      </c>
+      <c r="C22" s="54">
+        <v>1.0329999999999999</v>
+      </c>
+      <c r="D22" s="64">
+        <v>9</v>
+      </c>
+      <c r="E22" s="76">
+        <v>139.1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="68">
+        <v>21</v>
+      </c>
+      <c r="B23" s="64">
+        <v>1</v>
+      </c>
+      <c r="C23" s="54">
+        <v>1.0389999999999999</v>
+      </c>
+      <c r="D23" s="64">
+        <v>9</v>
+      </c>
+      <c r="E23" s="76">
+        <v>149.69999999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="68">
+        <v>22</v>
+      </c>
+      <c r="B24" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C24" s="54">
+        <v>1.04</v>
+      </c>
+      <c r="D24" s="64">
+        <v>9</v>
+      </c>
+      <c r="E24" s="76">
+        <v>220.47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="68">
+        <v>23</v>
+      </c>
+      <c r="B25" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C25" s="54">
+        <v>1.0429999999999999</v>
+      </c>
+      <c r="D25" s="64">
+        <v>9</v>
+      </c>
+      <c r="E25" s="76">
+        <v>61.99</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="68">
+        <v>24</v>
+      </c>
+      <c r="B26" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C26" s="54">
+        <v>1.044</v>
+      </c>
+      <c r="D26" s="64">
+        <v>9</v>
+      </c>
+      <c r="E26" s="76">
+        <v>14.14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="68">
+        <v>25</v>
+      </c>
+      <c r="B27" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C27" s="54">
+        <v>1.0489999999999999</v>
+      </c>
+      <c r="D27" s="64">
+        <v>9</v>
+      </c>
+      <c r="E27" s="76">
+        <v>103.8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="68">
+        <v>26</v>
+      </c>
+      <c r="B28" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C28" s="54">
+        <v>1.05</v>
+      </c>
+      <c r="D28" s="64">
+        <v>9</v>
+      </c>
+      <c r="E28" s="76">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="80">
+        <v>27</v>
+      </c>
+      <c r="B29" s="81">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C29" s="82">
+        <v>1.0509999999999999</v>
+      </c>
+      <c r="D29" s="81">
+        <v>9</v>
+      </c>
+      <c r="E29" s="83">
+        <v>31.58</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="56"/>
+      <c r="B30" s="34"/>
+      <c r="C30" s="54"/>
+      <c r="D30" s="34"/>
+      <c r="E30" s="60"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="58" t="s">
+        <v>48</v>
+      </c>
+      <c r="B31" s="58"/>
+      <c r="C31" s="62"/>
+      <c r="D31" s="58"/>
+      <c r="E31" s="60"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="77" t="s">
+        <v>0</v>
+      </c>
+      <c r="B32" s="65" t="s">
+        <v>97</v>
+      </c>
+      <c r="C32" s="78" t="s">
+        <v>98</v>
+      </c>
+      <c r="D32" s="65" t="s">
+        <v>93</v>
+      </c>
+      <c r="E32" s="79" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="68">
+        <v>1</v>
+      </c>
+      <c r="B33" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C33" s="8">
+        <v>2.16</v>
+      </c>
+      <c r="D33" s="64">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="E33" s="76">
+        <v>72.64</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="68">
+        <v>2</v>
+      </c>
+      <c r="B34" s="64">
+        <v>1</v>
+      </c>
+      <c r="C34" s="8">
+        <v>2.0049999999999999</v>
+      </c>
+      <c r="D34" s="64">
+        <v>6.1</v>
+      </c>
+      <c r="E34" s="76">
+        <v>13.62</v>
+      </c>
+      <c r="G34">
+        <v>73.55</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="68">
+        <v>3</v>
+      </c>
+      <c r="B35" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C35" s="8">
+        <v>2.0840000000000001</v>
+      </c>
+      <c r="D35" s="64">
+        <v>6.1</v>
+      </c>
+      <c r="E35" s="76">
+        <v>16</v>
+      </c>
+      <c r="G35">
+        <v>72.239999999999995</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="90">
+        <v>4</v>
+      </c>
+      <c r="B36" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C36" s="8">
+        <v>2.0870000000000002</v>
+      </c>
+      <c r="D36" s="64">
+        <v>6.1</v>
+      </c>
+      <c r="E36" s="76">
+        <v>19.46</v>
+      </c>
+      <c r="G36">
+        <v>68.260000000000005</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="68">
+        <v>5</v>
+      </c>
+      <c r="B37" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C37" s="8">
+        <v>2.109</v>
+      </c>
+      <c r="D37" s="64">
+        <v>6.1</v>
+      </c>
+      <c r="E37" s="76">
+        <v>33.049999999999997</v>
+      </c>
+      <c r="G37">
+        <v>158.71</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="68">
+        <v>6</v>
+      </c>
+      <c r="B38" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C38" s="8">
+        <v>2.1680000000000001</v>
+      </c>
+      <c r="D38" s="64">
+        <v>6.1</v>
+      </c>
+      <c r="E38" s="76">
+        <v>8.02</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="68">
+        <v>7</v>
+      </c>
+      <c r="B39" s="64">
+        <v>1</v>
+      </c>
+      <c r="C39" s="64">
+        <v>2.0139999999999998</v>
+      </c>
+      <c r="D39" s="64">
+        <v>7.2</v>
+      </c>
+      <c r="E39" s="76">
+        <v>17.22</v>
+      </c>
+      <c r="G39">
+        <v>68.3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="68">
+        <v>8</v>
+      </c>
+      <c r="B40" s="64">
+        <v>1</v>
+      </c>
+      <c r="C40" s="64">
+        <v>2.0150000000000001</v>
+      </c>
+      <c r="D40" s="64">
+        <v>7.2</v>
+      </c>
+      <c r="E40" s="76">
+        <v>21.87</v>
+      </c>
+      <c r="G40">
+        <v>68.459999999999994</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="68">
+        <v>9</v>
+      </c>
+      <c r="B41" s="64">
+        <v>1</v>
+      </c>
+      <c r="C41" s="64">
+        <v>2.016</v>
+      </c>
+      <c r="D41" s="64">
+        <v>7.2</v>
+      </c>
+      <c r="E41" s="76">
+        <v>5.0599999999999996</v>
+      </c>
+      <c r="G41">
+        <v>68.459999999999994</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="68">
+        <v>10</v>
+      </c>
+      <c r="B42" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C42" s="54">
+        <v>2.089</v>
+      </c>
+      <c r="D42" s="64">
+        <v>7.2</v>
+      </c>
+      <c r="E42" s="76">
+        <v>6.05</v>
+      </c>
+      <c r="G42">
+        <v>67.64</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="68">
+        <v>11</v>
+      </c>
+      <c r="B43" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C43" s="54">
+        <v>2.09</v>
+      </c>
+      <c r="D43" s="64">
+        <v>7.2</v>
+      </c>
+      <c r="E43" s="76">
+        <v>12.15</v>
+      </c>
+      <c r="G43">
+        <v>68.459999999999994</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="68">
+        <v>12</v>
+      </c>
+      <c r="B44" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C44" s="54">
+        <v>2.0910000000000002</v>
+      </c>
+      <c r="D44" s="64">
+        <v>7.2</v>
+      </c>
+      <c r="E44" s="76">
+        <v>10.63</v>
+      </c>
+      <c r="G44">
+        <v>149.25</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="68">
+        <v>13</v>
+      </c>
+      <c r="B45" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C45" s="54">
+        <v>2.0950000000000002</v>
+      </c>
+      <c r="D45" s="64">
+        <v>7.2</v>
+      </c>
+      <c r="E45" s="76">
+        <v>8.7899999999999991</v>
+      </c>
+      <c r="G45">
+        <v>68.459999999999994</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="68">
+        <v>14</v>
+      </c>
+      <c r="B46" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C46" s="54">
+        <v>2.0960000000000001</v>
+      </c>
+      <c r="D46" s="64">
+        <v>7.2</v>
+      </c>
+      <c r="E46" s="76">
+        <v>14.39</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="68">
+        <v>15</v>
+      </c>
+      <c r="B47" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C47" s="54">
+        <v>2.1</v>
+      </c>
+      <c r="D47" s="64">
+        <v>7.2</v>
+      </c>
+      <c r="E47" s="76">
+        <v>8.19</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="68">
+        <v>16</v>
+      </c>
+      <c r="B48" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C48" s="54">
+        <v>2.101</v>
+      </c>
+      <c r="D48" s="64">
+        <v>7.2</v>
+      </c>
+      <c r="E48" s="76">
+        <v>12.22</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="68">
+        <v>17</v>
+      </c>
+      <c r="B49" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C49" s="54">
+        <v>2.1040000000000001</v>
+      </c>
+      <c r="D49" s="64">
+        <v>7.2</v>
+      </c>
+      <c r="E49" s="76">
+        <v>8.4499999999999993</v>
+      </c>
+      <c r="G49">
+        <v>79.790000000000006</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="68">
+        <v>18</v>
+      </c>
+      <c r="B50" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C50" s="54">
+        <v>2.105</v>
+      </c>
+      <c r="D50" s="64">
+        <v>7.2</v>
+      </c>
+      <c r="E50" s="76">
+        <v>14.25</v>
+      </c>
+      <c r="G50">
+        <v>170.56</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="68">
+        <v>19</v>
+      </c>
+      <c r="B51" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C51" s="54">
+        <v>2.1070000000000002</v>
+      </c>
+      <c r="D51" s="64">
+        <v>7.2</v>
+      </c>
+      <c r="E51" s="84">
+        <v>8.14</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="80">
+        <v>20</v>
+      </c>
+      <c r="B52" s="81">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C52" s="82">
+        <v>2.1080000000000001</v>
+      </c>
+      <c r="D52" s="81">
+        <v>7.2</v>
+      </c>
+      <c r="E52" s="87">
+        <v>16.28</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="75">
+        <v>21</v>
+      </c>
+      <c r="B53" s="64">
+        <v>1</v>
+      </c>
+      <c r="C53" s="54">
+        <v>2.0169999999999999</v>
+      </c>
+      <c r="D53" s="64">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="E53" s="76">
+        <v>3.22</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="75">
+        <v>22</v>
+      </c>
+      <c r="B54" s="64">
+        <v>1</v>
+      </c>
+      <c r="C54" s="54">
+        <v>2.1619999999999999</v>
+      </c>
+      <c r="D54" s="64">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="E54" s="76">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="75">
+        <v>23</v>
+      </c>
+      <c r="B55" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C55" s="54">
+        <v>2.097</v>
+      </c>
+      <c r="D55" s="64">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="E55" s="76">
+        <v>4.8499999999999996</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="75">
+        <v>24</v>
+      </c>
+      <c r="B56" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C56" s="54">
+        <v>2.0979999999999999</v>
+      </c>
+      <c r="D56" s="64">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="E56" s="76">
+        <v>4.76</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="75">
+        <v>25</v>
+      </c>
+      <c r="B57" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C57" s="54">
+        <v>2.1019999999999999</v>
+      </c>
+      <c r="D57" s="64">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="E57" s="76">
+        <v>9.24</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="75">
+        <v>34</v>
+      </c>
+      <c r="B58" s="64">
+        <v>1</v>
+      </c>
+      <c r="C58" s="54">
+        <v>2.0009999999999999</v>
+      </c>
+      <c r="D58" s="64">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="E58" s="76">
+        <v>73.55</v>
+      </c>
+      <c r="G58">
+        <v>10.24</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="75">
+        <v>33</v>
+      </c>
+      <c r="B59" s="64">
+        <v>1</v>
+      </c>
+      <c r="C59" s="54">
+        <v>2.0019999999999998</v>
+      </c>
+      <c r="D59" s="64">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="E59" s="76">
+        <v>72.239999999999995</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="75">
+        <v>27</v>
+      </c>
+      <c r="B60" s="64">
+        <v>1</v>
+      </c>
+      <c r="C60" s="54">
+        <v>2.0030000000000001</v>
+      </c>
+      <c r="D60" s="64">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="E60" s="76">
+        <v>68.260000000000005</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="75">
+        <v>36</v>
+      </c>
+      <c r="B61" s="64">
+        <v>1</v>
+      </c>
+      <c r="C61" s="54">
+        <v>2.004</v>
+      </c>
+      <c r="D61" s="64">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="E61" s="76">
+        <v>158.71</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="75">
+        <v>30</v>
+      </c>
+      <c r="B62" s="64">
+        <v>1</v>
+      </c>
+      <c r="C62" s="54">
+        <v>2.0070000000000001</v>
+      </c>
+      <c r="D62" s="64">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="E62" s="76">
+        <v>68.3</v>
+      </c>
+      <c r="G62" t="s">
+        <v>112</v>
+      </c>
+      <c r="I62">
+        <v>23.36</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="75">
+        <v>32</v>
+      </c>
+      <c r="B63" s="64">
+        <v>1</v>
+      </c>
+      <c r="C63" s="54">
+        <v>2.008</v>
+      </c>
+      <c r="D63" s="64">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="E63" s="76">
+        <v>68.459999999999994</v>
+      </c>
+      <c r="G63">
+        <f t="shared" ref="G63:G68" si="1">--MID($G$62,IF(ROW(A1)=1,1,FIND("; ",$G$62,FIND("; ",$G$62,1)*(ROW(A1)-1))+2),FIND("; ",$G$62&amp;"; ",IF(ROW(A1)=1,1,FIND("; ",$G$62,FIND("; ",$G$62,1)*(ROW(A1)-1))+2))-IF(ROW(A1)=1,1,FIND("; ",$G$62,FIND("; ",$G$62,1)*(ROW(A1)-1))+2))</f>
+        <v>2.0750000000000002</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="75">
+        <v>31</v>
+      </c>
+      <c r="B64" s="64">
+        <v>1</v>
+      </c>
+      <c r="C64" s="54">
+        <v>2.0089999999999999</v>
+      </c>
+      <c r="D64" s="64">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="E64" s="76">
+        <v>68.459999999999994</v>
+      </c>
+      <c r="G64">
+        <f t="shared" si="1"/>
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="75">
+        <v>26</v>
+      </c>
+      <c r="B65" s="64">
+        <v>1</v>
+      </c>
+      <c r="C65" s="54">
+        <v>2.0099999999999998</v>
+      </c>
+      <c r="D65" s="64">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="E65" s="76">
+        <v>67.64</v>
+      </c>
+      <c r="G65" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="I65">
+        <v>21.09</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="75">
+        <v>28</v>
+      </c>
+      <c r="B66" s="64">
+        <v>1</v>
+      </c>
+      <c r="C66" s="54">
+        <v>2.0110000000000001</v>
+      </c>
+      <c r="D66" s="64">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="E66" s="76">
+        <v>68.459999999999994</v>
+      </c>
+      <c r="G66" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="75">
+        <v>35</v>
+      </c>
+      <c r="B67" s="64">
+        <v>1</v>
+      </c>
+      <c r="C67" s="54">
+        <v>2.012</v>
+      </c>
+      <c r="D67" s="64">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="E67" s="76">
+        <v>149.25</v>
+      </c>
+      <c r="G67" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="75">
+        <v>29</v>
+      </c>
+      <c r="B68" s="64">
+        <v>1</v>
+      </c>
+      <c r="C68" s="54">
+        <v>2.0129999999999999</v>
+      </c>
+      <c r="D68" s="64">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="E68" s="76">
+        <v>68.459999999999994</v>
+      </c>
+      <c r="G68" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="I68">
+        <v>19.329999999999998</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="75">
+        <v>42</v>
+      </c>
+      <c r="B69" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C69" s="54">
+        <v>2.0750000000000002</v>
+      </c>
+      <c r="D69" s="64">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="E69" s="76">
+        <v>79.790000000000006</v>
+      </c>
+      <c r="G69" t="e">
+        <f t="shared" ref="G69:G79" si="2">--MID($G$62,IF(ROW(A7)=1,1,FIND("; ",$G$62,FIND("; ",$G$62,1)*(ROW(A7)-1))+2),FIND("; ",$G$62&amp;"; ",IF(ROW(A7)=1,1,FIND("; ",$G$62,FIND("; ",$G$62,1)*(ROW(A7)-1))+2))-IF(ROW(A7)=1,1,FIND("; ",$G$62,FIND("; ",$G$62,1)*(ROW(A7)-1))+2))</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="75">
+        <v>43</v>
+      </c>
+      <c r="B70" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C70" s="54">
+        <v>2.08</v>
+      </c>
+      <c r="D70" s="64">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="E70" s="76">
+        <v>170.56</v>
+      </c>
+      <c r="G70" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="75">
+        <v>37</v>
+      </c>
+      <c r="B71" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C71" s="54">
+        <v>2.0880000000000001</v>
+      </c>
+      <c r="D71" s="64">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="E71" s="76">
+        <v>10.24</v>
+      </c>
+      <c r="G71" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="I71">
+        <v>19.36</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="75">
+        <v>41</v>
+      </c>
+      <c r="B72" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C72" s="54">
+        <v>2.0939999999999999</v>
+      </c>
+      <c r="D72" s="64">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="E72" s="76">
+        <v>23.36</v>
+      </c>
+      <c r="G72" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="90">
+        <v>40</v>
+      </c>
+      <c r="B73" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C73" s="54">
+        <v>2.0990000000000002</v>
+      </c>
+      <c r="D73" s="64">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="E73" s="76">
+        <v>21.09</v>
+      </c>
+      <c r="G73" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="75">
+        <v>39</v>
+      </c>
+      <c r="B74" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C74" s="54">
+        <v>2.1030000000000002</v>
+      </c>
+      <c r="D74" s="64">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="E74" s="76">
+        <v>19.329999999999998</v>
+      </c>
+      <c r="G74" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="75">
+        <v>38</v>
+      </c>
+      <c r="B75" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C75" s="54">
+        <v>2.1059999999999999</v>
+      </c>
+      <c r="D75" s="64">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="E75" s="76">
+        <v>19.36</v>
+      </c>
+      <c r="G75" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="75">
+        <v>44</v>
+      </c>
+      <c r="B76" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C76" s="54">
+        <v>2.081</v>
+      </c>
+      <c r="D76" s="64">
+        <v>11</v>
+      </c>
+      <c r="E76" s="76">
+        <v>298.27999999999997</v>
+      </c>
+      <c r="G76" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="I76">
+        <v>298.27999999999997</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="75">
+        <v>45</v>
+      </c>
+      <c r="B77" s="81">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C77" s="82">
+        <v>2.085</v>
+      </c>
+      <c r="D77" s="81">
+        <v>11.1</v>
+      </c>
+      <c r="E77" s="83">
+        <v>168.62</v>
+      </c>
+      <c r="G77" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="H77">
+        <v>168.62</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A78" s="74"/>
+      <c r="B78" s="34"/>
+      <c r="C78" s="54"/>
+      <c r="D78" s="34"/>
+      <c r="E78" s="66"/>
+      <c r="G78" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G79" t="e">
+        <f t="shared" si="2"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A80" s="58" t="s">
+        <v>48</v>
+      </c>
+      <c r="B80" s="58"/>
+      <c r="C80" s="62"/>
+      <c r="D80" s="58"/>
+      <c r="E80" s="60"/>
+      <c r="G80" t="e">
+        <f>--MID($G$62,IF(ROW(A18)=1,1,FIND("; ",$G$62,FIND("; ",$G$62,1)*(ROW(A18)-1))+2),FIND("; ",$G$62&amp;"; ",IF(ROW(A18)=1,1,FIND("; ",$G$62,FIND("; ",$G$62,1)*(ROW(A18)-1))+2))-IF(ROW(A18)=1,1,FIND("; ",$G$62,FIND("; ",$G$62,1)*(ROW(A18)-1))+2))</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A81" s="77" t="s">
+        <v>0</v>
+      </c>
+      <c r="B81" s="65" t="s">
+        <v>97</v>
+      </c>
+      <c r="C81" s="78" t="s">
+        <v>98</v>
+      </c>
+      <c r="D81" s="65" t="s">
+        <v>93</v>
+      </c>
+      <c r="E81" s="79" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A82" s="68">
+        <v>1</v>
+      </c>
+      <c r="B82" s="64">
+        <v>1</v>
+      </c>
+      <c r="C82" s="8">
+        <v>3.0059999999999998</v>
+      </c>
+      <c r="D82" s="64">
+        <v>6.1</v>
+      </c>
+      <c r="E82" s="76">
+        <v>13.62</v>
+      </c>
+      <c r="I82">
+        <v>129.68</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A83" s="68">
+        <v>2</v>
+      </c>
+      <c r="B83" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C83" s="8">
+        <v>3.0939999999999999</v>
+      </c>
+      <c r="D83" s="64">
+        <v>6.1</v>
+      </c>
+      <c r="E83" s="76">
+        <v>15.07</v>
+      </c>
+      <c r="I83">
+        <v>73.05</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A84" s="68">
+        <v>3</v>
+      </c>
+      <c r="B84" s="64">
+        <v>1</v>
+      </c>
+      <c r="C84" s="8">
+        <v>3.0150000000000001</v>
+      </c>
+      <c r="D84" s="64">
+        <v>7.2</v>
+      </c>
+      <c r="E84" s="76">
+        <v>17.21</v>
+      </c>
+      <c r="I84">
+        <v>71.709999999999994</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A85" s="68">
+        <v>4</v>
+      </c>
+      <c r="B85" s="64">
+        <v>1</v>
+      </c>
+      <c r="C85" s="8">
+        <v>3.016</v>
+      </c>
+      <c r="D85" s="64">
+        <v>7.2</v>
+      </c>
+      <c r="E85" s="76">
+        <v>21.12</v>
+      </c>
+      <c r="I85">
+        <v>67.59</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A86" s="68">
+        <v>5</v>
+      </c>
+      <c r="B86" s="64">
+        <v>1</v>
+      </c>
+      <c r="C86" s="8">
+        <v>3.0169999999999999</v>
+      </c>
+      <c r="D86" s="64">
+        <v>7.2</v>
+      </c>
+      <c r="E86" s="76">
+        <v>5.0599999999999996</v>
+      </c>
+      <c r="I86">
+        <v>239.62</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A87" s="68">
+        <v>9</v>
+      </c>
+      <c r="B87" s="64">
+        <v>1</v>
+      </c>
+      <c r="C87" s="64">
+        <v>3.0009999999999999</v>
+      </c>
+      <c r="D87" s="64">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="E87" s="76">
+        <v>129.68</v>
+      </c>
+      <c r="I87">
+        <v>13.62</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A88" s="68">
+        <v>10</v>
+      </c>
+      <c r="B88" s="64">
+        <v>1</v>
+      </c>
+      <c r="C88" s="64">
+        <v>3.0019999999999998</v>
+      </c>
+      <c r="D88" s="64">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="E88" s="76">
+        <v>73.05</v>
+      </c>
+      <c r="I88">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A89" s="68">
+        <v>11</v>
+      </c>
+      <c r="B89" s="64">
+        <v>1</v>
+      </c>
+      <c r="C89" s="54">
+        <v>3.0030000000000001</v>
+      </c>
+      <c r="D89" s="64">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="E89" s="76">
+        <v>71.709999999999994</v>
+      </c>
+      <c r="I89">
+        <v>67.84</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A90" s="68">
+        <v>12</v>
+      </c>
+      <c r="B90" s="64">
+        <v>1</v>
+      </c>
+      <c r="C90" s="54">
+        <v>3.004</v>
+      </c>
+      <c r="D90" s="64">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="E90" s="76">
+        <v>67.59</v>
+      </c>
+      <c r="I90">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A91" s="68">
+        <v>13</v>
+      </c>
+      <c r="B91" s="64">
+        <v>1</v>
+      </c>
+      <c r="C91" s="54">
+        <v>3.0049999999999999</v>
+      </c>
+      <c r="D91" s="64">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="E91" s="76">
+        <v>239.62</v>
+      </c>
+      <c r="I91">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A92" s="68">
+        <v>14</v>
+      </c>
+      <c r="B92" s="64">
+        <v>1</v>
+      </c>
+      <c r="C92" s="54">
+        <v>3.008</v>
+      </c>
+      <c r="D92" s="64">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="E92" s="76">
+        <v>67.84</v>
+      </c>
+      <c r="I92">
+        <v>67.14</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A93" s="68">
+        <v>15</v>
+      </c>
+      <c r="B93" s="64">
+        <v>1</v>
+      </c>
+      <c r="C93" s="54">
+        <v>3.0089999999999999</v>
+      </c>
+      <c r="D93" s="64">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="E93" s="76">
+        <v>68</v>
+      </c>
+      <c r="I93">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A94" s="68">
+        <v>16</v>
+      </c>
+      <c r="B94" s="64">
+        <v>1</v>
+      </c>
+      <c r="C94" s="54">
+        <v>3.01</v>
+      </c>
+      <c r="D94" s="64">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="E94" s="76">
+        <v>68</v>
+      </c>
+      <c r="I94">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A95" s="68">
+        <v>17</v>
+      </c>
+      <c r="B95" s="64">
+        <v>1</v>
+      </c>
+      <c r="C95" s="54">
+        <v>3.0110000000000001</v>
+      </c>
+      <c r="D95" s="64">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="E95" s="76">
+        <v>67.14</v>
+      </c>
+      <c r="I95">
+        <v>148.61000000000001</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A96" s="68">
+        <v>18</v>
+      </c>
+      <c r="B96" s="64">
+        <v>1</v>
+      </c>
+      <c r="C96" s="54">
+        <v>3.012</v>
+      </c>
+      <c r="D96" s="64">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="E96" s="76">
+        <v>68</v>
+      </c>
+      <c r="I96">
+        <v>17.21</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A97" s="68">
+        <v>19</v>
+      </c>
+      <c r="B97" s="64">
+        <v>1</v>
+      </c>
+      <c r="C97" s="54">
+        <v>3.0129999999999999</v>
+      </c>
+      <c r="D97" s="64">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="E97" s="76">
+        <v>68</v>
+      </c>
+      <c r="I97">
+        <v>21.12</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="68">
+        <v>6</v>
+      </c>
+      <c r="B98" s="64">
+        <v>1</v>
+      </c>
+      <c r="C98" s="8">
+        <v>3.0179999999999998</v>
+      </c>
+      <c r="D98" s="64">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="E98" s="76">
+        <v>3.2</v>
+      </c>
+      <c r="I98">
+        <v>5.0599999999999996</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A99" s="68">
+        <v>20</v>
+      </c>
+      <c r="B99" s="64">
+        <v>1</v>
+      </c>
+      <c r="C99" s="54">
+        <v>3.0139999999999998</v>
+      </c>
+      <c r="D99" s="64">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="E99" s="76">
+        <v>148.61000000000001</v>
+      </c>
+      <c r="I99">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A100" s="68">
+        <v>21</v>
+      </c>
+      <c r="B100" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C100" s="54">
+        <v>3.0190000000000001</v>
+      </c>
+      <c r="D100" s="64">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="E100" s="76">
+        <v>244.28</v>
+      </c>
+      <c r="I100">
+        <v>244.28</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="68">
+        <v>8</v>
+      </c>
+      <c r="B101" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C101" s="64">
+        <v>3.0209999999999999</v>
+      </c>
+      <c r="D101" s="64">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="E101" s="76">
+        <v>15.62</v>
+      </c>
+      <c r="I101">
+        <v>137.72999999999999</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A102" s="68">
+        <v>22</v>
+      </c>
+      <c r="B102" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C102" s="54">
+        <v>3.02</v>
+      </c>
+      <c r="D102" s="64">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="E102" s="76">
+        <v>137.72999999999999</v>
+      </c>
+      <c r="I102">
+        <v>15.62</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="68">
+        <v>7</v>
+      </c>
+      <c r="B103" s="64">
+        <v>1</v>
+      </c>
+      <c r="C103" s="64">
+        <v>3.0920000000000001</v>
+      </c>
+      <c r="D103" s="64">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="E103" s="76">
+        <v>5.24</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A104" s="68">
+        <v>23</v>
+      </c>
+      <c r="B104" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C104" s="54">
+        <v>3.085</v>
+      </c>
+      <c r="D104" s="64">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="E104" s="76">
+        <v>13.16</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A105" s="80">
+        <v>24</v>
+      </c>
+      <c r="B105" s="81">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C105" s="82" t="s">
+        <v>94</v>
+      </c>
+      <c r="D105" s="81">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="E105" s="83">
+        <v>140.80000000000001</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A106" s="57"/>
+      <c r="B106" s="34"/>
+      <c r="C106" s="54"/>
+      <c r="D106" s="34"/>
+      <c r="E106" s="66"/>
+    </row>
+  </sheetData>
+  <sortState ref="C58:C81">
+    <sortCondition ref="C39"/>
+  </sortState>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="3">
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F33"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="7.5703125" customWidth="1"/>
+    <col min="2" max="2" width="39.28515625" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" customWidth="1"/>
+    <col min="6" max="6" width="8.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="15"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="5"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="99">
+        <v>1</v>
+      </c>
+      <c r="B3" s="100" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="101" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="99" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="102">
+        <v>1</v>
+      </c>
+      <c r="F3" s="103">
+        <v>46.62</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="74">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="9"/>
+      <c r="D4" s="74" t="s">
+        <v>41</v>
+      </c>
+      <c r="E4" s="8">
+        <v>8</v>
+      </c>
+      <c r="F4" s="25">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="74">
+        <v>1.2</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="74" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="8">
+        <v>1.8</v>
+      </c>
+      <c r="F5" s="25">
+        <v>3356.64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="74">
+        <v>1.3</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="9"/>
+      <c r="D6" s="74" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F6" s="25">
+        <v>51.281999999999996</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="74">
+        <v>1.4</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" s="74" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" s="8">
+        <v>1</v>
+      </c>
+      <c r="F7" s="25">
+        <v>46.62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="104">
+        <v>2</v>
+      </c>
+      <c r="B8" s="105" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="106" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" s="104" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="107">
+        <v>1</v>
+      </c>
+      <c r="F8" s="50">
+        <f>'1эт'!E9+'2эт'!E14+'3эт'!E7</f>
+        <v>122.87</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="74">
+        <v>2.1</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="9"/>
+      <c r="D9" s="74" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" s="8">
+        <v>8</v>
+      </c>
+      <c r="F9" s="25">
+        <f>ROUNDDOWN(E9*F8,0)</f>
+        <v>982</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="74">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="74" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="8">
+        <v>1.8</v>
+      </c>
+      <c r="F10" s="25">
+        <f>E10*F8*60</f>
+        <v>13269.960000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="74">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="9"/>
+      <c r="D11" s="74" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F11" s="25">
+        <f>E11*F8</f>
+        <v>135.15700000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="74">
+        <v>2.4</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="9"/>
+      <c r="D12" s="74" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="8">
+        <v>1</v>
+      </c>
+      <c r="F12" s="25">
+        <f>E12*F8</f>
+        <v>122.87</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A13" s="111">
+        <v>3</v>
+      </c>
+      <c r="B13" s="112" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="113" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="111" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="114">
+        <v>1</v>
+      </c>
+      <c r="F13" s="115">
+        <f>'1эт'!E46</f>
+        <v>2310.2799999999997</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="74">
+        <v>3.1</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="9"/>
+      <c r="D14" s="74" t="s">
+        <v>41</v>
+      </c>
+      <c r="E14" s="8">
+        <v>8</v>
+      </c>
+      <c r="F14" s="25">
+        <f>ROUNDDOWN(E14*F13,0)</f>
+        <v>18482</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="74">
+        <v>3.2</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="9"/>
+      <c r="D15" s="74" t="s">
+        <v>6</v>
+      </c>
+      <c r="E15" s="8">
+        <v>1.8</v>
+      </c>
+      <c r="F15" s="25">
+        <f>E15*F13*65</f>
+        <v>270302.76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="74">
+        <v>3.3</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="9"/>
+      <c r="D16" s="74" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F16" s="25">
+        <f>E16*F13</f>
+        <v>2541.308</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="74">
+        <v>3.4</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="9"/>
+      <c r="D17" s="74" t="s">
+        <v>5</v>
+      </c>
+      <c r="E17" s="8">
+        <v>1</v>
+      </c>
+      <c r="F17" s="25">
+        <f>E17*F13</f>
+        <v>2310.2799999999997</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="67">
+        <v>4</v>
+      </c>
+      <c r="B18" s="73" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="91" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" s="67" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" s="70">
+        <v>1</v>
+      </c>
+      <c r="F18" s="60">
+        <f>'2эт'!E25</f>
+        <v>466.9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="74">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="9"/>
+      <c r="D19" s="74" t="s">
+        <v>6</v>
+      </c>
+      <c r="E19" s="8">
+        <v>0.255</v>
+      </c>
+      <c r="F19" s="25">
+        <f>E19*F18</f>
+        <v>119.0595</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="74">
+        <v>4.2</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="9"/>
+      <c r="D20" s="74" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="8">
+        <v>1</v>
+      </c>
+      <c r="F20" s="25">
+        <f>E20*F18</f>
+        <v>466.9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="74">
+        <v>4.3</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="9"/>
+      <c r="D21" s="74" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F21" s="25">
+        <f>E21*F18</f>
+        <v>513.59</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="74">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" s="9"/>
+      <c r="D22" s="74" t="s">
+        <v>6</v>
+      </c>
+      <c r="E22" s="8">
+        <v>1.8</v>
+      </c>
+      <c r="F22" s="25">
+        <f>E22*F18*68</f>
+        <v>57148.56</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="74">
+        <v>4.5</v>
+      </c>
+      <c r="B23" s="73" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" s="91"/>
+      <c r="D23" s="67" t="s">
+        <v>41</v>
+      </c>
+      <c r="E23" s="70">
+        <v>8</v>
+      </c>
+      <c r="F23" s="25">
+        <f>ROUNDDOWN(E23*F18,0)</f>
+        <v>3735</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A24" s="67">
+        <v>5</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D24" s="74" t="s">
+        <v>7</v>
+      </c>
+      <c r="E24" s="8">
+        <v>1</v>
+      </c>
+      <c r="F24" s="25">
+        <f>'1эт'!E15</f>
+        <v>19.420000000000002</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="74">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C25" s="9"/>
+      <c r="D25" s="74" t="s">
+        <v>41</v>
+      </c>
+      <c r="E25" s="8">
+        <v>8</v>
+      </c>
+      <c r="F25" s="25">
+        <f>ROUNDDOWN(E25*F24,0)</f>
+        <v>155</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="74">
+        <v>5.2</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" s="9"/>
+      <c r="D26" s="74" t="s">
+        <v>6</v>
+      </c>
+      <c r="E26" s="8">
+        <v>1.8</v>
+      </c>
+      <c r="F26" s="25">
+        <f>E26*F24*70</f>
+        <v>2446.92</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="74">
+        <v>5.3</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C27" s="9"/>
+      <c r="D27" s="74" t="s">
+        <v>7</v>
+      </c>
+      <c r="E27" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F27" s="25">
+        <f>E27*F24</f>
+        <v>21.362000000000002</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="74">
+        <v>5.4</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="9"/>
+      <c r="D28" s="74" t="s">
+        <v>5</v>
+      </c>
+      <c r="E28" s="8">
+        <v>1</v>
+      </c>
+      <c r="F28" s="25">
+        <f>E28*F24</f>
+        <v>19.420000000000002</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A29" s="67">
+        <v>6</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D29" s="74" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" s="8">
+        <v>1</v>
+      </c>
+      <c r="F29" s="25">
+        <f>'2эт'!E21+'3эт'!E13</f>
+        <v>100.99</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="74">
+        <v>6.1</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C30" s="9"/>
+      <c r="D30" s="74" t="s">
+        <v>5</v>
+      </c>
+      <c r="E30" s="8">
+        <v>1</v>
+      </c>
+      <c r="F30" s="25">
+        <f>F29*E30</f>
+        <v>100.99</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="74">
+        <v>6.2</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C31" s="9"/>
+      <c r="D31" s="74" t="s">
+        <v>7</v>
+      </c>
+      <c r="E31" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F31" s="25">
+        <f>E31*F29</f>
+        <v>111.089</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="74">
+        <v>6.3</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C32" s="9"/>
+      <c r="D32" s="74" t="s">
+        <v>6</v>
+      </c>
+      <c r="E32" s="8">
+        <v>1.8</v>
+      </c>
+      <c r="F32" s="25">
+        <f>E32*F29*80</f>
+        <v>14542.559999999998</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="74">
+        <v>6.4</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C33" s="9"/>
+      <c r="D33" s="74" t="s">
+        <v>41</v>
+      </c>
+      <c r="E33" s="8">
+        <v>8</v>
+      </c>
+      <c r="F33" s="25">
+        <f>ROUNDDOWN(E33*F29,0)</f>
+        <v>807</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E46"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="16384" width="9.140625" style="110"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="96" t="s">
+        <v>110</v>
+      </c>
+      <c r="B1" s="97"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="98"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="86" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="86" t="s">
+        <v>97</v>
+      </c>
+      <c r="C2" s="86" t="s">
+        <v>98</v>
+      </c>
+      <c r="D2" s="86" t="s">
+        <v>93</v>
+      </c>
+      <c r="E2" s="86" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="86">
+        <v>1</v>
+      </c>
+      <c r="B3" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C3" s="86">
+        <v>1.054</v>
+      </c>
+      <c r="D3" s="86">
+        <v>7.1</v>
+      </c>
+      <c r="E3" s="86">
+        <v>46.62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="96" t="s">
+        <v>110</v>
+      </c>
+      <c r="B5" s="97"/>
+      <c r="C5" s="97"/>
+      <c r="D5" s="97"/>
+      <c r="E5" s="98"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="86" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="86" t="s">
+        <v>97</v>
+      </c>
+      <c r="C6" s="86" t="s">
+        <v>98</v>
+      </c>
+      <c r="D6" s="86" t="s">
+        <v>93</v>
+      </c>
+      <c r="E6" s="86" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="86">
+        <v>1</v>
+      </c>
+      <c r="B7" s="86">
+        <v>1</v>
+      </c>
+      <c r="C7" s="86" t="s">
+        <v>113</v>
+      </c>
+      <c r="D7" s="86">
+        <v>9.1</v>
+      </c>
+      <c r="E7" s="109">
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="86">
+        <v>2</v>
+      </c>
+      <c r="B8" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C8" s="86" t="s">
+        <v>113</v>
+      </c>
+      <c r="D8" s="86">
+        <v>9.1</v>
+      </c>
+      <c r="E8" s="109">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D9" s="110" t="s">
+        <v>114</v>
+      </c>
+      <c r="E9" s="110">
+        <f>SUM(E7:E8)</f>
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="96" t="s">
+        <v>110</v>
+      </c>
+      <c r="B11" s="97"/>
+      <c r="C11" s="97"/>
+      <c r="D11" s="97"/>
+      <c r="E11" s="98"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" s="86" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="86" t="s">
+        <v>97</v>
+      </c>
+      <c r="C12" s="86" t="s">
+        <v>98</v>
+      </c>
+      <c r="D12" s="86" t="s">
+        <v>93</v>
+      </c>
+      <c r="E12" s="86" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="86">
+        <v>1</v>
+      </c>
+      <c r="B13" s="86">
+        <v>1</v>
+      </c>
+      <c r="C13" s="86" t="s">
+        <v>113</v>
+      </c>
+      <c r="D13" s="86">
+        <v>5</v>
+      </c>
+      <c r="E13" s="109">
+        <v>11.69</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" s="86">
+        <v>2</v>
+      </c>
+      <c r="B14" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C14" s="86" t="s">
+        <v>113</v>
+      </c>
+      <c r="D14" s="86">
+        <v>5</v>
+      </c>
+      <c r="E14" s="109">
+        <v>7.73</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D15" s="110" t="s">
+        <v>114</v>
+      </c>
+      <c r="E15" s="110">
+        <f>SUM(E13:E14)</f>
+        <v>19.420000000000002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" s="86" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" s="86"/>
+      <c r="C17" s="86"/>
+      <c r="D17" s="86"/>
+      <c r="E17" s="86"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" s="86" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="86" t="s">
+        <v>97</v>
+      </c>
+      <c r="C18" s="86" t="s">
+        <v>98</v>
+      </c>
+      <c r="D18" s="86" t="s">
+        <v>93</v>
+      </c>
+      <c r="E18" s="86" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" s="86">
+        <v>1</v>
+      </c>
+      <c r="B19" s="86">
+        <v>1</v>
+      </c>
+      <c r="C19" s="86">
+        <v>1.024</v>
+      </c>
+      <c r="D19" s="86">
+        <v>6</v>
+      </c>
+      <c r="E19" s="86">
+        <v>13.62</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" s="86">
+        <v>2</v>
+      </c>
+      <c r="B20" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C20" s="86">
+        <v>1.0449999999999999</v>
+      </c>
+      <c r="D20" s="86">
+        <v>6</v>
+      </c>
+      <c r="E20" s="86">
+        <v>161.78</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" s="86">
+        <v>3</v>
+      </c>
+      <c r="B21" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C21" s="86">
+        <v>1.046</v>
+      </c>
+      <c r="D21" s="86">
+        <v>6</v>
+      </c>
+      <c r="E21" s="86">
+        <v>161.15</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" s="86">
+        <v>4</v>
+      </c>
+      <c r="B22" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C22" s="86">
+        <v>1.0529999999999999</v>
+      </c>
+      <c r="D22" s="86">
+        <v>6</v>
+      </c>
+      <c r="E22" s="86">
+        <v>443.48</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" s="86">
+        <v>5</v>
+      </c>
+      <c r="B23" s="86">
+        <v>1</v>
+      </c>
+      <c r="C23" s="86">
+        <v>1.034</v>
+      </c>
+      <c r="D23" s="86">
+        <v>7</v>
+      </c>
+      <c r="E23" s="86">
+        <v>17.22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" s="86">
+        <v>6</v>
+      </c>
+      <c r="B24" s="86">
+        <v>1</v>
+      </c>
+      <c r="C24" s="86">
+        <v>1.0349999999999999</v>
+      </c>
+      <c r="D24" s="86">
+        <v>7</v>
+      </c>
+      <c r="E24" s="86">
+        <v>21.63</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25" s="86">
+        <v>7</v>
+      </c>
+      <c r="B25" s="86">
+        <v>1</v>
+      </c>
+      <c r="C25" s="86">
+        <v>1.036</v>
+      </c>
+      <c r="D25" s="86">
+        <v>7</v>
+      </c>
+      <c r="E25" s="86">
+        <v>5.76</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" s="86">
+        <v>8</v>
+      </c>
+      <c r="B26" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C26" s="86">
+        <v>1.054</v>
+      </c>
+      <c r="D26" s="86">
+        <v>7</v>
+      </c>
+      <c r="E26" s="86">
+        <v>14.54</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" s="86">
+        <v>9</v>
+      </c>
+      <c r="B27" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C27" s="86">
+        <v>1.054</v>
+      </c>
+      <c r="D27" s="86">
+        <v>7.1</v>
+      </c>
+      <c r="E27" s="86">
+        <v>46.62</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" s="86">
+        <v>10</v>
+      </c>
+      <c r="B28" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C28" s="86">
+        <v>1.048</v>
+      </c>
+      <c r="D28" s="86">
+        <v>8.1</v>
+      </c>
+      <c r="E28" s="86">
+        <v>23.92</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29" s="86">
+        <v>11</v>
+      </c>
+      <c r="B29" s="86">
+        <v>1</v>
+      </c>
+      <c r="C29" s="86">
+        <v>1.0369999999999999</v>
+      </c>
+      <c r="D29" s="86">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="E29" s="86">
+        <v>3.34</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30" s="86">
+        <v>12</v>
+      </c>
+      <c r="B30" s="86">
+        <v>1</v>
+      </c>
+      <c r="C30" s="86">
+        <v>1.038</v>
+      </c>
+      <c r="D30" s="86">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="E30" s="86">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31" s="86">
+        <v>13</v>
+      </c>
+      <c r="B31" s="86">
+        <v>1</v>
+      </c>
+      <c r="C31" s="86">
+        <v>1.026</v>
+      </c>
+      <c r="D31" s="86">
+        <v>9</v>
+      </c>
+      <c r="E31" s="86">
+        <v>191.68</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32" s="86">
+        <v>14</v>
+      </c>
+      <c r="B32" s="86">
+        <v>1</v>
+      </c>
+      <c r="C32" s="86">
+        <v>1.0269999999999999</v>
+      </c>
+      <c r="D32" s="86">
+        <v>9</v>
+      </c>
+      <c r="E32" s="86">
+        <v>114.04</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33" s="86">
+        <v>15</v>
+      </c>
+      <c r="B33" s="86">
+        <v>1</v>
+      </c>
+      <c r="C33" s="86">
+        <v>1.028</v>
+      </c>
+      <c r="D33" s="86">
+        <v>9</v>
+      </c>
+      <c r="E33" s="86">
+        <v>68.81</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34" s="86">
+        <v>16</v>
+      </c>
+      <c r="B34" s="86">
+        <v>1</v>
+      </c>
+      <c r="C34" s="86">
+        <v>1.0289999999999999</v>
+      </c>
+      <c r="D34" s="86">
+        <v>9</v>
+      </c>
+      <c r="E34" s="86">
+        <v>68.81</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A35" s="86">
+        <v>17</v>
+      </c>
+      <c r="B35" s="86">
+        <v>1</v>
+      </c>
+      <c r="C35" s="86">
+        <v>1.03</v>
+      </c>
+      <c r="D35" s="86">
+        <v>9</v>
+      </c>
+      <c r="E35" s="86">
+        <v>68.89</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A36" s="86">
+        <v>18</v>
+      </c>
+      <c r="B36" s="86">
+        <v>1</v>
+      </c>
+      <c r="C36" s="86">
+        <v>1.0309999999999999</v>
+      </c>
+      <c r="D36" s="86">
+        <v>9</v>
+      </c>
+      <c r="E36" s="86">
+        <v>68.89</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A37" s="86">
+        <v>19</v>
+      </c>
+      <c r="B37" s="86">
+        <v>1</v>
+      </c>
+      <c r="C37" s="86">
+        <v>1.032</v>
+      </c>
+      <c r="D37" s="86">
+        <v>9</v>
+      </c>
+      <c r="E37" s="86">
+        <v>68.069999999999993</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A38" s="86">
+        <v>20</v>
+      </c>
+      <c r="B38" s="86">
+        <v>1</v>
+      </c>
+      <c r="C38" s="86">
+        <v>1.0329999999999999</v>
+      </c>
+      <c r="D38" s="86">
+        <v>9</v>
+      </c>
+      <c r="E38" s="86">
+        <v>139.1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A39" s="86">
+        <v>21</v>
+      </c>
+      <c r="B39" s="86">
+        <v>1</v>
+      </c>
+      <c r="C39" s="86">
+        <v>1.0389999999999999</v>
+      </c>
+      <c r="D39" s="86">
+        <v>9</v>
+      </c>
+      <c r="E39" s="86">
+        <v>149.69999999999999</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A40" s="86">
+        <v>22</v>
+      </c>
+      <c r="B40" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C40" s="86">
+        <v>1.04</v>
+      </c>
+      <c r="D40" s="86">
+        <v>9</v>
+      </c>
+      <c r="E40" s="86">
+        <v>220.47</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A41" s="86">
+        <v>23</v>
+      </c>
+      <c r="B41" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C41" s="86">
+        <v>1.0429999999999999</v>
+      </c>
+      <c r="D41" s="86">
+        <v>9</v>
+      </c>
+      <c r="E41" s="86">
+        <v>61.99</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A42" s="86">
+        <v>24</v>
+      </c>
+      <c r="B42" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C42" s="86">
+        <v>1.044</v>
+      </c>
+      <c r="D42" s="86">
+        <v>9</v>
+      </c>
+      <c r="E42" s="86">
+        <v>14.14</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A43" s="86">
+        <v>25</v>
+      </c>
+      <c r="B43" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C43" s="86">
+        <v>1.0489999999999999</v>
+      </c>
+      <c r="D43" s="86">
+        <v>9</v>
+      </c>
+      <c r="E43" s="86">
+        <v>103.8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A44" s="86">
+        <v>26</v>
+      </c>
+      <c r="B44" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C44" s="86">
+        <v>1.05</v>
+      </c>
+      <c r="D44" s="86">
+        <v>9</v>
+      </c>
+      <c r="E44" s="86">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A45" s="86">
+        <v>27</v>
+      </c>
+      <c r="B45" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C45" s="86">
+        <v>1.0509999999999999</v>
+      </c>
+      <c r="D45" s="86">
+        <v>9</v>
+      </c>
+      <c r="E45" s="86">
+        <v>31.58</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A46" s="86"/>
+      <c r="B46" s="86"/>
+      <c r="C46" s="86"/>
+      <c r="D46" s="86" t="s">
+        <v>114</v>
+      </c>
+      <c r="E46" s="86">
+        <f>SUM(E19:E45)</f>
+        <v>2310.2799999999997</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A11:E11"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="16384" width="9.140625" style="110"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="96" t="s">
+        <v>111</v>
+      </c>
+      <c r="B1" s="97"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="98"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="86" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="86" t="s">
+        <v>97</v>
+      </c>
+      <c r="C2" s="86" t="s">
+        <v>98</v>
+      </c>
+      <c r="D2" s="86" t="s">
+        <v>93</v>
+      </c>
+      <c r="E2" s="86" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="86">
+        <v>1</v>
+      </c>
+      <c r="B3" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C3" s="86">
+        <v>1.054</v>
+      </c>
+      <c r="D3" s="86">
+        <v>7.1</v>
+      </c>
+      <c r="E3" s="86">
+        <v>46.62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="108" t="s">
+        <v>111</v>
+      </c>
+      <c r="B5" s="108"/>
+      <c r="C5" s="108"/>
+      <c r="D5" s="108"/>
+      <c r="E5" s="108"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="86" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="86" t="s">
+        <v>97</v>
+      </c>
+      <c r="C6" s="86" t="s">
+        <v>98</v>
+      </c>
+      <c r="D6" s="86" t="s">
+        <v>93</v>
+      </c>
+      <c r="E6" s="86" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="86">
+        <v>1</v>
+      </c>
+      <c r="B7" s="86">
+        <v>1</v>
+      </c>
+      <c r="C7" s="86">
+        <v>2.0169999999999999</v>
+      </c>
+      <c r="D7" s="86">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="E7" s="86">
+        <v>3.22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="86">
+        <v>2</v>
+      </c>
+      <c r="B8" s="86">
+        <v>1</v>
+      </c>
+      <c r="C8" s="86">
+        <v>2.1619999999999999</v>
+      </c>
+      <c r="D8" s="86">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="E8" s="86">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="86">
+        <v>3</v>
+      </c>
+      <c r="B9" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C9" s="86">
+        <v>2.097</v>
+      </c>
+      <c r="D9" s="86">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="E9" s="86">
+        <v>4.8499999999999996</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" s="86">
+        <v>4</v>
+      </c>
+      <c r="B10" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C10" s="86">
+        <v>2.0979999999999999</v>
+      </c>
+      <c r="D10" s="86">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="E10" s="86">
+        <v>4.76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="86">
+        <v>5</v>
+      </c>
+      <c r="B11" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C11" s="86">
+        <v>2.1019999999999999</v>
+      </c>
+      <c r="D11" s="86">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="E11" s="86">
+        <v>9.24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" s="86">
+        <v>6</v>
+      </c>
+      <c r="B12" s="86">
+        <v>1</v>
+      </c>
+      <c r="C12" s="86" t="s">
+        <v>113</v>
+      </c>
+      <c r="D12" s="86">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="E12" s="109">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="86">
+        <v>7</v>
+      </c>
+      <c r="B13" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C13" s="86" t="s">
+        <v>113</v>
+      </c>
+      <c r="D13" s="86">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="E13" s="109">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" s="86"/>
+      <c r="B14" s="86"/>
+      <c r="C14" s="86"/>
+      <c r="D14" s="86" t="s">
+        <v>114</v>
+      </c>
+      <c r="E14" s="86">
+        <f>SUM(E7:E13)</f>
+        <v>42.32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" s="108" t="s">
+        <v>111</v>
+      </c>
+      <c r="B16" s="108"/>
+      <c r="C16" s="108"/>
+      <c r="D16" s="108"/>
+      <c r="E16" s="108"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" s="86" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="86" t="s">
+        <v>97</v>
+      </c>
+      <c r="C17" s="86" t="s">
+        <v>98</v>
+      </c>
+      <c r="D17" s="86" t="s">
+        <v>93</v>
+      </c>
+      <c r="E17" s="86" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" s="86">
+        <v>1</v>
+      </c>
+      <c r="B18" s="86">
+        <v>1</v>
+      </c>
+      <c r="C18" s="86" t="s">
+        <v>113</v>
+      </c>
+      <c r="D18" s="86">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="E18" s="86">
+        <v>8.2799999999999994</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" s="86">
+        <v>2</v>
+      </c>
+      <c r="B19" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C19" s="86" t="s">
+        <v>113</v>
+      </c>
+      <c r="D19" s="86">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="E19" s="86">
+        <v>8.09</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" s="86">
+        <v>1</v>
+      </c>
+      <c r="B20" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C20" s="86">
+        <v>2.16</v>
+      </c>
+      <c r="D20" s="86">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="E20" s="86">
+        <v>72.64</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" s="86"/>
+      <c r="B21" s="86"/>
+      <c r="C21" s="86"/>
+      <c r="D21" s="86" t="s">
+        <v>114</v>
+      </c>
+      <c r="E21" s="86">
+        <f>SUM(E18:E20)</f>
+        <v>89.009999999999991</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" s="86"/>
+      <c r="B23" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C23" s="86">
+        <v>2.081</v>
+      </c>
+      <c r="D23" s="86">
+        <v>11</v>
+      </c>
+      <c r="E23" s="86">
+        <v>298.27999999999997</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" s="86"/>
+      <c r="B24" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C24" s="86">
+        <v>2.085</v>
+      </c>
+      <c r="D24" s="86">
+        <v>11.1</v>
+      </c>
+      <c r="E24" s="86">
+        <v>168.62</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D25" s="86" t="s">
+        <v>114</v>
+      </c>
+      <c r="E25" s="86">
+        <f>SUM(E23:E24)</f>
+        <v>466.9</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A16:E16"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="108" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1" s="108"/>
+      <c r="C1" s="108"/>
+      <c r="D1" s="108"/>
+      <c r="E1" s="108"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="86" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="86" t="s">
+        <v>97</v>
+      </c>
+      <c r="C2" s="86" t="s">
+        <v>98</v>
+      </c>
+      <c r="D2" s="86" t="s">
+        <v>93</v>
+      </c>
+      <c r="E2" s="86" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="86">
+        <v>1</v>
+      </c>
+      <c r="B3" s="86">
+        <v>1</v>
+      </c>
+      <c r="C3" s="86">
+        <v>3.0179999999999998</v>
+      </c>
+      <c r="D3" s="86">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="E3" s="86">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="86">
+        <v>2</v>
+      </c>
+      <c r="B4" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C4" s="86">
+        <v>3.0209999999999999</v>
+      </c>
+      <c r="D4" s="86">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="E4" s="86">
+        <v>15.62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="86">
+        <v>3</v>
+      </c>
+      <c r="B5" s="86">
+        <v>1</v>
+      </c>
+      <c r="C5" s="86">
+        <v>3.0920000000000001</v>
+      </c>
+      <c r="D5" s="86">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="E5" s="86">
+        <v>5.24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="86">
+        <v>4</v>
+      </c>
+      <c r="B6" s="86">
+        <v>1</v>
+      </c>
+      <c r="C6" s="86" t="s">
+        <v>113</v>
+      </c>
+      <c r="D6" s="86">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="E6" s="109">
+        <v>14.79</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="86"/>
+      <c r="B7" s="86"/>
+      <c r="C7" s="86"/>
+      <c r="D7" s="86" t="s">
+        <v>114</v>
+      </c>
+      <c r="E7" s="86">
+        <f>SUM(E3:E6)</f>
+        <v>38.85</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="108" t="s">
+        <v>109</v>
+      </c>
+      <c r="B9" s="108"/>
+      <c r="C9" s="108"/>
+      <c r="D9" s="108"/>
+      <c r="E9" s="108"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="86" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="86" t="s">
+        <v>97</v>
+      </c>
+      <c r="C10" s="86" t="s">
+        <v>98</v>
+      </c>
+      <c r="D10" s="86" t="s">
+        <v>93</v>
+      </c>
+      <c r="E10" s="86" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="86">
+        <v>1</v>
+      </c>
+      <c r="B11" s="86">
+        <v>1</v>
+      </c>
+      <c r="C11" s="86" t="s">
+        <v>113</v>
+      </c>
+      <c r="D11" s="86">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="E11" s="86">
+        <v>6.03</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="86">
+        <v>2</v>
+      </c>
+      <c r="B12" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C12" s="86" t="s">
+        <v>113</v>
+      </c>
+      <c r="D12" s="86">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="E12" s="86">
+        <v>5.95</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="86"/>
+      <c r="B13" s="86"/>
+      <c r="C13" s="86"/>
+      <c r="D13" s="86" t="s">
+        <v>114</v>
+      </c>
+      <c r="E13" s="86">
+        <f>SUM(E11:E12)</f>
+        <v>11.98</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A9:E9"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1225,7 +7379,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1238,15 +7392,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="92" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
+      <c r="B1" s="92"/>
+      <c r="C1" s="92"/>
+      <c r="D1" s="92"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="92"/>
+      <c r="G1" s="92"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="10"/>
@@ -2116,7 +8270,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2307,7 +8461,7 @@
       <c r="B8" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="56" t="s">
+      <c r="C8" s="55" t="s">
         <v>96</v>
       </c>
       <c r="D8" s="29" t="s">
@@ -2441,7 +8595,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2454,15 +8608,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="92" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="55"/>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
+      <c r="B1" s="92"/>
+      <c r="C1" s="92"/>
+      <c r="D1" s="92"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="92"/>
+      <c r="G1" s="92"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="10"/>
@@ -3072,7 +9226,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4183,11 +10337,885 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <sheetPr>
+    <tabColor theme="4" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="7.5703125" customWidth="1"/>
+    <col min="2" max="2" width="50.28515625" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" customWidth="1"/>
+    <col min="6" max="6" width="7.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="15"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="5"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A3" s="67">
+        <v>1</v>
+      </c>
+      <c r="B3" s="73" t="s">
+        <v>102</v>
+      </c>
+      <c r="C3" s="69" t="s">
+        <v>104</v>
+      </c>
+      <c r="D3" s="67" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="70">
+        <v>1</v>
+      </c>
+      <c r="F3" s="60">
+        <f>Из1эт!E29+Из2эт!E17</f>
+        <v>2427.35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="56">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="C4" s="9"/>
+      <c r="D4" s="56" t="s">
+        <v>105</v>
+      </c>
+      <c r="E4" s="8">
+        <v>1.03</v>
+      </c>
+      <c r="F4" s="25">
+        <f>E4*F3*50/1000</f>
+        <v>125.00852500000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor theme="4" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:E29"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="9.140625" style="63"/>
+    <col min="5" max="5" width="9.140625" style="61"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="93" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1" s="94"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="95"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="56" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="34" t="s">
+        <v>97</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D2" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="E2" s="59" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="56">
+        <v>1</v>
+      </c>
+      <c r="B3" s="64">
+        <v>1</v>
+      </c>
+      <c r="C3" s="64">
+        <v>1.024</v>
+      </c>
+      <c r="D3" s="64">
+        <v>6</v>
+      </c>
+      <c r="E3" s="60">
+        <v>13.62</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="57">
+        <v>2</v>
+      </c>
+      <c r="B4" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C4" s="64">
+        <v>1.0449999999999999</v>
+      </c>
+      <c r="D4" s="64">
+        <v>6</v>
+      </c>
+      <c r="E4" s="60">
+        <v>161.78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="57">
+        <v>3</v>
+      </c>
+      <c r="B5" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C5" s="64">
+        <v>1.046</v>
+      </c>
+      <c r="D5" s="64">
+        <v>6</v>
+      </c>
+      <c r="E5" s="60">
+        <v>161.15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="57">
+        <v>4</v>
+      </c>
+      <c r="B6" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C6" s="64">
+        <v>1.0529999999999999</v>
+      </c>
+      <c r="D6" s="64">
+        <v>6</v>
+      </c>
+      <c r="E6" s="60">
+        <v>443.48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="57">
+        <v>5</v>
+      </c>
+      <c r="B7" s="64">
+        <v>1</v>
+      </c>
+      <c r="C7" s="64">
+        <v>1.034</v>
+      </c>
+      <c r="D7" s="64">
+        <v>7</v>
+      </c>
+      <c r="E7" s="60">
+        <v>17.22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="57">
+        <v>6</v>
+      </c>
+      <c r="B8" s="64">
+        <v>1</v>
+      </c>
+      <c r="C8" s="64">
+        <v>1.0349999999999999</v>
+      </c>
+      <c r="D8" s="64">
+        <v>7</v>
+      </c>
+      <c r="E8" s="60">
+        <v>21.63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="57">
+        <v>7</v>
+      </c>
+      <c r="B9" s="64">
+        <v>1</v>
+      </c>
+      <c r="C9" s="64">
+        <v>1.036</v>
+      </c>
+      <c r="D9" s="64">
+        <v>7</v>
+      </c>
+      <c r="E9" s="60">
+        <v>5.76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="57">
+        <v>8</v>
+      </c>
+      <c r="B10" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C10" s="64">
+        <v>1.054</v>
+      </c>
+      <c r="D10" s="64">
+        <v>7</v>
+      </c>
+      <c r="E10" s="60">
+        <v>14.54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="57">
+        <v>9</v>
+      </c>
+      <c r="B11" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C11" s="64">
+        <v>1.048</v>
+      </c>
+      <c r="D11" s="64">
+        <v>8.1</v>
+      </c>
+      <c r="E11" s="60">
+        <v>23.92</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="57">
+        <v>10</v>
+      </c>
+      <c r="B12" s="64">
+        <v>1</v>
+      </c>
+      <c r="C12" s="64">
+        <v>1.0369999999999999</v>
+      </c>
+      <c r="D12" s="64">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="E12" s="60">
+        <v>3.34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="57">
+        <v>11</v>
+      </c>
+      <c r="B13" s="64">
+        <v>1</v>
+      </c>
+      <c r="C13" s="64">
+        <v>1.038</v>
+      </c>
+      <c r="D13" s="64">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="E13" s="60">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="57">
+        <v>12</v>
+      </c>
+      <c r="B14" s="64">
+        <v>1</v>
+      </c>
+      <c r="C14" s="8">
+        <v>1.026</v>
+      </c>
+      <c r="D14" s="64">
+        <v>9</v>
+      </c>
+      <c r="E14" s="60">
+        <v>191.68</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="57">
+        <v>13</v>
+      </c>
+      <c r="B15" s="64">
+        <v>1</v>
+      </c>
+      <c r="C15" s="54">
+        <v>1.0269999999999999</v>
+      </c>
+      <c r="D15" s="64">
+        <v>9</v>
+      </c>
+      <c r="E15" s="60">
+        <v>114.04</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="57">
+        <v>14</v>
+      </c>
+      <c r="B16" s="64">
+        <v>1</v>
+      </c>
+      <c r="C16" s="54">
+        <v>1.028</v>
+      </c>
+      <c r="D16" s="64">
+        <v>9</v>
+      </c>
+      <c r="E16" s="60">
+        <v>68.81</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="57">
+        <v>15</v>
+      </c>
+      <c r="B17" s="64">
+        <v>1</v>
+      </c>
+      <c r="C17" s="54">
+        <v>1.0289999999999999</v>
+      </c>
+      <c r="D17" s="64">
+        <v>9</v>
+      </c>
+      <c r="E17" s="60">
+        <v>68.81</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="57">
+        <v>16</v>
+      </c>
+      <c r="B18" s="64">
+        <v>1</v>
+      </c>
+      <c r="C18" s="54">
+        <v>1.03</v>
+      </c>
+      <c r="D18" s="64">
+        <v>9</v>
+      </c>
+      <c r="E18" s="60">
+        <v>68.89</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="57">
+        <v>17</v>
+      </c>
+      <c r="B19" s="64">
+        <v>1</v>
+      </c>
+      <c r="C19" s="54">
+        <v>1.0309999999999999</v>
+      </c>
+      <c r="D19" s="64">
+        <v>9</v>
+      </c>
+      <c r="E19" s="60">
+        <v>68.89</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="57">
+        <v>18</v>
+      </c>
+      <c r="B20" s="64">
+        <v>1</v>
+      </c>
+      <c r="C20" s="54">
+        <v>1.032</v>
+      </c>
+      <c r="D20" s="64">
+        <v>9</v>
+      </c>
+      <c r="E20" s="60">
+        <v>68.069999999999993</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="57">
+        <v>19</v>
+      </c>
+      <c r="B21" s="64">
+        <v>1</v>
+      </c>
+      <c r="C21" s="54">
+        <v>1.0329999999999999</v>
+      </c>
+      <c r="D21" s="64">
+        <v>9</v>
+      </c>
+      <c r="E21" s="60">
+        <v>139.1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="57">
+        <v>20</v>
+      </c>
+      <c r="B22" s="64">
+        <v>1</v>
+      </c>
+      <c r="C22" s="54">
+        <v>1.0389999999999999</v>
+      </c>
+      <c r="D22" s="64">
+        <v>9</v>
+      </c>
+      <c r="E22" s="60">
+        <v>149.69999999999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="57">
+        <v>21</v>
+      </c>
+      <c r="B23" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C23" s="54">
+        <v>1.04</v>
+      </c>
+      <c r="D23" s="64">
+        <v>9</v>
+      </c>
+      <c r="E23" s="60">
+        <v>220.47</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="57">
+        <v>22</v>
+      </c>
+      <c r="B24" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C24" s="54">
+        <v>1.0429999999999999</v>
+      </c>
+      <c r="D24" s="64">
+        <v>9</v>
+      </c>
+      <c r="E24" s="60">
+        <v>61.99</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="57">
+        <v>23</v>
+      </c>
+      <c r="B25" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C25" s="54">
+        <v>1.044</v>
+      </c>
+      <c r="D25" s="64">
+        <v>9</v>
+      </c>
+      <c r="E25" s="60">
+        <v>14.14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="57">
+        <v>24</v>
+      </c>
+      <c r="B26" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C26" s="54">
+        <v>1.0489999999999999</v>
+      </c>
+      <c r="D26" s="64">
+        <v>9</v>
+      </c>
+      <c r="E26" s="60">
+        <v>103.8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="57">
+        <v>25</v>
+      </c>
+      <c r="B27" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C27" s="54">
+        <v>1.05</v>
+      </c>
+      <c r="D27" s="64">
+        <v>9</v>
+      </c>
+      <c r="E27" s="60">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="57">
+        <v>26</v>
+      </c>
+      <c r="B28" s="64">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C28" s="54">
+        <v>1.0509999999999999</v>
+      </c>
+      <c r="D28" s="64">
+        <v>9</v>
+      </c>
+      <c r="E28" s="60">
+        <v>31.58</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="56"/>
+      <c r="B29" s="34"/>
+      <c r="C29" s="54"/>
+      <c r="D29" s="34" t="s">
+        <v>106</v>
+      </c>
+      <c r="E29" s="60">
+        <f>SUM(E3:E28)</f>
+        <v>2263.66</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor theme="4" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="93" t="s">
+        <v>107</v>
+      </c>
+      <c r="B1" s="94"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="95"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="56" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="34" t="s">
+        <v>97</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D2" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="E2" s="59" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="56">
+        <v>1</v>
+      </c>
+      <c r="B3" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="C3" s="64">
+        <v>2.0139999999999998</v>
+      </c>
+      <c r="D3" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="E3" s="60">
+        <v>17.22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="56">
+        <v>2</v>
+      </c>
+      <c r="B4" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="C4" s="64">
+        <v>2.0150000000000001</v>
+      </c>
+      <c r="D4" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="E4" s="60">
+        <v>21.87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="56">
+        <v>3</v>
+      </c>
+      <c r="B5" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5" s="64">
+        <v>2.016</v>
+      </c>
+      <c r="D5" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="E5" s="60">
+        <v>5.0599999999999996</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="56">
+        <v>4</v>
+      </c>
+      <c r="B6" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="C6" s="54">
+        <v>2.089</v>
+      </c>
+      <c r="D6" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="E6" s="60">
+        <v>6.05</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="56">
+        <v>5</v>
+      </c>
+      <c r="B7" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" s="54">
+        <v>2.09</v>
+      </c>
+      <c r="D7" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="E7" s="60">
+        <v>12.15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="56">
+        <v>6</v>
+      </c>
+      <c r="B8" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="C8" s="54">
+        <v>2.0910000000000002</v>
+      </c>
+      <c r="D8" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="E8" s="60">
+        <v>10.63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="56">
+        <v>7</v>
+      </c>
+      <c r="B9" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="C9" s="54">
+        <v>2.0950000000000002</v>
+      </c>
+      <c r="D9" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="E9" s="60">
+        <v>8.7899999999999991</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="56">
+        <v>8</v>
+      </c>
+      <c r="B10" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10" s="54">
+        <v>2.0960000000000001</v>
+      </c>
+      <c r="D10" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="E10" s="60">
+        <v>14.39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="56">
+        <v>9</v>
+      </c>
+      <c r="B11" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="C11" s="54">
+        <v>2.1</v>
+      </c>
+      <c r="D11" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="E11" s="60">
+        <v>8.19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="56">
+        <v>10</v>
+      </c>
+      <c r="B12" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="C12" s="54">
+        <v>2.101</v>
+      </c>
+      <c r="D12" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="E12" s="60">
+        <v>12.22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="56">
+        <v>11</v>
+      </c>
+      <c r="B13" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="C13" s="54">
+        <v>2.1040000000000001</v>
+      </c>
+      <c r="D13" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="E13" s="60">
+        <v>8.4499999999999993</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="56">
+        <v>12</v>
+      </c>
+      <c r="B14" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="C14" s="54">
+        <v>2.105</v>
+      </c>
+      <c r="D14" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="E14" s="60">
+        <v>14.25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="56">
+        <v>13</v>
+      </c>
+      <c r="B15" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="C15" s="54">
+        <v>2.1070000000000002</v>
+      </c>
+      <c r="D15" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="E15" s="71">
+        <v>8.14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="56">
+        <v>14</v>
+      </c>
+      <c r="B16" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="C16" s="54">
+        <v>2.1080000000000001</v>
+      </c>
+      <c r="D16" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="E16" s="71">
+        <v>16.28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="56"/>
+      <c r="B17" s="34"/>
+      <c r="C17" s="54"/>
+      <c r="D17" s="34" t="s">
+        <v>52</v>
+      </c>
+      <c r="E17" s="72">
+        <f>SUM(E3:E16)</f>
+        <v>163.69000000000003</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/school_lublino/vor_lublino_floors.xlsx
+++ b/school_lublino/vor_lublino_floors.xlsx
@@ -9,30 +9,31 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14190" windowHeight="6840" firstSheet="13" activeTab="14"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14190" windowHeight="6840" firstSheet="10" activeTab="15"/>
   </bookViews>
   <sheets>
     <sheet name="АА" sheetId="16" state="hidden" r:id="rId1"/>
     <sheet name="ВОР 2 эт" sheetId="2" r:id="rId2"/>
-    <sheet name="Спец 2 эт" sheetId="4" state="hidden" r:id="rId3"/>
+    <sheet name="Спец 2 эт" sheetId="4" r:id="rId3"/>
     <sheet name="ВОР 3 эт" sheetId="3" r:id="rId4"/>
-    <sheet name="Спец 3 эт" sheetId="6" state="hidden" r:id="rId5"/>
+    <sheet name="Спец 3 эт" sheetId="6" r:id="rId5"/>
     <sheet name="общий (2)" sheetId="5" state="hidden" r:id="rId6"/>
-    <sheet name="ВорИзол" sheetId="10" r:id="rId7"/>
-    <sheet name="Из1эт" sheetId="8" state="hidden" r:id="rId8"/>
-    <sheet name="Из2эт" sheetId="9" state="hidden" r:id="rId9"/>
-    <sheet name="ВорПленка" sheetId="12" r:id="rId10"/>
-    <sheet name="Плк1э" sheetId="13" state="hidden" r:id="rId11"/>
-    <sheet name="Плк2э" sheetId="14" state="hidden" r:id="rId12"/>
-    <sheet name="Плк3э" sheetId="15" state="hidden" r:id="rId13"/>
-    <sheet name="Общ" sheetId="7" r:id="rId14"/>
-    <sheet name="СКБ-1эт" sheetId="17" r:id="rId15"/>
-    <sheet name="1эт" sheetId="18" r:id="rId16"/>
-    <sheet name="2эт" sheetId="19" r:id="rId17"/>
-    <sheet name="3эт" sheetId="20" r:id="rId18"/>
+    <sheet name="не сделали" sheetId="21" r:id="rId7"/>
+    <sheet name="ВорИзол" sheetId="10" r:id="rId8"/>
+    <sheet name="Из1эт" sheetId="8" state="hidden" r:id="rId9"/>
+    <sheet name="Из2эт" sheetId="9" state="hidden" r:id="rId10"/>
+    <sheet name="ВорПленка" sheetId="12" r:id="rId11"/>
+    <sheet name="Плк1э" sheetId="13" state="hidden" r:id="rId12"/>
+    <sheet name="Плк2э" sheetId="14" state="hidden" r:id="rId13"/>
+    <sheet name="Плк3э" sheetId="15" state="hidden" r:id="rId14"/>
+    <sheet name="Общ" sheetId="7" r:id="rId15"/>
+    <sheet name="СКБ-1эт" sheetId="17" r:id="rId16"/>
+    <sheet name="1эт" sheetId="18" r:id="rId17"/>
+    <sheet name="2эт" sheetId="19" r:id="rId18"/>
+    <sheet name="3эт" sheetId="20" r:id="rId19"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Спец 3 эт'!$B$2:$K$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Спец 3 эт'!$B$2:$K$23</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="120">
   <si>
     <t>№ п.п.</t>
   </si>
@@ -395,6 +396,22 @@
   </si>
   <si>
     <t>сумма</t>
+  </si>
+  <si>
+    <t>Типы 4.4, 6, 6.1, 7, 7.1, 8.1, 8.2, 9</t>
+  </si>
+  <si>
+    <t>Типы 9.3
+60мм</t>
+  </si>
+  <si>
+    <t>1эт</t>
+  </si>
+  <si>
+    <t>2эт</t>
+  </si>
+  <si>
+    <t>3 эт</t>
   </si>
 </sst>
 </file>
@@ -443,7 +460,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -483,6 +500,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFCCFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEDAFB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF880AE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -632,7 +661,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="116">
+  <cellXfs count="130">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -881,27 +910,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -930,9 +938,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -950,6 +955,70 @@
     </xf>
     <xf numFmtId="2" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1632,6 +1701,11 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFF880AE"/>
+      <color rgb="FF9D1365"/>
+      <color rgb="FFFEDAFB"/>
+      <color rgb="FFFEC6FA"/>
+      <color rgb="FFFF99FF"/>
       <color rgb="FFFFCCFF"/>
     </mruColors>
   </colors>
@@ -1997,6 +2071,298 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
+    <tabColor theme="4" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="123" t="s">
+        <v>107</v>
+      </c>
+      <c r="B1" s="124"/>
+      <c r="C1" s="124"/>
+      <c r="D1" s="124"/>
+      <c r="E1" s="125"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="56" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="34" t="s">
+        <v>97</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D2" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="E2" s="59" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="56">
+        <v>1</v>
+      </c>
+      <c r="B3" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="C3" s="64">
+        <v>2.0139999999999998</v>
+      </c>
+      <c r="D3" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="E3" s="60">
+        <v>17.22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="56">
+        <v>2</v>
+      </c>
+      <c r="B4" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="C4" s="64">
+        <v>2.0150000000000001</v>
+      </c>
+      <c r="D4" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="E4" s="60">
+        <v>21.87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="56">
+        <v>3</v>
+      </c>
+      <c r="B5" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5" s="64">
+        <v>2.016</v>
+      </c>
+      <c r="D5" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="E5" s="60">
+        <v>5.0599999999999996</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="56">
+        <v>4</v>
+      </c>
+      <c r="B6" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="C6" s="54">
+        <v>2.089</v>
+      </c>
+      <c r="D6" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="E6" s="60">
+        <v>6.05</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="56">
+        <v>5</v>
+      </c>
+      <c r="B7" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" s="54">
+        <v>2.09</v>
+      </c>
+      <c r="D7" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="E7" s="60">
+        <v>12.15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="56">
+        <v>6</v>
+      </c>
+      <c r="B8" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="C8" s="54">
+        <v>2.0910000000000002</v>
+      </c>
+      <c r="D8" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="E8" s="60">
+        <v>10.63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="56">
+        <v>7</v>
+      </c>
+      <c r="B9" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="C9" s="54">
+        <v>2.0950000000000002</v>
+      </c>
+      <c r="D9" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="E9" s="60">
+        <v>8.7899999999999991</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="56">
+        <v>8</v>
+      </c>
+      <c r="B10" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10" s="54">
+        <v>2.0960000000000001</v>
+      </c>
+      <c r="D10" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="E10" s="60">
+        <v>14.39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="56">
+        <v>9</v>
+      </c>
+      <c r="B11" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="C11" s="54">
+        <v>2.1</v>
+      </c>
+      <c r="D11" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="E11" s="60">
+        <v>8.19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="56">
+        <v>10</v>
+      </c>
+      <c r="B12" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="C12" s="54">
+        <v>2.101</v>
+      </c>
+      <c r="D12" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="E12" s="60">
+        <v>12.22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="56">
+        <v>11</v>
+      </c>
+      <c r="B13" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="C13" s="54">
+        <v>2.1040000000000001</v>
+      </c>
+      <c r="D13" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="E13" s="60">
+        <v>8.4499999999999993</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="56">
+        <v>12</v>
+      </c>
+      <c r="B14" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="C14" s="54">
+        <v>2.105</v>
+      </c>
+      <c r="D14" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="E14" s="60">
+        <v>14.25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="56">
+        <v>13</v>
+      </c>
+      <c r="B15" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="C15" s="54">
+        <v>2.1070000000000002</v>
+      </c>
+      <c r="D15" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="E15" s="71">
+        <v>8.14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="56">
+        <v>14</v>
+      </c>
+      <c r="B16" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="C16" s="54">
+        <v>2.1080000000000001</v>
+      </c>
+      <c r="D16" s="34" t="s">
+        <v>101</v>
+      </c>
+      <c r="E16" s="71">
+        <v>16.28</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="56"/>
+      <c r="B17" s="34"/>
+      <c r="C17" s="54"/>
+      <c r="D17" s="34" t="s">
+        <v>52</v>
+      </c>
+      <c r="E17" s="72">
+        <f>SUM(E3:E16)</f>
+        <v>163.69000000000003</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
     <tabColor theme="5" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:F4"/>
@@ -2040,7 +2406,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="39" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A3" s="67">
         <v>1</v>
       </c>
@@ -2048,7 +2414,7 @@
         <v>14</v>
       </c>
       <c r="C3" s="69" t="s">
-        <v>47</v>
+        <v>115</v>
       </c>
       <c r="D3" s="67" t="s">
         <v>7</v>
@@ -2085,7 +2451,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="5" tint="0.79998168889431442"/>
@@ -2099,13 +2465,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="126" t="s">
         <v>110</v>
       </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="98"/>
+      <c r="B1" s="127"/>
+      <c r="C1" s="127"/>
+      <c r="D1" s="127"/>
+      <c r="E1" s="128"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="86" t="s">
@@ -2603,7 +2969,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="5" tint="0.79998168889431442"/>
@@ -2618,13 +2984,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="126" t="s">
         <v>111</v>
       </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="98"/>
+      <c r="B1" s="127"/>
+      <c r="C1" s="127"/>
+      <c r="D1" s="127"/>
+      <c r="E1" s="128"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="86" t="s">
@@ -3003,7 +3369,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="5" tint="0.79998168889431442"/>
@@ -3016,13 +3382,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="93" t="s">
+      <c r="A1" s="123" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="95"/>
+      <c r="B1" s="124"/>
+      <c r="C1" s="124"/>
+      <c r="D1" s="124"/>
+      <c r="E1" s="125"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="77" t="s">
@@ -3146,12 +3512,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
-  <dimension ref="A1:I106"/>
+  <dimension ref="A1:I122"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="9.140625" style="63"/>
@@ -3159,13 +3525,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="93" t="s">
+      <c r="A1" s="123" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="95"/>
+      <c r="B1" s="124"/>
+      <c r="C1" s="124"/>
+      <c r="D1" s="124"/>
+      <c r="E1" s="125"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="77" t="s">
@@ -5144,6 +5510,136 @@
       <c r="C106" s="54"/>
       <c r="D106" s="34"/>
       <c r="E106" s="66"/>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C111"/>
+      <c r="E111"/>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C112"/>
+      <c r="E112"/>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B113" t="s">
+        <v>117</v>
+      </c>
+      <c r="C113"/>
+      <c r="E113" t="s">
+        <v>118</v>
+      </c>
+      <c r="H113" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>6</v>
+      </c>
+      <c r="B114">
+        <v>13.62</v>
+      </c>
+      <c r="C114">
+        <v>758.84</v>
+      </c>
+      <c r="E114"/>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>6.1</v>
+      </c>
+      <c r="C115"/>
+      <c r="E115">
+        <v>13.62</v>
+      </c>
+      <c r="F115">
+        <v>76.59</v>
+      </c>
+      <c r="H115">
+        <v>13.62</v>
+      </c>
+      <c r="I115">
+        <v>15.08</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>7</v>
+      </c>
+      <c r="B116">
+        <v>43.85</v>
+      </c>
+      <c r="C116">
+        <v>14.52</v>
+      </c>
+      <c r="E116"/>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>7.2</v>
+      </c>
+      <c r="C117"/>
+      <c r="E117">
+        <v>43.43</v>
+      </c>
+      <c r="F117">
+        <v>119.37</v>
+      </c>
+      <c r="H117">
+        <v>43.43</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>8.1</v>
+      </c>
+      <c r="C118">
+        <v>23.92</v>
+      </c>
+      <c r="E118"/>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="B119">
+        <v>8.5500000000000007</v>
+      </c>
+      <c r="C119"/>
+      <c r="E119"/>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>9</v>
+      </c>
+      <c r="B120">
+        <v>935.07</v>
+      </c>
+      <c r="C120">
+        <v>453.24</v>
+      </c>
+      <c r="E120"/>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="C121"/>
+      <c r="E121">
+        <v>929.87</v>
+      </c>
+      <c r="F121">
+        <v>377.24</v>
+      </c>
+      <c r="H121">
+        <v>1135.8499999999999</v>
+      </c>
+      <c r="I121">
+        <v>534.9</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C122"/>
+      <c r="E122"/>
     </row>
   </sheetData>
   <sortState ref="C58:C81">
@@ -5162,9 +5658,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F33"/>
+  <sheetPr>
+    <tabColor theme="0" tint="-0.14999847407452621"/>
+  </sheetPr>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.5703125" customWidth="1"/>
@@ -5206,23 +5705,24 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="99">
-        <v>1</v>
-      </c>
-      <c r="B3" s="100" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="101" t="s">
-        <v>40</v>
-      </c>
-      <c r="D3" s="99" t="s">
+      <c r="A3" s="97">
+        <v>1</v>
+      </c>
+      <c r="B3" s="98" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="99" t="s">
+        <v>116</v>
+      </c>
+      <c r="D3" s="97" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="102">
-        <v>1</v>
-      </c>
-      <c r="F3" s="103">
-        <v>46.62</v>
+      <c r="E3" s="100">
+        <v>1</v>
+      </c>
+      <c r="F3" s="50">
+        <f>'1эт'!E5+'2эт'!E5+'3эт'!E4</f>
+        <v>69.010000000000005</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -5240,7 +5740,8 @@
         <v>8</v>
       </c>
       <c r="F4" s="25">
-        <v>372</v>
+        <f>ROUNDDOWN(E4*F3,0)</f>
+        <v>552</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -5258,11 +5759,12 @@
         <v>1.8</v>
       </c>
       <c r="F5" s="25">
-        <v>3356.64</v>
+        <f>E5*F3*60</f>
+        <v>7453.0800000000008</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="74">
+      <c r="A6" s="108">
         <v>1.3</v>
       </c>
       <c r="B6" s="9" t="s">
@@ -5276,11 +5778,12 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="F6" s="25">
-        <v>51.281999999999996</v>
+        <f>E6*F3</f>
+        <v>75.911000000000016</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="74">
+      <c r="A7" s="108">
         <v>1.4</v>
       </c>
       <c r="B7" s="9" t="s">
@@ -5294,28 +5797,29 @@
         <v>1</v>
       </c>
       <c r="F7" s="25">
-        <v>46.62</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="104">
+        <f>E7*F3</f>
+        <v>69.010000000000005</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A8" s="103">
         <v>2</v>
       </c>
-      <c r="B8" s="105" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="106" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" s="104" t="s">
+      <c r="B8" s="104" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="105" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="103" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="107">
-        <v>1</v>
-      </c>
-      <c r="F8" s="50">
-        <f>'1эт'!E9+'2эт'!E14+'3эт'!E7</f>
-        <v>122.87</v>
+      <c r="E8" s="106">
+        <v>1</v>
+      </c>
+      <c r="F8" s="107">
+        <f>'1эт'!E41</f>
+        <v>2263.66</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -5334,7 +5838,7 @@
       </c>
       <c r="F9" s="25">
         <f>ROUNDDOWN(E9*F8,0)</f>
-        <v>982</v>
+        <v>18109</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -5352,12 +5856,12 @@
         <v>1.8</v>
       </c>
       <c r="F10" s="25">
-        <f>E10*F8*60</f>
-        <v>13269.960000000001</v>
+        <f>E10*F8*65</f>
+        <v>264848.21999999997</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="74">
+      <c r="A11" s="108">
         <v>2.2999999999999998</v>
       </c>
       <c r="B11" s="9" t="s">
@@ -5372,11 +5876,11 @@
       </c>
       <c r="F11" s="25">
         <f>E11*F8</f>
-        <v>135.15700000000001</v>
+        <v>2490.0259999999998</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="74">
+      <c r="A12" s="108">
         <v>2.4</v>
       </c>
       <c r="B12" s="9" t="s">
@@ -5391,28 +5895,28 @@
       </c>
       <c r="F12" s="25">
         <f>E12*F8</f>
-        <v>122.87</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A13" s="111">
+        <v>2263.66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="109">
         <v>3</v>
       </c>
-      <c r="B13" s="112" t="s">
+      <c r="B13" s="110" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="113" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" s="111" t="s">
+      <c r="C13" s="111" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="109" t="s">
         <v>7</v>
       </c>
-      <c r="E13" s="114">
-        <v>1</v>
-      </c>
-      <c r="F13" s="115">
-        <f>'1эт'!E46</f>
-        <v>2310.2799999999997</v>
+      <c r="E13" s="112">
+        <v>1</v>
+      </c>
+      <c r="F13" s="44">
+        <f>'2эт'!E16</f>
+        <v>168.62</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -5420,18 +5924,18 @@
         <v>3.1</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="74" t="s">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="E14" s="8">
-        <v>8</v>
+        <v>0.255</v>
       </c>
       <c r="F14" s="25">
-        <f>ROUNDDOWN(E14*F13,0)</f>
-        <v>18482</v>
+        <f>E14*F13</f>
+        <v>42.998100000000001</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -5439,22 +5943,22 @@
         <v>3.2</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="74" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E15" s="8">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="F15" s="25">
-        <f>E15*F13*65</f>
-        <v>270302.76</v>
+        <f>E15*F13</f>
+        <v>168.62</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="74">
+      <c r="A16" s="108">
         <v>3.3</v>
       </c>
       <c r="B16" s="9" t="s">
@@ -5469,163 +5973,163 @@
       </c>
       <c r="F16" s="25">
         <f>E16*F13</f>
-        <v>2541.308</v>
+        <v>185.48200000000003</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="74">
+      <c r="A17" s="108">
         <v>3.4</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="74" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E17" s="8">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="F17" s="25">
-        <f>E17*F13</f>
-        <v>2310.2799999999997</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A18" s="67">
+        <f>E17*F13*68</f>
+        <v>20639.088</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="108">
+        <v>3.5</v>
+      </c>
+      <c r="B18" s="73" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="91"/>
+      <c r="D18" s="67" t="s">
+        <v>41</v>
+      </c>
+      <c r="E18" s="70">
+        <v>8</v>
+      </c>
+      <c r="F18" s="25">
+        <f>ROUNDDOWN(E18*F13,0)</f>
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A19" s="117">
         <v>4</v>
       </c>
-      <c r="B18" s="73" t="s">
+      <c r="B19" s="118" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="91" t="s">
-        <v>44</v>
-      </c>
-      <c r="D18" s="67" t="s">
+      <c r="C19" s="118" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" s="117" t="s">
         <v>7</v>
       </c>
-      <c r="E18" s="70">
-        <v>1</v>
-      </c>
-      <c r="F18" s="60">
-        <f>'2эт'!E25</f>
-        <v>466.9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="74">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="B19" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="9"/>
-      <c r="D19" s="74" t="s">
-        <v>6</v>
-      </c>
-      <c r="E19" s="8">
-        <v>0.255</v>
-      </c>
-      <c r="F19" s="25">
-        <f>E19*F18</f>
-        <v>119.0595</v>
+      <c r="E19" s="119">
+        <v>1</v>
+      </c>
+      <c r="F19" s="120">
+        <f>'1эт'!E11</f>
+        <v>19.420000000000002</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="74">
-        <v>4.2</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="74" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="E20" s="8">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F20" s="25">
-        <f>E20*F18</f>
-        <v>466.9</v>
+        <f>ROUNDDOWN(E20*F19,0)</f>
+        <v>155</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="74">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="74" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E21" s="8">
-        <v>1.1000000000000001</v>
+        <v>1.8</v>
       </c>
       <c r="F21" s="25">
-        <f>E21*F18</f>
-        <v>513.59</v>
+        <f>E21*F19*70</f>
+        <v>2446.92</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="74">
-        <v>4.4000000000000004</v>
+      <c r="A22" s="108">
+        <v>4.3</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="74" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E22" s="8">
-        <v>1.8</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="F22" s="25">
-        <f>E22*F18*68</f>
-        <v>57148.56</v>
+        <f>E22*F19</f>
+        <v>21.362000000000002</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="74">
-        <v>4.5</v>
-      </c>
-      <c r="B23" s="73" t="s">
-        <v>22</v>
-      </c>
-      <c r="C23" s="91"/>
-      <c r="D23" s="67" t="s">
-        <v>41</v>
-      </c>
-      <c r="E23" s="70">
-        <v>8</v>
+      <c r="A23" s="108">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" s="9"/>
+      <c r="D23" s="74" t="s">
+        <v>5</v>
+      </c>
+      <c r="E23" s="8">
+        <v>1</v>
       </c>
       <c r="F23" s="25">
-        <f>ROUNDDOWN(E23*F18,0)</f>
-        <v>3735</v>
+        <f>E23*F19</f>
+        <v>19.420000000000002</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A24" s="67">
+      <c r="A24" s="113">
         <v>5</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="114" t="s">
         <v>26</v>
       </c>
-      <c r="C24" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D24" s="74" t="s">
+      <c r="C24" s="114" t="s">
+        <v>46</v>
+      </c>
+      <c r="D24" s="113" t="s">
         <v>7</v>
       </c>
-      <c r="E24" s="8">
-        <v>1</v>
-      </c>
-      <c r="F24" s="25">
-        <f>'1эт'!E15</f>
-        <v>19.420000000000002</v>
+      <c r="E24" s="115">
+        <v>1</v>
+      </c>
+      <c r="F24" s="116">
+        <f>'2эт'!E12+'3эт'!E10</f>
+        <v>100.99</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -5633,18 +6137,18 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="74" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="E25" s="8">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F25" s="25">
-        <f>ROUNDDOWN(E25*F24,0)</f>
-        <v>155</v>
+        <f>F24*E25</f>
+        <v>100.99</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -5652,872 +6156,82 @@
         <v>5.2</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="74" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E26" s="8">
-        <v>1.8</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="F26" s="25">
-        <f>E26*F24*70</f>
-        <v>2446.92</v>
+        <f>E26*F24</f>
+        <v>111.089</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="74">
+      <c r="A27" s="108">
         <v>5.3</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="74" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E27" s="8">
-        <v>1.1000000000000001</v>
+        <v>1.8</v>
       </c>
       <c r="F27" s="25">
-        <f>E27*F24</f>
-        <v>21.362000000000002</v>
+        <f>E27*F24*80</f>
+        <v>14542.559999999998</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="74">
+      <c r="A28" s="108">
         <v>5.4</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="74" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="E28" s="8">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F28" s="25">
-        <f>E28*F24</f>
-        <v>19.420000000000002</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A29" s="67">
-        <v>6</v>
-      </c>
-      <c r="B29" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="D29" s="74" t="s">
-        <v>7</v>
-      </c>
-      <c r="E29" s="8">
-        <v>1</v>
-      </c>
-      <c r="F29" s="25">
-        <f>'2эт'!E21+'3эт'!E13</f>
-        <v>100.99</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="74">
-        <v>6.1</v>
-      </c>
-      <c r="B30" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C30" s="9"/>
-      <c r="D30" s="74" t="s">
-        <v>5</v>
-      </c>
-      <c r="E30" s="8">
-        <v>1</v>
-      </c>
-      <c r="F30" s="25">
-        <f>F29*E30</f>
-        <v>100.99</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="74">
-        <v>6.2</v>
-      </c>
-      <c r="B31" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C31" s="9"/>
-      <c r="D31" s="74" t="s">
-        <v>7</v>
-      </c>
-      <c r="E31" s="8">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="F31" s="25">
-        <f>E31*F29</f>
-        <v>111.089</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="74">
-        <v>6.3</v>
-      </c>
-      <c r="B32" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C32" s="9"/>
-      <c r="D32" s="74" t="s">
-        <v>6</v>
-      </c>
-      <c r="E32" s="8">
-        <v>1.8</v>
-      </c>
-      <c r="F32" s="25">
-        <f>E32*F29*80</f>
-        <v>14542.559999999998</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="74">
-        <v>6.4</v>
-      </c>
-      <c r="B33" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="C33" s="9"/>
-      <c r="D33" s="74" t="s">
-        <v>41</v>
-      </c>
-      <c r="E33" s="8">
-        <v>8</v>
-      </c>
-      <c r="F33" s="25">
-        <f>ROUNDDOWN(E33*F29,0)</f>
+        <f>ROUNDDOWN(E28*F24,0)</f>
         <v>807</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E46"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="16384" width="9.140625" style="110"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" s="96" t="s">
-        <v>110</v>
-      </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="98"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="86" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="86" t="s">
-        <v>97</v>
-      </c>
-      <c r="C2" s="86" t="s">
-        <v>98</v>
-      </c>
-      <c r="D2" s="86" t="s">
-        <v>93</v>
-      </c>
-      <c r="E2" s="86" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="86">
-        <v>1</v>
-      </c>
-      <c r="B3" s="86">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C3" s="86">
-        <v>1.054</v>
-      </c>
-      <c r="D3" s="86">
-        <v>7.1</v>
-      </c>
-      <c r="E3" s="86">
-        <v>46.62</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="96" t="s">
-        <v>110</v>
-      </c>
-      <c r="B5" s="97"/>
-      <c r="C5" s="97"/>
-      <c r="D5" s="97"/>
-      <c r="E5" s="98"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="86" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="86" t="s">
-        <v>97</v>
-      </c>
-      <c r="C6" s="86" t="s">
-        <v>98</v>
-      </c>
-      <c r="D6" s="86" t="s">
-        <v>93</v>
-      </c>
-      <c r="E6" s="86" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="86">
-        <v>1</v>
-      </c>
-      <c r="B7" s="86">
-        <v>1</v>
-      </c>
-      <c r="C7" s="86" t="s">
-        <v>113</v>
-      </c>
-      <c r="D7" s="86">
-        <v>9.1</v>
-      </c>
-      <c r="E7" s="109">
-        <v>37.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="86">
-        <v>2</v>
-      </c>
-      <c r="B8" s="86">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C8" s="86" t="s">
-        <v>113</v>
-      </c>
-      <c r="D8" s="86">
-        <v>9.1</v>
-      </c>
-      <c r="E8" s="109">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D9" s="110" t="s">
-        <v>114</v>
-      </c>
-      <c r="E9" s="110">
-        <f>SUM(E7:E8)</f>
-        <v>41.7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="96" t="s">
-        <v>110</v>
-      </c>
-      <c r="B11" s="97"/>
-      <c r="C11" s="97"/>
-      <c r="D11" s="97"/>
-      <c r="E11" s="98"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="86" t="s">
-        <v>0</v>
-      </c>
-      <c r="B12" s="86" t="s">
-        <v>97</v>
-      </c>
-      <c r="C12" s="86" t="s">
-        <v>98</v>
-      </c>
-      <c r="D12" s="86" t="s">
-        <v>93</v>
-      </c>
-      <c r="E12" s="86" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" s="86">
-        <v>1</v>
-      </c>
-      <c r="B13" s="86">
-        <v>1</v>
-      </c>
-      <c r="C13" s="86" t="s">
-        <v>113</v>
-      </c>
-      <c r="D13" s="86">
-        <v>5</v>
-      </c>
-      <c r="E13" s="109">
-        <v>11.69</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" s="86">
-        <v>2</v>
-      </c>
-      <c r="B14" s="86">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C14" s="86" t="s">
-        <v>113</v>
-      </c>
-      <c r="D14" s="86">
-        <v>5</v>
-      </c>
-      <c r="E14" s="109">
-        <v>7.73</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D15" s="110" t="s">
-        <v>114</v>
-      </c>
-      <c r="E15" s="110">
-        <f>SUM(E13:E14)</f>
-        <v>19.420000000000002</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" s="86" t="s">
-        <v>48</v>
-      </c>
-      <c r="B17" s="86"/>
-      <c r="C17" s="86"/>
-      <c r="D17" s="86"/>
-      <c r="E17" s="86"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18" s="86" t="s">
-        <v>0</v>
-      </c>
-      <c r="B18" s="86" t="s">
-        <v>97</v>
-      </c>
-      <c r="C18" s="86" t="s">
-        <v>98</v>
-      </c>
-      <c r="D18" s="86" t="s">
-        <v>93</v>
-      </c>
-      <c r="E18" s="86" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19" s="86">
-        <v>1</v>
-      </c>
-      <c r="B19" s="86">
-        <v>1</v>
-      </c>
-      <c r="C19" s="86">
-        <v>1.024</v>
-      </c>
-      <c r="D19" s="86">
-        <v>6</v>
-      </c>
-      <c r="E19" s="86">
-        <v>13.62</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A20" s="86">
-        <v>2</v>
-      </c>
-      <c r="B20" s="86">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C20" s="86">
-        <v>1.0449999999999999</v>
-      </c>
-      <c r="D20" s="86">
-        <v>6</v>
-      </c>
-      <c r="E20" s="86">
-        <v>161.78</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A21" s="86">
-        <v>3</v>
-      </c>
-      <c r="B21" s="86">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C21" s="86">
-        <v>1.046</v>
-      </c>
-      <c r="D21" s="86">
-        <v>6</v>
-      </c>
-      <c r="E21" s="86">
-        <v>161.15</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A22" s="86">
-        <v>4</v>
-      </c>
-      <c r="B22" s="86">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C22" s="86">
-        <v>1.0529999999999999</v>
-      </c>
-      <c r="D22" s="86">
-        <v>6</v>
-      </c>
-      <c r="E22" s="86">
-        <v>443.48</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23" s="86">
-        <v>5</v>
-      </c>
-      <c r="B23" s="86">
-        <v>1</v>
-      </c>
-      <c r="C23" s="86">
-        <v>1.034</v>
-      </c>
-      <c r="D23" s="86">
-        <v>7</v>
-      </c>
-      <c r="E23" s="86">
-        <v>17.22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A24" s="86">
-        <v>6</v>
-      </c>
-      <c r="B24" s="86">
-        <v>1</v>
-      </c>
-      <c r="C24" s="86">
-        <v>1.0349999999999999</v>
-      </c>
-      <c r="D24" s="86">
-        <v>7</v>
-      </c>
-      <c r="E24" s="86">
-        <v>21.63</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A25" s="86">
-        <v>7</v>
-      </c>
-      <c r="B25" s="86">
-        <v>1</v>
-      </c>
-      <c r="C25" s="86">
-        <v>1.036</v>
-      </c>
-      <c r="D25" s="86">
-        <v>7</v>
-      </c>
-      <c r="E25" s="86">
-        <v>5.76</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A26" s="86">
-        <v>8</v>
-      </c>
-      <c r="B26" s="86">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C26" s="86">
-        <v>1.054</v>
-      </c>
-      <c r="D26" s="86">
-        <v>7</v>
-      </c>
-      <c r="E26" s="86">
-        <v>14.54</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A27" s="86">
-        <v>9</v>
-      </c>
-      <c r="B27" s="86">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C27" s="86">
-        <v>1.054</v>
-      </c>
-      <c r="D27" s="86">
-        <v>7.1</v>
-      </c>
-      <c r="E27" s="86">
-        <v>46.62</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A28" s="86">
-        <v>10</v>
-      </c>
-      <c r="B28" s="86">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C28" s="86">
-        <v>1.048</v>
-      </c>
-      <c r="D28" s="86">
-        <v>8.1</v>
-      </c>
-      <c r="E28" s="86">
-        <v>23.92</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A29" s="86">
-        <v>11</v>
-      </c>
-      <c r="B29" s="86">
-        <v>1</v>
-      </c>
-      <c r="C29" s="86">
-        <v>1.0369999999999999</v>
-      </c>
-      <c r="D29" s="86">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="E29" s="86">
-        <v>3.34</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A30" s="86">
-        <v>12</v>
-      </c>
-      <c r="B30" s="86">
-        <v>1</v>
-      </c>
-      <c r="C30" s="86">
-        <v>1.038</v>
-      </c>
-      <c r="D30" s="86">
-        <v>8.1999999999999993</v>
-      </c>
-      <c r="E30" s="86">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A31" s="86">
-        <v>13</v>
-      </c>
-      <c r="B31" s="86">
-        <v>1</v>
-      </c>
-      <c r="C31" s="86">
-        <v>1.026</v>
-      </c>
-      <c r="D31" s="86">
-        <v>9</v>
-      </c>
-      <c r="E31" s="86">
-        <v>191.68</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A32" s="86">
-        <v>14</v>
-      </c>
-      <c r="B32" s="86">
-        <v>1</v>
-      </c>
-      <c r="C32" s="86">
-        <v>1.0269999999999999</v>
-      </c>
-      <c r="D32" s="86">
-        <v>9</v>
-      </c>
-      <c r="E32" s="86">
-        <v>114.04</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A33" s="86">
-        <v>15</v>
-      </c>
-      <c r="B33" s="86">
-        <v>1</v>
-      </c>
-      <c r="C33" s="86">
-        <v>1.028</v>
-      </c>
-      <c r="D33" s="86">
-        <v>9</v>
-      </c>
-      <c r="E33" s="86">
-        <v>68.81</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A34" s="86">
-        <v>16</v>
-      </c>
-      <c r="B34" s="86">
-        <v>1</v>
-      </c>
-      <c r="C34" s="86">
-        <v>1.0289999999999999</v>
-      </c>
-      <c r="D34" s="86">
-        <v>9</v>
-      </c>
-      <c r="E34" s="86">
-        <v>68.81</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A35" s="86">
-        <v>17</v>
-      </c>
-      <c r="B35" s="86">
-        <v>1</v>
-      </c>
-      <c r="C35" s="86">
-        <v>1.03</v>
-      </c>
-      <c r="D35" s="86">
-        <v>9</v>
-      </c>
-      <c r="E35" s="86">
-        <v>68.89</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A36" s="86">
-        <v>18</v>
-      </c>
-      <c r="B36" s="86">
-        <v>1</v>
-      </c>
-      <c r="C36" s="86">
-        <v>1.0309999999999999</v>
-      </c>
-      <c r="D36" s="86">
-        <v>9</v>
-      </c>
-      <c r="E36" s="86">
-        <v>68.89</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A37" s="86">
-        <v>19</v>
-      </c>
-      <c r="B37" s="86">
-        <v>1</v>
-      </c>
-      <c r="C37" s="86">
-        <v>1.032</v>
-      </c>
-      <c r="D37" s="86">
-        <v>9</v>
-      </c>
-      <c r="E37" s="86">
-        <v>68.069999999999993</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A38" s="86">
-        <v>20</v>
-      </c>
-      <c r="B38" s="86">
-        <v>1</v>
-      </c>
-      <c r="C38" s="86">
-        <v>1.0329999999999999</v>
-      </c>
-      <c r="D38" s="86">
-        <v>9</v>
-      </c>
-      <c r="E38" s="86">
-        <v>139.1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A39" s="86">
-        <v>21</v>
-      </c>
-      <c r="B39" s="86">
-        <v>1</v>
-      </c>
-      <c r="C39" s="86">
-        <v>1.0389999999999999</v>
-      </c>
-      <c r="D39" s="86">
-        <v>9</v>
-      </c>
-      <c r="E39" s="86">
-        <v>149.69999999999999</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A40" s="86">
-        <v>22</v>
-      </c>
-      <c r="B40" s="86">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C40" s="86">
-        <v>1.04</v>
-      </c>
-      <c r="D40" s="86">
-        <v>9</v>
-      </c>
-      <c r="E40" s="86">
-        <v>220.47</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A41" s="86">
-        <v>23</v>
-      </c>
-      <c r="B41" s="86">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C41" s="86">
-        <v>1.0429999999999999</v>
-      </c>
-      <c r="D41" s="86">
-        <v>9</v>
-      </c>
-      <c r="E41" s="86">
-        <v>61.99</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A42" s="86">
-        <v>24</v>
-      </c>
-      <c r="B42" s="86">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C42" s="86">
-        <v>1.044</v>
-      </c>
-      <c r="D42" s="86">
-        <v>9</v>
-      </c>
-      <c r="E42" s="86">
-        <v>14.14</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A43" s="86">
-        <v>25</v>
-      </c>
-      <c r="B43" s="86">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C43" s="86">
-        <v>1.0489999999999999</v>
-      </c>
-      <c r="D43" s="86">
-        <v>9</v>
-      </c>
-      <c r="E43" s="86">
-        <v>103.8</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A44" s="86">
-        <v>26</v>
-      </c>
-      <c r="B44" s="86">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C44" s="86">
-        <v>1.05</v>
-      </c>
-      <c r="D44" s="86">
-        <v>9</v>
-      </c>
-      <c r="E44" s="86">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A45" s="86">
-        <v>27</v>
-      </c>
-      <c r="B45" s="86">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C45" s="86">
-        <v>1.0509999999999999</v>
-      </c>
-      <c r="D45" s="86">
-        <v>9</v>
-      </c>
-      <c r="E45" s="86">
-        <v>31.58</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A46" s="86"/>
-      <c r="B46" s="86"/>
-      <c r="C46" s="86"/>
-      <c r="D46" s="86" t="s">
-        <v>114</v>
-      </c>
-      <c r="E46" s="86">
-        <f>SUM(E19:E45)</f>
-        <v>2310.2799999999997</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A11:E11"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E25"/>
+  <sheetPr>
+    <tabColor theme="0" tint="-0.14999847407452621"/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="110"/>
+    <col min="1" max="16384" width="9.140625" style="102"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" s="96" t="s">
-        <v>111</v>
-      </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="98"/>
+      <c r="A1" s="126" t="s">
+        <v>110</v>
+      </c>
+      <c r="B1" s="127"/>
+      <c r="C1" s="127"/>
+      <c r="D1" s="127"/>
+      <c r="E1" s="128"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="86" t="s">
@@ -6541,327 +6255,838 @@
         <v>1</v>
       </c>
       <c r="B3" s="86">
+        <v>1</v>
+      </c>
+      <c r="C3" s="86" t="s">
+        <v>113</v>
+      </c>
+      <c r="D3" s="86">
+        <v>9.1</v>
+      </c>
+      <c r="E3" s="101">
+        <f>37.5-2.48</f>
+        <v>35.020000000000003</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="86">
+        <v>2</v>
+      </c>
+      <c r="B4" s="86">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C3" s="86">
-        <v>1.054</v>
-      </c>
-      <c r="D3" s="86">
-        <v>7.1</v>
-      </c>
-      <c r="E3" s="86">
-        <v>46.62</v>
+      <c r="C4" s="86" t="s">
+        <v>113</v>
+      </c>
+      <c r="D4" s="86">
+        <v>9.1</v>
+      </c>
+      <c r="E4" s="101">
+        <v>4.2</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="108" t="s">
-        <v>111</v>
-      </c>
-      <c r="B5" s="108"/>
-      <c r="C5" s="108"/>
-      <c r="D5" s="108"/>
-      <c r="E5" s="108"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="86" t="s">
+      <c r="D5" s="102" t="s">
+        <v>114</v>
+      </c>
+      <c r="E5" s="102">
+        <f>SUM(E3:E4)</f>
+        <v>39.220000000000006</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="126" t="s">
+        <v>110</v>
+      </c>
+      <c r="B7" s="127"/>
+      <c r="C7" s="127"/>
+      <c r="D7" s="127"/>
+      <c r="E7" s="128"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="86" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="86" t="s">
+      <c r="B8" s="86" t="s">
         <v>97</v>
       </c>
-      <c r="C6" s="86" t="s">
+      <c r="C8" s="86" t="s">
         <v>98</v>
       </c>
-      <c r="D6" s="86" t="s">
+      <c r="D8" s="86" t="s">
         <v>93</v>
       </c>
-      <c r="E6" s="86" t="s">
+      <c r="E8" s="86" t="s">
         <v>51</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="86">
-        <v>1</v>
-      </c>
-      <c r="B7" s="86">
-        <v>1</v>
-      </c>
-      <c r="C7" s="86">
-        <v>2.0169999999999999</v>
-      </c>
-      <c r="D7" s="86">
-        <v>8.3000000000000007</v>
-      </c>
-      <c r="E7" s="86">
-        <v>3.22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="86">
-        <v>2</v>
-      </c>
-      <c r="B8" s="86">
-        <v>1</v>
-      </c>
-      <c r="C8" s="86">
-        <v>2.1619999999999999</v>
-      </c>
-      <c r="D8" s="86">
-        <v>8.3000000000000007</v>
-      </c>
-      <c r="E8" s="86">
-        <v>5.25</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="86">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B9" s="86">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C9" s="86">
-        <v>2.097</v>
+        <v>1</v>
+      </c>
+      <c r="C9" s="86" t="s">
+        <v>113</v>
       </c>
       <c r="D9" s="86">
-        <v>8.3000000000000007</v>
-      </c>
-      <c r="E9" s="86">
-        <v>4.8499999999999996</v>
+        <v>5</v>
+      </c>
+      <c r="E9" s="101">
+        <v>11.69</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="86">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B10" s="86">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C10" s="86">
-        <v>2.0979999999999999</v>
+      <c r="C10" s="86" t="s">
+        <v>113</v>
       </c>
       <c r="D10" s="86">
-        <v>8.3000000000000007</v>
-      </c>
-      <c r="E10" s="86">
-        <v>4.76</v>
+        <v>5</v>
+      </c>
+      <c r="E10" s="101">
+        <v>7.73</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="86">
-        <v>5</v>
-      </c>
-      <c r="B11" s="86">
+      <c r="D11" s="102" t="s">
+        <v>114</v>
+      </c>
+      <c r="E11" s="102">
+        <f>SUM(E9:E10)</f>
+        <v>19.420000000000002</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="126" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="127"/>
+      <c r="C13" s="127"/>
+      <c r="D13" s="127"/>
+      <c r="E13" s="128"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" s="86" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="86" t="s">
+        <v>97</v>
+      </c>
+      <c r="C14" s="86" t="s">
+        <v>98</v>
+      </c>
+      <c r="D14" s="86" t="s">
+        <v>93</v>
+      </c>
+      <c r="E14" s="86" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" s="86">
+        <v>1</v>
+      </c>
+      <c r="B15" s="86">
+        <v>1</v>
+      </c>
+      <c r="C15" s="86">
+        <v>1.024</v>
+      </c>
+      <c r="D15" s="86">
+        <v>6</v>
+      </c>
+      <c r="E15" s="86">
+        <v>13.62</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" s="86">
+        <v>2</v>
+      </c>
+      <c r="B16" s="86">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C11" s="86">
-        <v>2.1019999999999999</v>
-      </c>
-      <c r="D11" s="86">
-        <v>8.3000000000000007</v>
-      </c>
-      <c r="E11" s="86">
-        <v>9.24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="86">
+      <c r="C16" s="86">
+        <v>1.0449999999999999</v>
+      </c>
+      <c r="D16" s="86">
         <v>6</v>
       </c>
-      <c r="B12" s="86">
-        <v>1</v>
-      </c>
-      <c r="C12" s="86" t="s">
-        <v>113</v>
-      </c>
-      <c r="D12" s="86">
-        <v>9.3000000000000007</v>
-      </c>
-      <c r="E12" s="109">
-        <v>14.5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" s="86">
-        <v>7</v>
-      </c>
-      <c r="B13" s="86">
+      <c r="E16" s="86">
+        <v>161.78</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" s="86">
+        <v>3</v>
+      </c>
+      <c r="B17" s="86">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C13" s="86" t="s">
-        <v>113</v>
-      </c>
-      <c r="D13" s="86">
-        <v>9.3000000000000007</v>
-      </c>
-      <c r="E13" s="109">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" s="86"/>
-      <c r="B14" s="86"/>
-      <c r="C14" s="86"/>
-      <c r="D14" s="86" t="s">
-        <v>114</v>
-      </c>
-      <c r="E14" s="86">
-        <f>SUM(E7:E13)</f>
-        <v>42.32</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A16" s="108" t="s">
-        <v>111</v>
-      </c>
-      <c r="B16" s="108"/>
-      <c r="C16" s="108"/>
-      <c r="D16" s="108"/>
-      <c r="E16" s="108"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" s="86" t="s">
-        <v>0</v>
-      </c>
-      <c r="B17" s="86" t="s">
-        <v>97</v>
-      </c>
-      <c r="C17" s="86" t="s">
-        <v>98</v>
-      </c>
-      <c r="D17" s="86" t="s">
-        <v>93</v>
-      </c>
-      <c r="E17" s="86" t="s">
-        <v>51</v>
+      <c r="C17" s="86">
+        <v>1.046</v>
+      </c>
+      <c r="D17" s="86">
+        <v>6</v>
+      </c>
+      <c r="E17" s="86">
+        <v>161.15</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="86">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B18" s="86">
-        <v>1</v>
-      </c>
-      <c r="C18" s="86" t="s">
-        <v>113</v>
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C18" s="86">
+        <v>1.0529999999999999</v>
       </c>
       <c r="D18" s="86">
-        <v>5.0999999999999996</v>
+        <v>6</v>
       </c>
       <c r="E18" s="86">
-        <v>8.2799999999999994</v>
+        <v>443.48</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="86">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B19" s="86">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C19" s="86" t="s">
-        <v>113</v>
+        <v>1</v>
+      </c>
+      <c r="C19" s="86">
+        <v>1.034</v>
       </c>
       <c r="D19" s="86">
-        <v>5.0999999999999996</v>
+        <v>7</v>
       </c>
       <c r="E19" s="86">
-        <v>8.09</v>
+        <v>17.22</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="86">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B20" s="86">
+        <v>1</v>
+      </c>
+      <c r="C20" s="86">
+        <v>1.0349999999999999</v>
+      </c>
+      <c r="D20" s="86">
+        <v>7</v>
+      </c>
+      <c r="E20" s="86">
+        <v>21.63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" s="86">
+        <v>7</v>
+      </c>
+      <c r="B21" s="86">
+        <v>1</v>
+      </c>
+      <c r="C21" s="86">
+        <v>1.036</v>
+      </c>
+      <c r="D21" s="86">
+        <v>7</v>
+      </c>
+      <c r="E21" s="86">
+        <v>5.76</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" s="86">
+        <v>8</v>
+      </c>
+      <c r="B22" s="86">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C20" s="86">
-        <v>2.16</v>
-      </c>
-      <c r="D20" s="86">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="E20" s="86">
-        <v>72.64</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A21" s="86"/>
-      <c r="B21" s="86"/>
-      <c r="C21" s="86"/>
-      <c r="D21" s="86" t="s">
-        <v>114</v>
-      </c>
-      <c r="E21" s="86">
-        <f>SUM(E18:E20)</f>
-        <v>89.009999999999991</v>
+      <c r="C22" s="86">
+        <v>1.054</v>
+      </c>
+      <c r="D22" s="86">
+        <v>7</v>
+      </c>
+      <c r="E22" s="86">
+        <v>14.54</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23" s="86"/>
+      <c r="A23" s="86">
+        <v>9</v>
+      </c>
       <c r="B23" s="86">
         <v>4.0999999999999996</v>
       </c>
       <c r="C23" s="86">
-        <v>2.081</v>
+        <v>1.048</v>
       </c>
       <c r="D23" s="86">
+        <v>8.1</v>
+      </c>
+      <c r="E23" s="86">
+        <v>23.92</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" s="86">
+        <v>10</v>
+      </c>
+      <c r="B24" s="86">
+        <v>1</v>
+      </c>
+      <c r="C24" s="86">
+        <v>1.0369999999999999</v>
+      </c>
+      <c r="D24" s="86">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="E24" s="86">
+        <v>3.34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25" s="86">
         <v>11</v>
       </c>
-      <c r="E23" s="86">
-        <v>298.27999999999997</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A24" s="86"/>
-      <c r="B24" s="86">
+      <c r="B25" s="86">
+        <v>1</v>
+      </c>
+      <c r="C25" s="86">
+        <v>1.038</v>
+      </c>
+      <c r="D25" s="86">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="E25" s="86">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" s="86">
+        <v>12</v>
+      </c>
+      <c r="B26" s="86">
+        <v>1</v>
+      </c>
+      <c r="C26" s="86">
+        <v>1.026</v>
+      </c>
+      <c r="D26" s="86">
+        <v>9</v>
+      </c>
+      <c r="E26" s="86">
+        <v>191.68</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" s="86">
+        <v>13</v>
+      </c>
+      <c r="B27" s="86">
+        <v>1</v>
+      </c>
+      <c r="C27" s="86">
+        <v>1.0269999999999999</v>
+      </c>
+      <c r="D27" s="86">
+        <v>9</v>
+      </c>
+      <c r="E27" s="86">
+        <v>114.04</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" s="86">
+        <v>14</v>
+      </c>
+      <c r="B28" s="86">
+        <v>1</v>
+      </c>
+      <c r="C28" s="86">
+        <v>1.028</v>
+      </c>
+      <c r="D28" s="86">
+        <v>9</v>
+      </c>
+      <c r="E28" s="86">
+        <v>68.81</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29" s="86">
+        <v>15</v>
+      </c>
+      <c r="B29" s="86">
+        <v>1</v>
+      </c>
+      <c r="C29" s="86">
+        <v>1.0289999999999999</v>
+      </c>
+      <c r="D29" s="86">
+        <v>9</v>
+      </c>
+      <c r="E29" s="86">
+        <v>68.81</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30" s="86">
+        <v>16</v>
+      </c>
+      <c r="B30" s="86">
+        <v>1</v>
+      </c>
+      <c r="C30" s="86">
+        <v>1.03</v>
+      </c>
+      <c r="D30" s="86">
+        <v>9</v>
+      </c>
+      <c r="E30" s="86">
+        <v>68.89</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31" s="86">
+        <v>17</v>
+      </c>
+      <c r="B31" s="86">
+        <v>1</v>
+      </c>
+      <c r="C31" s="86">
+        <v>1.0309999999999999</v>
+      </c>
+      <c r="D31" s="86">
+        <v>9</v>
+      </c>
+      <c r="E31" s="86">
+        <v>68.89</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32" s="86">
+        <v>18</v>
+      </c>
+      <c r="B32" s="86">
+        <v>1</v>
+      </c>
+      <c r="C32" s="86">
+        <v>1.032</v>
+      </c>
+      <c r="D32" s="86">
+        <v>9</v>
+      </c>
+      <c r="E32" s="86">
+        <v>68.069999999999993</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33" s="86">
+        <v>19</v>
+      </c>
+      <c r="B33" s="86">
+        <v>1</v>
+      </c>
+      <c r="C33" s="86">
+        <v>1.0329999999999999</v>
+      </c>
+      <c r="D33" s="86">
+        <v>9</v>
+      </c>
+      <c r="E33" s="86">
+        <v>139.1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34" s="86">
+        <v>20</v>
+      </c>
+      <c r="B34" s="86">
+        <v>1</v>
+      </c>
+      <c r="C34" s="86">
+        <v>1.0389999999999999</v>
+      </c>
+      <c r="D34" s="86">
+        <v>9</v>
+      </c>
+      <c r="E34" s="86">
+        <v>149.69999999999999</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A35" s="86">
+        <v>21</v>
+      </c>
+      <c r="B35" s="86">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C24" s="86">
-        <v>2.085</v>
-      </c>
-      <c r="D24" s="86">
-        <v>11.1</v>
-      </c>
-      <c r="E24" s="86">
-        <v>168.62</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D25" s="86" t="s">
+      <c r="C35" s="86">
+        <v>1.04</v>
+      </c>
+      <c r="D35" s="86">
+        <v>9</v>
+      </c>
+      <c r="E35" s="86">
+        <v>220.47</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A36" s="86">
+        <v>22</v>
+      </c>
+      <c r="B36" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C36" s="86">
+        <v>1.0429999999999999</v>
+      </c>
+      <c r="D36" s="86">
+        <v>9</v>
+      </c>
+      <c r="E36" s="86">
+        <v>61.99</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A37" s="86">
+        <v>23</v>
+      </c>
+      <c r="B37" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C37" s="86">
+        <v>1.044</v>
+      </c>
+      <c r="D37" s="86">
+        <v>9</v>
+      </c>
+      <c r="E37" s="86">
+        <v>14.14</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A38" s="86">
+        <v>24</v>
+      </c>
+      <c r="B38" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C38" s="86">
+        <v>1.0489999999999999</v>
+      </c>
+      <c r="D38" s="86">
+        <v>9</v>
+      </c>
+      <c r="E38" s="86">
+        <v>103.8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A39" s="86">
+        <v>25</v>
+      </c>
+      <c r="B39" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C39" s="86">
+        <v>1.05</v>
+      </c>
+      <c r="D39" s="86">
+        <v>9</v>
+      </c>
+      <c r="E39" s="86">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A40" s="86">
+        <v>26</v>
+      </c>
+      <c r="B40" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C40" s="86">
+        <v>1.0509999999999999</v>
+      </c>
+      <c r="D40" s="86">
+        <v>9</v>
+      </c>
+      <c r="E40" s="86">
+        <v>31.58</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A41" s="86"/>
+      <c r="B41" s="86"/>
+      <c r="C41" s="86"/>
+      <c r="D41" s="86" t="s">
         <v>114</v>
       </c>
-      <c r="E25" s="86">
-        <f>SUM(E23:E24)</f>
-        <v>466.9</v>
+      <c r="E41" s="86">
+        <f>SUM(E15:E40)</f>
+        <v>2263.66</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A13:E13"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor theme="0" tint="-0.14999847407452621"/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="16384" width="9.140625" style="102"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="129" t="s">
+        <v>111</v>
+      </c>
+      <c r="B1" s="129"/>
+      <c r="C1" s="129"/>
+      <c r="D1" s="129"/>
+      <c r="E1" s="129"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="86" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="86" t="s">
+        <v>97</v>
+      </c>
+      <c r="C2" s="86" t="s">
+        <v>98</v>
+      </c>
+      <c r="D2" s="86" t="s">
+        <v>93</v>
+      </c>
+      <c r="E2" s="86" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="86">
+        <v>1</v>
+      </c>
+      <c r="B3" s="86">
+        <v>1</v>
+      </c>
+      <c r="C3" s="86" t="s">
+        <v>113</v>
+      </c>
+      <c r="D3" s="86">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="E3" s="101">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="86">
+        <v>2</v>
+      </c>
+      <c r="B4" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C4" s="86" t="s">
+        <v>113</v>
+      </c>
+      <c r="D4" s="86">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="E4" s="101">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="86"/>
+      <c r="B5" s="86"/>
+      <c r="C5" s="86"/>
+      <c r="D5" s="86" t="s">
+        <v>114</v>
+      </c>
+      <c r="E5" s="121">
+        <f>SUM(E3:E4)</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="129" t="s">
+        <v>111</v>
+      </c>
+      <c r="B7" s="129"/>
+      <c r="C7" s="129"/>
+      <c r="D7" s="129"/>
+      <c r="E7" s="129"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="86" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="86" t="s">
+        <v>97</v>
+      </c>
+      <c r="C8" s="86" t="s">
+        <v>98</v>
+      </c>
+      <c r="D8" s="86" t="s">
+        <v>93</v>
+      </c>
+      <c r="E8" s="86" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="86">
+        <v>1</v>
+      </c>
+      <c r="B9" s="86">
+        <v>1</v>
+      </c>
+      <c r="C9" s="86" t="s">
+        <v>113</v>
+      </c>
+      <c r="D9" s="86">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="E9" s="86">
+        <v>8.2799999999999994</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" s="86">
+        <v>2</v>
+      </c>
+      <c r="B10" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C10" s="86" t="s">
+        <v>113</v>
+      </c>
+      <c r="D10" s="86">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="E10" s="86">
+        <v>8.09</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="86">
+        <v>3</v>
+      </c>
+      <c r="B11" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C11" s="86">
+        <v>2.16</v>
+      </c>
+      <c r="D11" s="86">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="E11" s="86">
+        <v>72.64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" s="86"/>
+      <c r="B12" s="86"/>
+      <c r="C12" s="86"/>
+      <c r="D12" s="86" t="s">
+        <v>114</v>
+      </c>
+      <c r="E12" s="86">
+        <f>SUM(E9:E11)</f>
+        <v>89.009999999999991</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" s="129" t="s">
+        <v>111</v>
+      </c>
+      <c r="B14" s="129"/>
+      <c r="C14" s="129"/>
+      <c r="D14" s="129"/>
+      <c r="E14" s="129"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" s="86">
+        <v>1</v>
+      </c>
+      <c r="B15" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C15" s="86">
+        <v>2.085</v>
+      </c>
+      <c r="D15" s="86">
+        <v>11.1</v>
+      </c>
+      <c r="E15" s="86">
+        <v>168.62</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D16" s="86" t="s">
+        <v>114</v>
+      </c>
+      <c r="E16" s="86">
+        <f>SUM(E15:E15)</f>
+        <v>168.62</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A14:E14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E13"/>
+  <sheetPr>
+    <tabColor theme="0" tint="-0.14999847407452621"/>
+  </sheetPr>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="108" t="s">
+      <c r="A1" s="129" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="108"/>
-      <c r="C1" s="108"/>
-      <c r="D1" s="108"/>
-      <c r="E1" s="108"/>
+      <c r="B1" s="129"/>
+      <c r="C1" s="129"/>
+      <c r="D1" s="129"/>
+      <c r="E1" s="129"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="86" t="s">
@@ -6882,161 +7107,110 @@
     </row>
     <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="86">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B3" s="86">
         <v>1</v>
       </c>
-      <c r="C3" s="86">
-        <v>3.0179999999999998</v>
+      <c r="C3" s="86" t="s">
+        <v>113</v>
       </c>
       <c r="D3" s="86">
-        <v>8.3000000000000007</v>
-      </c>
-      <c r="E3" s="86">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="86">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="E3" s="101">
+        <v>14.79</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="86"/>
+      <c r="B4" s="86"/>
+      <c r="C4" s="86"/>
+      <c r="D4" s="86" t="s">
+        <v>114</v>
+      </c>
+      <c r="E4" s="86">
+        <f>SUM(E3:E3)</f>
+        <v>14.79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="129" t="s">
+        <v>109</v>
+      </c>
+      <c r="B6" s="129"/>
+      <c r="C6" s="129"/>
+      <c r="D6" s="129"/>
+      <c r="E6" s="129"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="86" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="86" t="s">
+        <v>97</v>
+      </c>
+      <c r="C7" s="86" t="s">
+        <v>98</v>
+      </c>
+      <c r="D7" s="86" t="s">
+        <v>93</v>
+      </c>
+      <c r="E7" s="86" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="86">
+        <v>1</v>
+      </c>
+      <c r="B8" s="86">
+        <v>1</v>
+      </c>
+      <c r="C8" s="86" t="s">
+        <v>113</v>
+      </c>
+      <c r="D8" s="86">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="E8" s="86">
+        <v>6.03</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="86">
         <v>2</v>
       </c>
-      <c r="B4" s="86">
+      <c r="B9" s="86">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C4" s="86">
-        <v>3.0209999999999999</v>
-      </c>
-      <c r="D4" s="86">
-        <v>8.3000000000000007</v>
-      </c>
-      <c r="E4" s="86">
-        <v>15.62</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="86">
-        <v>3</v>
-      </c>
-      <c r="B5" s="86">
-        <v>1</v>
-      </c>
-      <c r="C5" s="86">
-        <v>3.0920000000000001</v>
-      </c>
-      <c r="D5" s="86">
-        <v>8.3000000000000007</v>
-      </c>
-      <c r="E5" s="86">
-        <v>5.24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="86">
-        <v>4</v>
-      </c>
-      <c r="B6" s="86">
-        <v>1</v>
-      </c>
-      <c r="C6" s="86" t="s">
+      <c r="C9" s="86" t="s">
         <v>113</v>
       </c>
-      <c r="D6" s="86">
-        <v>9.3000000000000007</v>
-      </c>
-      <c r="E6" s="109">
-        <v>14.79</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="86"/>
-      <c r="B7" s="86"/>
-      <c r="C7" s="86"/>
-      <c r="D7" s="86" t="s">
+      <c r="D9" s="86">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="E9" s="86">
+        <v>5.95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="86"/>
+      <c r="B10" s="86"/>
+      <c r="C10" s="86"/>
+      <c r="D10" s="86" t="s">
         <v>114</v>
       </c>
-      <c r="E7" s="86">
-        <f>SUM(E3:E6)</f>
-        <v>38.85</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="108" t="s">
-        <v>109</v>
-      </c>
-      <c r="B9" s="108"/>
-      <c r="C9" s="108"/>
-      <c r="D9" s="108"/>
-      <c r="E9" s="108"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="86" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" s="86" t="s">
-        <v>97</v>
-      </c>
-      <c r="C10" s="86" t="s">
-        <v>98</v>
-      </c>
-      <c r="D10" s="86" t="s">
-        <v>93</v>
-      </c>
-      <c r="E10" s="86" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="86">
-        <v>1</v>
-      </c>
-      <c r="B11" s="86">
-        <v>1</v>
-      </c>
-      <c r="C11" s="86" t="s">
-        <v>113</v>
-      </c>
-      <c r="D11" s="86">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="E11" s="86">
-        <v>6.03</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="86">
-        <v>2</v>
-      </c>
-      <c r="B12" s="86">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="C12" s="86" t="s">
-        <v>113</v>
-      </c>
-      <c r="D12" s="86">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="E12" s="86">
-        <v>5.95</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="86"/>
-      <c r="B13" s="86"/>
-      <c r="C13" s="86"/>
-      <c r="D13" s="86" t="s">
-        <v>114</v>
-      </c>
-      <c r="E13" s="86">
-        <f>SUM(E11:E12)</f>
+      <c r="E10" s="86">
+        <f>SUM(E8:E9)</f>
         <v>11.98</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7392,15 +7566,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="92" t="s">
+      <c r="A1" s="122" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="92"/>
-      <c r="C1" s="92"/>
-      <c r="D1" s="92"/>
-      <c r="E1" s="92"/>
-      <c r="F1" s="92"/>
-      <c r="G1" s="92"/>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="10"/>
@@ -8335,7 +8509,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="22">
-        <f>'Спец 3 эт'!E28</f>
+        <f>'Спец 3 эт'!E24</f>
         <v>25.92</v>
       </c>
       <c r="G3" s="23">
@@ -8471,15 +8645,15 @@
         <v>1</v>
       </c>
       <c r="F8" s="22">
-        <f>'Спец 3 эт'!C28+'Спец 3 эт'!D28+'Спец 3 эт'!F28</f>
-        <v>1745.29</v>
+        <f>'Спец 3 эт'!C24+'Спец 3 эт'!D24+'Спец 3 эт'!F24</f>
+        <v>1231.23</v>
       </c>
       <c r="G8" s="23">
         <v>5553.92</v>
       </c>
       <c r="I8" s="32">
         <f t="shared" si="0"/>
-        <v>-3808.63</v>
+        <v>-4322.6900000000005</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -8498,14 +8672,14 @@
       </c>
       <c r="F9" s="25">
         <f>ROUND(E9*F8, 0)</f>
-        <v>13962</v>
+        <v>9850</v>
       </c>
       <c r="G9" s="16">
         <v>44431.360000000001</v>
       </c>
       <c r="I9" s="32">
         <f t="shared" si="0"/>
-        <v>-30469.360000000001</v>
+        <v>-34581.360000000001</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -8524,7 +8698,7 @@
       </c>
       <c r="F10" s="25">
         <f>E10*F8*65</f>
-        <v>204198.93</v>
+        <v>144053.91</v>
       </c>
       <c r="G10" s="16">
         <v>649808.64000000001</v>
@@ -8535,7 +8709,7 @@
       </c>
       <c r="I10" s="32">
         <f t="shared" si="0"/>
-        <v>-445609.71</v>
+        <v>-505754.73</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -8554,14 +8728,14 @@
       </c>
       <c r="F11" s="25">
         <f>E11*F8</f>
-        <v>1919.8190000000002</v>
+        <v>1354.3530000000001</v>
       </c>
       <c r="G11" s="16">
         <v>6109.3119999999999</v>
       </c>
       <c r="I11" s="32">
         <f t="shared" si="0"/>
-        <v>-4189.4929999999995</v>
+        <v>-4754.9589999999998</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -8580,24 +8754,25 @@
       </c>
       <c r="F12" s="25">
         <f>E12*F8</f>
-        <v>1745.29</v>
+        <v>1231.23</v>
       </c>
       <c r="G12" s="16">
         <v>5553.92</v>
       </c>
       <c r="I12" s="32">
         <f t="shared" si="0"/>
-        <v>-3808.63</v>
+        <v>-4322.6900000000005</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7" style="11" customWidth="1"/>
@@ -8608,15 +8783,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="92" t="s">
+      <c r="A1" s="122" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="92"/>
-      <c r="C1" s="92"/>
-      <c r="D1" s="92"/>
-      <c r="E1" s="92"/>
-      <c r="F1" s="92"/>
-      <c r="G1" s="92"/>
+      <c r="B1" s="122"/>
+      <c r="C1" s="122"/>
+      <c r="D1" s="122"/>
+      <c r="E1" s="122"/>
+      <c r="F1" s="122"/>
+      <c r="G1" s="122"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="10"/>
@@ -8685,7 +8860,7 @@
       <c r="E4" s="41"/>
       <c r="F4" s="47"/>
       <c r="G4" s="25">
-        <f t="shared" ref="G4:G27" si="0">SUM(C4:F4)</f>
+        <f>SUM(C4:F4)</f>
         <v>13.62</v>
       </c>
       <c r="K4">
@@ -8706,7 +8881,7 @@
       <c r="E5" s="41"/>
       <c r="F5" s="47"/>
       <c r="G5" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(C5:F5)</f>
         <v>15.07</v>
       </c>
       <c r="K5">
@@ -8727,7 +8902,7 @@
       <c r="E6" s="41"/>
       <c r="F6" s="47"/>
       <c r="G6" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(C6:F6)</f>
         <v>17.21</v>
       </c>
       <c r="K6">
@@ -8748,7 +8923,7 @@
       <c r="E7" s="41"/>
       <c r="F7" s="47"/>
       <c r="G7" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(C7:F7)</f>
         <v>21.12</v>
       </c>
       <c r="K7">
@@ -8769,7 +8944,7 @@
       <c r="E8" s="41"/>
       <c r="F8" s="47"/>
       <c r="G8" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(C8:F8)</f>
         <v>5.0599999999999996</v>
       </c>
       <c r="K8">
@@ -8790,7 +8965,7 @@
       </c>
       <c r="F9" s="47"/>
       <c r="G9" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(C9:F9)</f>
         <v>5.0599999999999996</v>
       </c>
       <c r="K9">
@@ -8811,7 +8986,7 @@
       </c>
       <c r="F10" s="47"/>
       <c r="G10" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(C10:F10)</f>
         <v>5.24</v>
       </c>
       <c r="K10">
@@ -8832,7 +9007,7 @@
       </c>
       <c r="F11" s="47"/>
       <c r="G11" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(C11:F11)</f>
         <v>15.62</v>
       </c>
       <c r="K11">
@@ -8840,137 +9015,137 @@
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="10">
+      <c r="A12" s="108">
         <v>9</v>
       </c>
       <c r="B12" s="54">
-        <v>3.0009999999999999</v>
+        <v>3.004</v>
       </c>
       <c r="C12" s="50"/>
       <c r="D12" s="44"/>
       <c r="E12" s="41"/>
       <c r="F12" s="47">
-        <v>129.68</v>
+        <v>67.59</v>
       </c>
       <c r="G12" s="25">
-        <f t="shared" si="0"/>
-        <v>129.68</v>
+        <f>SUM(C12:F12)</f>
+        <v>67.59</v>
       </c>
       <c r="K12">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="10">
+      <c r="A13" s="108">
         <v>10</v>
       </c>
       <c r="B13" s="54">
-        <v>3.0019999999999998</v>
+        <v>3.008</v>
       </c>
       <c r="C13" s="50"/>
       <c r="D13" s="44"/>
       <c r="E13" s="41"/>
       <c r="F13" s="47">
-        <v>73.05</v>
+        <v>67.84</v>
       </c>
       <c r="G13" s="25">
-        <f t="shared" si="0"/>
-        <v>73.05</v>
+        <f>SUM(C13:F13)</f>
+        <v>67.84</v>
       </c>
       <c r="K13">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="10">
+      <c r="A14" s="108">
         <v>11</v>
       </c>
       <c r="B14" s="54">
-        <v>3.0030000000000001</v>
+        <v>3.0089999999999999</v>
       </c>
       <c r="C14" s="50"/>
       <c r="D14" s="44"/>
       <c r="E14" s="41"/>
       <c r="F14" s="47">
-        <v>71.709999999999994</v>
+        <v>68</v>
       </c>
       <c r="G14" s="25">
-        <f t="shared" si="0"/>
-        <v>71.709999999999994</v>
+        <f>SUM(C14:F14)</f>
+        <v>68</v>
       </c>
       <c r="K14">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="10">
+      <c r="A15" s="108">
         <v>12</v>
       </c>
       <c r="B15" s="54">
-        <v>3.004</v>
+        <v>3.01</v>
       </c>
       <c r="C15" s="50"/>
       <c r="D15" s="44"/>
       <c r="E15" s="41"/>
       <c r="F15" s="47">
-        <v>67.59</v>
+        <v>68</v>
       </c>
       <c r="G15" s="25">
-        <f t="shared" si="0"/>
-        <v>67.59</v>
+        <f>SUM(C15:F15)</f>
+        <v>68</v>
       </c>
       <c r="K15">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="10">
+      <c r="A16" s="108">
         <v>13</v>
       </c>
       <c r="B16" s="54">
-        <v>3.0049999999999999</v>
+        <v>3.0110000000000001</v>
       </c>
       <c r="C16" s="50"/>
       <c r="D16" s="44"/>
       <c r="E16" s="41"/>
       <c r="F16" s="47">
-        <v>239.62</v>
+        <v>67.14</v>
       </c>
       <c r="G16" s="25">
-        <f t="shared" si="0"/>
-        <v>239.62</v>
+        <f>SUM(C16:F16)</f>
+        <v>67.14</v>
       </c>
       <c r="K16">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="10">
+      <c r="A17" s="108">
         <v>14</v>
       </c>
       <c r="B17" s="54">
-        <v>3.008</v>
+        <v>3.012</v>
       </c>
       <c r="C17" s="50"/>
       <c r="D17" s="44"/>
       <c r="E17" s="41"/>
       <c r="F17" s="47">
-        <v>67.84</v>
+        <v>68</v>
       </c>
       <c r="G17" s="25">
-        <f t="shared" si="0"/>
-        <v>67.84</v>
+        <f>SUM(C17:F17)</f>
+        <v>68</v>
       </c>
       <c r="K17">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="10">
+      <c r="A18" s="108">
         <v>15</v>
       </c>
       <c r="B18" s="54">
-        <v>3.0089999999999999</v>
+        <v>3.0129999999999999</v>
       </c>
       <c r="C18" s="50"/>
       <c r="D18" s="44"/>
@@ -8979,7 +9154,7 @@
         <v>68</v>
       </c>
       <c r="G18" s="25">
-        <f t="shared" si="0"/>
+        <f>SUM(C18:F18)</f>
         <v>68</v>
       </c>
       <c r="K18">
@@ -8987,233 +9162,149 @@
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="10">
+      <c r="A19" s="108">
         <v>16</v>
       </c>
       <c r="B19" s="54">
-        <v>3.01</v>
+        <v>3.0139999999999998</v>
       </c>
       <c r="C19" s="50"/>
       <c r="D19" s="44"/>
       <c r="E19" s="41"/>
       <c r="F19" s="47">
-        <v>68</v>
+        <v>148.61000000000001</v>
       </c>
       <c r="G19" s="25">
-        <f t="shared" si="0"/>
-        <v>68</v>
+        <f>SUM(C19:F19)</f>
+        <v>148.61000000000001</v>
       </c>
       <c r="K19">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="10">
+      <c r="A20" s="108">
         <v>17</v>
       </c>
-      <c r="B20" s="54">
-        <v>3.0110000000000001</v>
+      <c r="B20" s="8">
+        <v>3.0190000000000001</v>
       </c>
       <c r="C20" s="50"/>
       <c r="D20" s="44"/>
       <c r="E20" s="41"/>
       <c r="F20" s="47">
-        <v>67.14</v>
+        <v>244.28</v>
       </c>
       <c r="G20" s="25">
-        <f t="shared" si="0"/>
-        <v>67.14</v>
+        <f>SUM(C20:F20)</f>
+        <v>244.28</v>
       </c>
       <c r="K20">
-        <v>1</v>
+        <v>4.0999999999999996</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="10">
+      <c r="A21" s="108">
         <v>18</v>
       </c>
       <c r="B21" s="54">
-        <v>3.012</v>
+        <v>3.02</v>
       </c>
       <c r="C21" s="50"/>
       <c r="D21" s="44"/>
       <c r="E21" s="41"/>
       <c r="F21" s="47">
-        <v>68</v>
+        <v>137.72999999999999</v>
       </c>
       <c r="G21" s="25">
-        <f t="shared" si="0"/>
-        <v>68</v>
+        <f>SUM(C21:F21)</f>
+        <v>137.72999999999999</v>
       </c>
       <c r="K21">
-        <v>1</v>
+        <v>4.0999999999999996</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="10">
+      <c r="A22" s="108">
         <v>19</v>
       </c>
       <c r="B22" s="54">
-        <v>3.0129999999999999</v>
+        <v>3.085</v>
       </c>
       <c r="C22" s="50"/>
       <c r="D22" s="44"/>
       <c r="E22" s="41"/>
       <c r="F22" s="47">
-        <v>68</v>
+        <v>13.16</v>
       </c>
       <c r="G22" s="25">
-        <f t="shared" si="0"/>
-        <v>68</v>
+        <f>SUM(C22:F22)</f>
+        <v>13.16</v>
       </c>
       <c r="K22">
-        <v>1</v>
+        <v>4.0999999999999996</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="10">
+      <c r="A23" s="108">
         <v>20</v>
       </c>
-      <c r="B23" s="54">
-        <v>3.0139999999999998</v>
+      <c r="B23" s="54" t="s">
+        <v>94</v>
       </c>
       <c r="C23" s="50"/>
       <c r="D23" s="44"/>
       <c r="E23" s="41"/>
       <c r="F23" s="47">
-        <v>148.61000000000001</v>
+        <v>140.80000000000001</v>
       </c>
       <c r="G23" s="25">
-        <f t="shared" si="0"/>
-        <v>148.61000000000001</v>
+        <f>SUM(C23:F23)</f>
+        <v>140.80000000000001</v>
       </c>
       <c r="K23">
-        <v>1</v>
+        <v>4.0999999999999996</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="10">
-        <v>21</v>
-      </c>
-      <c r="B24" s="8">
-        <v>3.0190000000000001</v>
-      </c>
-      <c r="C24" s="50"/>
-      <c r="D24" s="44"/>
-      <c r="E24" s="41"/>
+      <c r="A24" s="10"/>
+      <c r="B24" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" s="50">
+        <f>SUM(C4:C23)</f>
+        <v>28.689999999999998</v>
+      </c>
+      <c r="D24" s="44">
+        <f>SUM(D4:D23)</f>
+        <v>43.39</v>
+      </c>
+      <c r="E24" s="41">
+        <f>SUM(E4:E23)</f>
+        <v>25.92</v>
+      </c>
       <c r="F24" s="47">
-        <v>244.28</v>
+        <f>SUM(F4:F23)</f>
+        <v>1159.1500000000001</v>
       </c>
       <c r="G24" s="25">
-        <f t="shared" si="0"/>
-        <v>244.28</v>
-      </c>
-      <c r="K24">
-        <v>4.0999999999999996</v>
+        <f>SUM(G4:G23)</f>
+        <v>1257.1499999999999</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="10">
-        <v>22</v>
-      </c>
-      <c r="B25" s="54">
-        <v>3.02</v>
-      </c>
-      <c r="C25" s="50"/>
-      <c r="D25" s="44"/>
-      <c r="E25" s="41"/>
-      <c r="F25" s="47">
-        <v>137.72999999999999</v>
-      </c>
-      <c r="G25" s="25">
-        <f t="shared" si="0"/>
-        <v>137.72999999999999</v>
-      </c>
-      <c r="K25">
-        <v>4.0999999999999996</v>
+      <c r="B25" s="13"/>
+      <c r="H25">
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="10">
-        <v>23</v>
-      </c>
-      <c r="B26" s="54">
-        <v>3.085</v>
-      </c>
-      <c r="C26" s="50"/>
-      <c r="D26" s="44"/>
-      <c r="E26" s="41"/>
-      <c r="F26" s="47">
-        <v>13.16</v>
-      </c>
-      <c r="G26" s="25">
-        <f t="shared" si="0"/>
-        <v>13.16</v>
-      </c>
-      <c r="K26">
-        <v>4.0999999999999996</v>
+      <c r="I26">
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="10">
-        <v>24</v>
-      </c>
-      <c r="B27" s="54" t="s">
-        <v>94</v>
-      </c>
-      <c r="C27" s="50"/>
-      <c r="D27" s="44"/>
-      <c r="E27" s="41"/>
-      <c r="F27" s="47">
-        <v>140.80000000000001</v>
-      </c>
-      <c r="G27" s="25">
-        <f t="shared" si="0"/>
-        <v>140.80000000000001</v>
-      </c>
-      <c r="K27">
-        <v>4.0999999999999996</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="10"/>
-      <c r="B28" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="C28" s="50">
-        <f>SUM(C4:C27)</f>
-        <v>28.689999999999998</v>
-      </c>
-      <c r="D28" s="44">
-        <f>SUM(D4:D27)</f>
-        <v>43.39</v>
-      </c>
-      <c r="E28" s="41">
-        <f>SUM(E4:E27)</f>
-        <v>25.92</v>
-      </c>
-      <c r="F28" s="47">
-        <f>SUM(F4:F27)</f>
-        <v>1673.21</v>
-      </c>
-      <c r="G28" s="25">
-        <f>SUM(G4:G27)</f>
-        <v>1771.2100000000003</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B29" s="13"/>
-      <c r="H29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="I30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="J31">
+      <c r="J27">
         <v>0</v>
       </c>
     </row>
@@ -10340,6 +10431,357 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
+    <tabColor theme="0" tint="-0.14999847407452621"/>
+  </sheetPr>
+  <dimension ref="A1:K17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="7.5703125" customWidth="1"/>
+    <col min="2" max="2" width="50.28515625" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" customWidth="1"/>
+    <col min="6" max="6" width="8.85546875" customWidth="1"/>
+    <col min="7" max="9" width="0" hidden="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="92">
+        <v>1</v>
+      </c>
+      <c r="B1" s="93" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="94" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="92" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="95">
+        <v>1</v>
+      </c>
+      <c r="F1" s="96">
+        <v>46.62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="51.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="74">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="9"/>
+      <c r="D2" s="74" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" s="8">
+        <v>8</v>
+      </c>
+      <c r="F2" s="25">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="51.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="74">
+        <v>1.2</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="9"/>
+      <c r="D3" s="74" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="8">
+        <v>1.8</v>
+      </c>
+      <c r="F3" s="25">
+        <v>3356.64</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="39" x14ac:dyDescent="0.25">
+      <c r="A4" s="74">
+        <v>1.3</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="9"/>
+      <c r="D4" s="74" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F4" s="25">
+        <v>51.281999999999996</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="51.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="74">
+        <v>1.4</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="74" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" s="8">
+        <v>1</v>
+      </c>
+      <c r="F5" s="25">
+        <v>46.62</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" s="102" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="86">
+        <v>1</v>
+      </c>
+      <c r="B7" s="86">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="C7" s="86">
+        <v>2.081</v>
+      </c>
+      <c r="D7" s="86">
+        <v>11</v>
+      </c>
+      <c r="E7" s="86">
+        <v>298.27999999999997</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="A8" s="29">
+        <v>2</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="55" t="s">
+        <v>96</v>
+      </c>
+      <c r="D8" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="21">
+        <v>1</v>
+      </c>
+      <c r="F8" s="22">
+        <f>SUM(F14:F17)</f>
+        <v>514.05999999999995</v>
+      </c>
+      <c r="G8" s="23">
+        <v>5553.92</v>
+      </c>
+      <c r="I8" s="32">
+        <f t="shared" ref="I8:I12" si="0">F8-G8</f>
+        <v>-5039.8600000000006</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="108">
+        <v>2.1</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="9"/>
+      <c r="D9" s="108" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" s="8">
+        <v>8</v>
+      </c>
+      <c r="F9" s="25">
+        <f>ROUND(E9*F8, 0)</f>
+        <v>4112</v>
+      </c>
+      <c r="G9" s="16">
+        <v>44431.360000000001</v>
+      </c>
+      <c r="I9" s="32">
+        <f t="shared" si="0"/>
+        <v>-40319.360000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="108">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="B10" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="30"/>
+      <c r="D10" s="108" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="8">
+        <v>1.8</v>
+      </c>
+      <c r="F10" s="25">
+        <f>E10*F8*65</f>
+        <v>60145.01999999999</v>
+      </c>
+      <c r="G10" s="16">
+        <v>649808.64000000001</v>
+      </c>
+      <c r="H10">
+        <f>G10/G8/E10</f>
+        <v>65</v>
+      </c>
+      <c r="I10" s="32">
+        <f t="shared" si="0"/>
+        <v>-589663.62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="108">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="B11" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="30"/>
+      <c r="D11" s="108" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="F11" s="25">
+        <f>E11*F8</f>
+        <v>565.46600000000001</v>
+      </c>
+      <c r="G11" s="16">
+        <v>6109.3119999999999</v>
+      </c>
+      <c r="I11" s="32">
+        <f t="shared" si="0"/>
+        <v>-5543.8459999999995</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="108">
+        <v>2.4</v>
+      </c>
+      <c r="B12" s="30" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="30"/>
+      <c r="D12" s="108" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="8">
+        <v>1</v>
+      </c>
+      <c r="F12" s="25">
+        <f>E12*F8</f>
+        <v>514.05999999999995</v>
+      </c>
+      <c r="G12" s="16">
+        <v>5553.92</v>
+      </c>
+      <c r="I12" s="32">
+        <f t="shared" si="0"/>
+        <v>-5039.8600000000006</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="10">
+        <v>9</v>
+      </c>
+      <c r="B14" s="54">
+        <v>3.0009999999999999</v>
+      </c>
+      <c r="C14" s="50"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="47">
+        <v>129.68</v>
+      </c>
+      <c r="G14" s="25">
+        <f>SUM(C14:F14)</f>
+        <v>129.68</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="10">
+        <v>10</v>
+      </c>
+      <c r="B15" s="54">
+        <v>3.0019999999999998</v>
+      </c>
+      <c r="C15" s="50"/>
+      <c r="D15" s="44"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="47">
+        <v>73.05</v>
+      </c>
+      <c r="G15" s="25">
+        <f>SUM(C15:F15)</f>
+        <v>73.05</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="10">
+        <v>11</v>
+      </c>
+      <c r="B16" s="54">
+        <v>3.0030000000000001</v>
+      </c>
+      <c r="C16" s="50"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="47">
+        <v>71.709999999999994</v>
+      </c>
+      <c r="G16" s="25">
+        <f>SUM(C16:F16)</f>
+        <v>71.709999999999994</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="10">
+        <v>13</v>
+      </c>
+      <c r="B17" s="54">
+        <v>3.0049999999999999</v>
+      </c>
+      <c r="C17" s="50"/>
+      <c r="D17" s="44"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="47">
+        <v>239.62</v>
+      </c>
+      <c r="G17" s="25">
+        <f>SUM(C17:F17)</f>
+        <v>239.62</v>
+      </c>
+      <c r="K17">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
     <tabColor theme="4" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:F4"/>
@@ -10428,7 +10870,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="4" tint="0.79998168889431442"/>
@@ -10441,13 +10883,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="93" t="s">
+      <c r="A1" s="123" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="95"/>
+      <c r="B1" s="124"/>
+      <c r="C1" s="124"/>
+      <c r="D1" s="124"/>
+      <c r="E1" s="125"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="56" t="s">
@@ -10918,298 +11360,6 @@
       <c r="E29" s="60">
         <f>SUM(E3:E28)</f>
         <v>2263.66</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor theme="4" tint="0.79998168889431442"/>
-  </sheetPr>
-  <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="93" t="s">
-        <v>107</v>
-      </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="95"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="56" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="34" t="s">
-        <v>97</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="D2" s="34" t="s">
-        <v>93</v>
-      </c>
-      <c r="E2" s="59" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="56">
-        <v>1</v>
-      </c>
-      <c r="B3" s="34" t="s">
-        <v>99</v>
-      </c>
-      <c r="C3" s="64">
-        <v>2.0139999999999998</v>
-      </c>
-      <c r="D3" s="34" t="s">
-        <v>101</v>
-      </c>
-      <c r="E3" s="60">
-        <v>17.22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="56">
-        <v>2</v>
-      </c>
-      <c r="B4" s="34" t="s">
-        <v>99</v>
-      </c>
-      <c r="C4" s="64">
-        <v>2.0150000000000001</v>
-      </c>
-      <c r="D4" s="34" t="s">
-        <v>101</v>
-      </c>
-      <c r="E4" s="60">
-        <v>21.87</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="56">
-        <v>3</v>
-      </c>
-      <c r="B5" s="34" t="s">
-        <v>99</v>
-      </c>
-      <c r="C5" s="64">
-        <v>2.016</v>
-      </c>
-      <c r="D5" s="34" t="s">
-        <v>101</v>
-      </c>
-      <c r="E5" s="60">
-        <v>5.0599999999999996</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="56">
-        <v>4</v>
-      </c>
-      <c r="B6" s="34" t="s">
-        <v>100</v>
-      </c>
-      <c r="C6" s="54">
-        <v>2.089</v>
-      </c>
-      <c r="D6" s="34" t="s">
-        <v>101</v>
-      </c>
-      <c r="E6" s="60">
-        <v>6.05</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="56">
-        <v>5</v>
-      </c>
-      <c r="B7" s="34" t="s">
-        <v>100</v>
-      </c>
-      <c r="C7" s="54">
-        <v>2.09</v>
-      </c>
-      <c r="D7" s="34" t="s">
-        <v>101</v>
-      </c>
-      <c r="E7" s="60">
-        <v>12.15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="56">
-        <v>6</v>
-      </c>
-      <c r="B8" s="34" t="s">
-        <v>100</v>
-      </c>
-      <c r="C8" s="54">
-        <v>2.0910000000000002</v>
-      </c>
-      <c r="D8" s="34" t="s">
-        <v>101</v>
-      </c>
-      <c r="E8" s="60">
-        <v>10.63</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="56">
-        <v>7</v>
-      </c>
-      <c r="B9" s="34" t="s">
-        <v>100</v>
-      </c>
-      <c r="C9" s="54">
-        <v>2.0950000000000002</v>
-      </c>
-      <c r="D9" s="34" t="s">
-        <v>101</v>
-      </c>
-      <c r="E9" s="60">
-        <v>8.7899999999999991</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="56">
-        <v>8</v>
-      </c>
-      <c r="B10" s="34" t="s">
-        <v>100</v>
-      </c>
-      <c r="C10" s="54">
-        <v>2.0960000000000001</v>
-      </c>
-      <c r="D10" s="34" t="s">
-        <v>101</v>
-      </c>
-      <c r="E10" s="60">
-        <v>14.39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="56">
-        <v>9</v>
-      </c>
-      <c r="B11" s="34" t="s">
-        <v>100</v>
-      </c>
-      <c r="C11" s="54">
-        <v>2.1</v>
-      </c>
-      <c r="D11" s="34" t="s">
-        <v>101</v>
-      </c>
-      <c r="E11" s="60">
-        <v>8.19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="56">
-        <v>10</v>
-      </c>
-      <c r="B12" s="34" t="s">
-        <v>100</v>
-      </c>
-      <c r="C12" s="54">
-        <v>2.101</v>
-      </c>
-      <c r="D12" s="34" t="s">
-        <v>101</v>
-      </c>
-      <c r="E12" s="60">
-        <v>12.22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="56">
-        <v>11</v>
-      </c>
-      <c r="B13" s="34" t="s">
-        <v>100</v>
-      </c>
-      <c r="C13" s="54">
-        <v>2.1040000000000001</v>
-      </c>
-      <c r="D13" s="34" t="s">
-        <v>101</v>
-      </c>
-      <c r="E13" s="60">
-        <v>8.4499999999999993</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="56">
-        <v>12</v>
-      </c>
-      <c r="B14" s="34" t="s">
-        <v>100</v>
-      </c>
-      <c r="C14" s="54">
-        <v>2.105</v>
-      </c>
-      <c r="D14" s="34" t="s">
-        <v>101</v>
-      </c>
-      <c r="E14" s="60">
-        <v>14.25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="56">
-        <v>13</v>
-      </c>
-      <c r="B15" s="34" t="s">
-        <v>100</v>
-      </c>
-      <c r="C15" s="54">
-        <v>2.1070000000000002</v>
-      </c>
-      <c r="D15" s="34" t="s">
-        <v>101</v>
-      </c>
-      <c r="E15" s="71">
-        <v>8.14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="56">
-        <v>14</v>
-      </c>
-      <c r="B16" s="34" t="s">
-        <v>100</v>
-      </c>
-      <c r="C16" s="54">
-        <v>2.1080000000000001</v>
-      </c>
-      <c r="D16" s="34" t="s">
-        <v>101</v>
-      </c>
-      <c r="E16" s="71">
-        <v>16.28</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="56"/>
-      <c r="B17" s="34"/>
-      <c r="C17" s="54"/>
-      <c r="D17" s="34" t="s">
-        <v>52</v>
-      </c>
-      <c r="E17" s="72">
-        <f>SUM(E3:E16)</f>
-        <v>163.69000000000003</v>
       </c>
     </row>
   </sheetData>

--- a/school_lublino/vor_lublino_floors.xlsx
+++ b/school_lublino/vor_lublino_floors.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14190" windowHeight="6840" firstSheet="10" activeTab="15"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14190" windowHeight="6840" firstSheet="1" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="АА" sheetId="16" state="hidden" r:id="rId1"/>
@@ -20,8 +20,8 @@
     <sheet name="общий (2)" sheetId="5" state="hidden" r:id="rId6"/>
     <sheet name="не сделали" sheetId="21" r:id="rId7"/>
     <sheet name="ВорИзол" sheetId="10" r:id="rId8"/>
-    <sheet name="Из1эт" sheetId="8" state="hidden" r:id="rId9"/>
-    <sheet name="Из2эт" sheetId="9" state="hidden" r:id="rId10"/>
+    <sheet name="Из1эт" sheetId="8" r:id="rId9"/>
+    <sheet name="Из2эт" sheetId="9" r:id="rId10"/>
     <sheet name="ВорПленка" sheetId="12" r:id="rId11"/>
     <sheet name="Плк1э" sheetId="13" state="hidden" r:id="rId12"/>
     <sheet name="Плк2э" sheetId="14" state="hidden" r:id="rId13"/>
@@ -661,7 +661,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="130">
+  <cellXfs count="129">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -861,7 +861,6 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2077,13 +2076,13 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="123" t="s">
+      <c r="A1" s="122" t="s">
         <v>107</v>
       </c>
-      <c r="B1" s="124"/>
-      <c r="C1" s="124"/>
-      <c r="D1" s="124"/>
-      <c r="E1" s="125"/>
+      <c r="B1" s="123"/>
+      <c r="C1" s="123"/>
+      <c r="D1" s="123"/>
+      <c r="E1" s="124"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="56" t="s">
@@ -2116,7 +2115,7 @@
         <v>101</v>
       </c>
       <c r="E3" s="60">
-        <v>17.22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -2133,7 +2132,7 @@
         <v>101</v>
       </c>
       <c r="E4" s="60">
-        <v>21.87</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -2150,7 +2149,7 @@
         <v>101</v>
       </c>
       <c r="E5" s="60">
-        <v>5.0599999999999996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -2167,7 +2166,7 @@
         <v>101</v>
       </c>
       <c r="E6" s="60">
-        <v>6.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -2184,7 +2183,7 @@
         <v>101</v>
       </c>
       <c r="E7" s="60">
-        <v>12.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -2201,7 +2200,7 @@
         <v>101</v>
       </c>
       <c r="E8" s="60">
-        <v>10.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -2218,7 +2217,7 @@
         <v>101</v>
       </c>
       <c r="E9" s="60">
-        <v>8.7899999999999991</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -2235,7 +2234,7 @@
         <v>101</v>
       </c>
       <c r="E10" s="60">
-        <v>14.39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -2252,7 +2251,7 @@
         <v>101</v>
       </c>
       <c r="E11" s="60">
-        <v>8.19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -2269,7 +2268,7 @@
         <v>101</v>
       </c>
       <c r="E12" s="60">
-        <v>12.22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -2286,7 +2285,7 @@
         <v>101</v>
       </c>
       <c r="E13" s="60">
-        <v>8.4499999999999993</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -2303,7 +2302,7 @@
         <v>101</v>
       </c>
       <c r="E14" s="60">
-        <v>14.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -2319,8 +2318,8 @@
       <c r="D15" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="E15" s="71">
-        <v>8.14</v>
+      <c r="E15" s="60">
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -2336,8 +2335,8 @@
       <c r="D16" s="34" t="s">
         <v>101</v>
       </c>
-      <c r="E16" s="71">
-        <v>16.28</v>
+      <c r="E16" s="60">
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -2347,9 +2346,9 @@
       <c r="D17" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="E17" s="72">
+      <c r="E17" s="71">
         <f>SUM(E3:E16)</f>
-        <v>163.69000000000003</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2410,7 +2409,7 @@
       <c r="A3" s="67">
         <v>1</v>
       </c>
-      <c r="B3" s="73" t="s">
+      <c r="B3" s="72" t="s">
         <v>14</v>
       </c>
       <c r="C3" s="69" t="s">
@@ -2465,487 +2464,487 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="126" t="s">
+      <c r="A1" s="125" t="s">
         <v>110</v>
       </c>
-      <c r="B1" s="127"/>
-      <c r="C1" s="127"/>
-      <c r="D1" s="127"/>
-      <c r="E1" s="128"/>
+      <c r="B1" s="126"/>
+      <c r="C1" s="126"/>
+      <c r="D1" s="126"/>
+      <c r="E1" s="127"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="86" t="s">
+      <c r="A2" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="86" t="s">
+      <c r="B2" s="85" t="s">
         <v>97</v>
       </c>
-      <c r="C2" s="86" t="s">
+      <c r="C2" s="85" t="s">
         <v>98</v>
       </c>
-      <c r="D2" s="86" t="s">
+      <c r="D2" s="85" t="s">
         <v>93</v>
       </c>
-      <c r="E2" s="86" t="s">
+      <c r="E2" s="85" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="86">
-        <v>1</v>
-      </c>
-      <c r="B3" s="86">
-        <v>1</v>
-      </c>
-      <c r="C3" s="86">
+      <c r="A3" s="85">
+        <v>1</v>
+      </c>
+      <c r="B3" s="85">
+        <v>1</v>
+      </c>
+      <c r="C3" s="85">
         <v>1.024</v>
       </c>
-      <c r="D3" s="86">
+      <c r="D3" s="85">
         <v>6</v>
       </c>
-      <c r="E3" s="86">
+      <c r="E3" s="85">
         <v>13.62</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="86">
+      <c r="A4" s="85">
         <v>2</v>
       </c>
-      <c r="B4" s="86">
+      <c r="B4" s="85">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C4" s="86">
+      <c r="C4" s="85">
         <v>1.0449999999999999</v>
       </c>
-      <c r="D4" s="86">
+      <c r="D4" s="85">
         <v>6</v>
       </c>
-      <c r="E4" s="86">
+      <c r="E4" s="85">
         <v>161.78</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="86">
+      <c r="A5" s="85">
         <v>3</v>
       </c>
-      <c r="B5" s="86">
+      <c r="B5" s="85">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C5" s="86">
+      <c r="C5" s="85">
         <v>1.046</v>
       </c>
-      <c r="D5" s="86">
+      <c r="D5" s="85">
         <v>6</v>
       </c>
-      <c r="E5" s="86">
+      <c r="E5" s="85">
         <v>161.15</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="86">
+      <c r="A6" s="85">
         <v>4</v>
       </c>
-      <c r="B6" s="86">
+      <c r="B6" s="85">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C6" s="86">
+      <c r="C6" s="85">
         <v>1.0529999999999999</v>
       </c>
-      <c r="D6" s="86">
+      <c r="D6" s="85">
         <v>6</v>
       </c>
-      <c r="E6" s="86">
+      <c r="E6" s="85">
         <v>443.48</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="86">
+      <c r="A7" s="85">
         <v>5</v>
       </c>
-      <c r="B7" s="86">
-        <v>1</v>
-      </c>
-      <c r="C7" s="86">
+      <c r="B7" s="85">
+        <v>1</v>
+      </c>
+      <c r="C7" s="85">
         <v>1.034</v>
       </c>
-      <c r="D7" s="86">
+      <c r="D7" s="85">
         <v>7</v>
       </c>
-      <c r="E7" s="86">
+      <c r="E7" s="85">
         <v>17.22</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="86">
+      <c r="A8" s="85">
         <v>6</v>
       </c>
-      <c r="B8" s="86">
-        <v>1</v>
-      </c>
-      <c r="C8" s="86">
+      <c r="B8" s="85">
+        <v>1</v>
+      </c>
+      <c r="C8" s="85">
         <v>1.0349999999999999</v>
       </c>
-      <c r="D8" s="86">
+      <c r="D8" s="85">
         <v>7</v>
       </c>
-      <c r="E8" s="86">
+      <c r="E8" s="85">
         <v>21.63</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="86">
+      <c r="A9" s="85">
         <v>7</v>
       </c>
-      <c r="B9" s="86">
-        <v>1</v>
-      </c>
-      <c r="C9" s="86">
+      <c r="B9" s="85">
+        <v>1</v>
+      </c>
+      <c r="C9" s="85">
         <v>1.036</v>
       </c>
-      <c r="D9" s="86">
+      <c r="D9" s="85">
         <v>7</v>
       </c>
-      <c r="E9" s="86">
+      <c r="E9" s="85">
         <v>5.76</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="86">
+      <c r="A10" s="85">
         <v>8</v>
       </c>
-      <c r="B10" s="86">
+      <c r="B10" s="85">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C10" s="86">
+      <c r="C10" s="85">
         <v>1.054</v>
       </c>
-      <c r="D10" s="86">
+      <c r="D10" s="85">
         <v>7</v>
       </c>
-      <c r="E10" s="86">
+      <c r="E10" s="85">
         <v>14.54</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="86">
+      <c r="A11" s="85">
         <v>9</v>
       </c>
-      <c r="B11" s="86">
+      <c r="B11" s="85">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C11" s="86">
+      <c r="C11" s="85">
         <v>1.054</v>
       </c>
-      <c r="D11" s="86">
+      <c r="D11" s="85">
         <v>7.1</v>
       </c>
-      <c r="E11" s="86">
+      <c r="E11" s="85">
         <v>46.62</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="86">
+      <c r="A12" s="85">
         <v>10</v>
       </c>
-      <c r="B12" s="86">
+      <c r="B12" s="85">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C12" s="86">
+      <c r="C12" s="85">
         <v>1.048</v>
       </c>
-      <c r="D12" s="86">
+      <c r="D12" s="85">
         <v>8.1</v>
       </c>
-      <c r="E12" s="86">
+      <c r="E12" s="85">
         <v>23.92</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="86">
+      <c r="A13" s="85">
         <v>11</v>
       </c>
-      <c r="B13" s="86">
-        <v>1</v>
-      </c>
-      <c r="C13" s="86">
+      <c r="B13" s="85">
+        <v>1</v>
+      </c>
+      <c r="C13" s="85">
         <v>1.0369999999999999</v>
       </c>
-      <c r="D13" s="86">
+      <c r="D13" s="85">
         <v>8.1999999999999993</v>
       </c>
-      <c r="E13" s="86">
+      <c r="E13" s="85">
         <v>3.34</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="86">
+      <c r="A14" s="85">
         <v>12</v>
       </c>
-      <c r="B14" s="86">
-        <v>1</v>
-      </c>
-      <c r="C14" s="86">
+      <c r="B14" s="85">
+        <v>1</v>
+      </c>
+      <c r="C14" s="85">
         <v>1.038</v>
       </c>
-      <c r="D14" s="86">
+      <c r="D14" s="85">
         <v>8.1999999999999993</v>
       </c>
-      <c r="E14" s="86">
+      <c r="E14" s="85">
         <v>5.25</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="86">
+      <c r="A15" s="85">
         <v>13</v>
       </c>
-      <c r="B15" s="86">
-        <v>1</v>
-      </c>
-      <c r="C15" s="86">
+      <c r="B15" s="85">
+        <v>1</v>
+      </c>
+      <c r="C15" s="85">
         <v>1.026</v>
       </c>
-      <c r="D15" s="86">
+      <c r="D15" s="85">
         <v>9</v>
       </c>
-      <c r="E15" s="86">
+      <c r="E15" s="85">
         <v>191.68</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="86">
+      <c r="A16" s="85">
         <v>14</v>
       </c>
-      <c r="B16" s="86">
-        <v>1</v>
-      </c>
-      <c r="C16" s="86">
+      <c r="B16" s="85">
+        <v>1</v>
+      </c>
+      <c r="C16" s="85">
         <v>1.0269999999999999</v>
       </c>
-      <c r="D16" s="86">
+      <c r="D16" s="85">
         <v>9</v>
       </c>
-      <c r="E16" s="86">
+      <c r="E16" s="85">
         <v>114.04</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="86">
+      <c r="A17" s="85">
         <v>15</v>
       </c>
-      <c r="B17" s="86">
-        <v>1</v>
-      </c>
-      <c r="C17" s="86">
+      <c r="B17" s="85">
+        <v>1</v>
+      </c>
+      <c r="C17" s="85">
         <v>1.028</v>
       </c>
-      <c r="D17" s="86">
+      <c r="D17" s="85">
         <v>9</v>
       </c>
-      <c r="E17" s="86">
+      <c r="E17" s="85">
         <v>68.81</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="86">
+      <c r="A18" s="85">
         <v>16</v>
       </c>
-      <c r="B18" s="86">
-        <v>1</v>
-      </c>
-      <c r="C18" s="86">
+      <c r="B18" s="85">
+        <v>1</v>
+      </c>
+      <c r="C18" s="85">
         <v>1.0289999999999999</v>
       </c>
-      <c r="D18" s="86">
+      <c r="D18" s="85">
         <v>9</v>
       </c>
-      <c r="E18" s="86">
+      <c r="E18" s="85">
         <v>68.81</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="86">
+      <c r="A19" s="85">
         <v>17</v>
       </c>
-      <c r="B19" s="86">
-        <v>1</v>
-      </c>
-      <c r="C19" s="86">
+      <c r="B19" s="85">
+        <v>1</v>
+      </c>
+      <c r="C19" s="85">
         <v>1.03</v>
       </c>
-      <c r="D19" s="86">
+      <c r="D19" s="85">
         <v>9</v>
       </c>
-      <c r="E19" s="86">
+      <c r="E19" s="85">
         <v>68.89</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="86">
+      <c r="A20" s="85">
         <v>18</v>
       </c>
-      <c r="B20" s="86">
-        <v>1</v>
-      </c>
-      <c r="C20" s="86">
+      <c r="B20" s="85">
+        <v>1</v>
+      </c>
+      <c r="C20" s="85">
         <v>1.0309999999999999</v>
       </c>
-      <c r="D20" s="86">
+      <c r="D20" s="85">
         <v>9</v>
       </c>
-      <c r="E20" s="86">
+      <c r="E20" s="85">
         <v>68.89</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="86">
+      <c r="A21" s="85">
         <v>19</v>
       </c>
-      <c r="B21" s="86">
-        <v>1</v>
-      </c>
-      <c r="C21" s="86">
+      <c r="B21" s="85">
+        <v>1</v>
+      </c>
+      <c r="C21" s="85">
         <v>1.032</v>
       </c>
-      <c r="D21" s="86">
+      <c r="D21" s="85">
         <v>9</v>
       </c>
-      <c r="E21" s="86">
+      <c r="E21" s="85">
         <v>68.069999999999993</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="86">
+      <c r="A22" s="85">
         <v>20</v>
       </c>
-      <c r="B22" s="86">
-        <v>1</v>
-      </c>
-      <c r="C22" s="86">
+      <c r="B22" s="85">
+        <v>1</v>
+      </c>
+      <c r="C22" s="85">
         <v>1.0329999999999999</v>
       </c>
-      <c r="D22" s="86">
+      <c r="D22" s="85">
         <v>9</v>
       </c>
-      <c r="E22" s="86">
+      <c r="E22" s="85">
         <v>139.1</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="86">
+      <c r="A23" s="85">
         <v>21</v>
       </c>
-      <c r="B23" s="86">
-        <v>1</v>
-      </c>
-      <c r="C23" s="86">
+      <c r="B23" s="85">
+        <v>1</v>
+      </c>
+      <c r="C23" s="85">
         <v>1.0389999999999999</v>
       </c>
-      <c r="D23" s="86">
+      <c r="D23" s="85">
         <v>9</v>
       </c>
-      <c r="E23" s="86">
+      <c r="E23" s="85">
         <v>149.69999999999999</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="86">
+      <c r="A24" s="85">
         <v>22</v>
       </c>
-      <c r="B24" s="86">
+      <c r="B24" s="85">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C24" s="86">
+      <c r="C24" s="85">
         <v>1.04</v>
       </c>
-      <c r="D24" s="86">
+      <c r="D24" s="85">
         <v>9</v>
       </c>
-      <c r="E24" s="86">
+      <c r="E24" s="85">
         <v>220.47</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="86">
+      <c r="A25" s="85">
         <v>23</v>
       </c>
-      <c r="B25" s="86">
+      <c r="B25" s="85">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C25" s="86">
+      <c r="C25" s="85">
         <v>1.0429999999999999</v>
       </c>
-      <c r="D25" s="86">
+      <c r="D25" s="85">
         <v>9</v>
       </c>
-      <c r="E25" s="86">
+      <c r="E25" s="85">
         <v>61.99</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="86">
+      <c r="A26" s="85">
         <v>24</v>
       </c>
-      <c r="B26" s="86">
+      <c r="B26" s="85">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C26" s="86">
+      <c r="C26" s="85">
         <v>1.044</v>
       </c>
-      <c r="D26" s="86">
+      <c r="D26" s="85">
         <v>9</v>
       </c>
-      <c r="E26" s="86">
+      <c r="E26" s="85">
         <v>14.14</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="86">
+      <c r="A27" s="85">
         <v>25</v>
       </c>
-      <c r="B27" s="86">
+      <c r="B27" s="85">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C27" s="86">
+      <c r="C27" s="85">
         <v>1.0489999999999999</v>
       </c>
-      <c r="D27" s="86">
+      <c r="D27" s="85">
         <v>9</v>
       </c>
-      <c r="E27" s="86">
+      <c r="E27" s="85">
         <v>103.8</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="86">
+      <c r="A28" s="85">
         <v>26</v>
       </c>
-      <c r="B28" s="86">
+      <c r="B28" s="85">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C28" s="86">
+      <c r="C28" s="85">
         <v>1.05</v>
       </c>
-      <c r="D28" s="86">
+      <c r="D28" s="85">
         <v>9</v>
       </c>
-      <c r="E28" s="86">
+      <c r="E28" s="85">
         <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="86">
+      <c r="A29" s="85">
         <v>27</v>
       </c>
-      <c r="B29" s="86">
+      <c r="B29" s="85">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C29" s="86">
+      <c r="C29" s="85">
         <v>1.0509999999999999</v>
       </c>
-      <c r="D29" s="86">
+      <c r="D29" s="85">
         <v>9</v>
       </c>
-      <c r="E29" s="86">
+      <c r="E29" s="85">
         <v>31.58</v>
       </c>
     </row>
@@ -2956,7 +2955,7 @@
       <c r="D30" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="E30" s="72">
+      <c r="E30" s="71">
         <f>SUM(E1:E29)</f>
         <v>2310.2799999999997</v>
       </c>
@@ -2984,368 +2983,368 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="126" t="s">
+      <c r="A1" s="125" t="s">
         <v>111</v>
       </c>
-      <c r="B1" s="127"/>
-      <c r="C1" s="127"/>
-      <c r="D1" s="127"/>
-      <c r="E1" s="128"/>
+      <c r="B1" s="126"/>
+      <c r="C1" s="126"/>
+      <c r="D1" s="126"/>
+      <c r="E1" s="127"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="86" t="s">
+      <c r="A2" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="86" t="s">
+      <c r="B2" s="85" t="s">
         <v>97</v>
       </c>
-      <c r="C2" s="86" t="s">
+      <c r="C2" s="85" t="s">
         <v>98</v>
       </c>
-      <c r="D2" s="86" t="s">
+      <c r="D2" s="85" t="s">
         <v>93</v>
       </c>
-      <c r="E2" s="86" t="s">
+      <c r="E2" s="85" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="86">
-        <v>1</v>
-      </c>
-      <c r="B3" s="86">
+      <c r="A3" s="85">
+        <v>1</v>
+      </c>
+      <c r="B3" s="85">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C3" s="89">
+      <c r="C3" s="88">
         <v>2.16</v>
       </c>
-      <c r="D3" s="86">
+      <c r="D3" s="85">
         <v>4.4000000000000004</v>
       </c>
-      <c r="E3" s="86">
+      <c r="E3" s="85">
         <v>72.64</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="86">
+      <c r="A4" s="85">
         <v>2</v>
       </c>
-      <c r="B4" s="86">
-        <v>1</v>
-      </c>
-      <c r="C4" s="89">
+      <c r="B4" s="85">
+        <v>1</v>
+      </c>
+      <c r="C4" s="88">
         <v>2.0049999999999999</v>
       </c>
-      <c r="D4" s="86">
+      <c r="D4" s="85">
         <v>6.1</v>
       </c>
-      <c r="E4" s="86">
+      <c r="E4" s="85">
         <v>13.62</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="86">
+      <c r="A5" s="85">
         <v>3</v>
       </c>
-      <c r="B5" s="86">
+      <c r="B5" s="85">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C5" s="89">
+      <c r="C5" s="88">
         <v>2.0840000000000001</v>
       </c>
-      <c r="D5" s="86">
+      <c r="D5" s="85">
         <v>6.1</v>
       </c>
-      <c r="E5" s="88">
+      <c r="E5" s="87">
         <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="86">
+      <c r="A6" s="85">
         <v>4</v>
       </c>
-      <c r="B6" s="86">
+      <c r="B6" s="85">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C6" s="89">
+      <c r="C6" s="88">
         <v>2.0870000000000002</v>
       </c>
-      <c r="D6" s="86">
+      <c r="D6" s="85">
         <v>6.1</v>
       </c>
-      <c r="E6" s="86">
+      <c r="E6" s="85">
         <v>19.46</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="86">
+      <c r="A7" s="85">
         <v>5</v>
       </c>
-      <c r="B7" s="86">
+      <c r="B7" s="85">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C7" s="89">
+      <c r="C7" s="88">
         <v>2.109</v>
       </c>
-      <c r="D7" s="86">
+      <c r="D7" s="85">
         <v>6.1</v>
       </c>
-      <c r="E7" s="86">
+      <c r="E7" s="85">
         <v>33.049999999999997</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="86">
+      <c r="A8" s="85">
         <v>6</v>
       </c>
-      <c r="B8" s="86">
+      <c r="B8" s="85">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C8" s="89">
+      <c r="C8" s="88">
         <v>2.1680000000000001</v>
       </c>
-      <c r="D8" s="86">
+      <c r="D8" s="85">
         <v>6.1</v>
       </c>
-      <c r="E8" s="86">
+      <c r="E8" s="85">
         <v>8.02</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="86">
+      <c r="A9" s="85">
         <v>7</v>
       </c>
-      <c r="B9" s="86">
-        <v>1</v>
-      </c>
-      <c r="C9" s="89">
+      <c r="B9" s="85">
+        <v>1</v>
+      </c>
+      <c r="C9" s="88">
         <v>2.0139999999999998</v>
       </c>
-      <c r="D9" s="86">
+      <c r="D9" s="85">
         <v>7.2</v>
       </c>
-      <c r="E9" s="86">
+      <c r="E9" s="85">
         <v>17.22</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="86">
+      <c r="A10" s="85">
         <v>8</v>
       </c>
-      <c r="B10" s="86">
-        <v>1</v>
-      </c>
-      <c r="C10" s="89">
+      <c r="B10" s="85">
+        <v>1</v>
+      </c>
+      <c r="C10" s="88">
         <v>2.0150000000000001</v>
       </c>
-      <c r="D10" s="86">
+      <c r="D10" s="85">
         <v>7.2</v>
       </c>
-      <c r="E10" s="86">
+      <c r="E10" s="85">
         <v>21.87</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="86">
+      <c r="A11" s="85">
         <v>9</v>
       </c>
-      <c r="B11" s="86">
-        <v>1</v>
-      </c>
-      <c r="C11" s="89">
+      <c r="B11" s="85">
+        <v>1</v>
+      </c>
+      <c r="C11" s="88">
         <v>2.016</v>
       </c>
-      <c r="D11" s="86">
+      <c r="D11" s="85">
         <v>7.2</v>
       </c>
-      <c r="E11" s="86">
+      <c r="E11" s="85">
         <v>5.0599999999999996</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="86">
+      <c r="A12" s="85">
         <v>10</v>
       </c>
-      <c r="B12" s="86">
+      <c r="B12" s="85">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C12" s="89">
+      <c r="C12" s="88">
         <v>2.089</v>
       </c>
-      <c r="D12" s="86">
+      <c r="D12" s="85">
         <v>7.2</v>
       </c>
-      <c r="E12" s="86">
+      <c r="E12" s="85">
         <v>6.05</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="86">
+      <c r="A13" s="85">
         <v>11</v>
       </c>
-      <c r="B13" s="86">
+      <c r="B13" s="85">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C13" s="89">
+      <c r="C13" s="88">
         <v>2.09</v>
       </c>
-      <c r="D13" s="86">
+      <c r="D13" s="85">
         <v>7.2</v>
       </c>
-      <c r="E13" s="86">
+      <c r="E13" s="85">
         <v>12.15</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="86">
+      <c r="A14" s="85">
         <v>12</v>
       </c>
-      <c r="B14" s="86">
+      <c r="B14" s="85">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C14" s="89">
+      <c r="C14" s="88">
         <v>2.0910000000000002</v>
       </c>
-      <c r="D14" s="86">
+      <c r="D14" s="85">
         <v>7.2</v>
       </c>
-      <c r="E14" s="86">
+      <c r="E14" s="85">
         <v>10.63</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="86">
+      <c r="A15" s="85">
         <v>13</v>
       </c>
-      <c r="B15" s="86">
+      <c r="B15" s="85">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C15" s="89">
+      <c r="C15" s="88">
         <v>2.0950000000000002</v>
       </c>
-      <c r="D15" s="86">
+      <c r="D15" s="85">
         <v>7.2</v>
       </c>
-      <c r="E15" s="86">
+      <c r="E15" s="85">
         <v>8.7899999999999991</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="86">
+      <c r="A16" s="85">
         <v>14</v>
       </c>
-      <c r="B16" s="86">
+      <c r="B16" s="85">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C16" s="89">
+      <c r="C16" s="88">
         <v>2.0960000000000001</v>
       </c>
-      <c r="D16" s="86">
+      <c r="D16" s="85">
         <v>7.2</v>
       </c>
-      <c r="E16" s="86">
+      <c r="E16" s="85">
         <v>14.39</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="86">
+      <c r="A17" s="85">
         <v>15</v>
       </c>
-      <c r="B17" s="86">
+      <c r="B17" s="85">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C17" s="89">
+      <c r="C17" s="88">
         <v>2.1</v>
       </c>
-      <c r="D17" s="86">
+      <c r="D17" s="85">
         <v>7.2</v>
       </c>
-      <c r="E17" s="86">
+      <c r="E17" s="85">
         <v>8.19</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="86">
+      <c r="A18" s="85">
         <v>16</v>
       </c>
-      <c r="B18" s="86">
+      <c r="B18" s="85">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C18" s="89">
+      <c r="C18" s="88">
         <v>2.101</v>
       </c>
-      <c r="D18" s="86">
+      <c r="D18" s="85">
         <v>7.2</v>
       </c>
-      <c r="E18" s="86">
+      <c r="E18" s="85">
         <v>12.22</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="86">
+      <c r="A19" s="85">
         <v>17</v>
       </c>
-      <c r="B19" s="86">
+      <c r="B19" s="85">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C19" s="89">
+      <c r="C19" s="88">
         <v>2.1040000000000001</v>
       </c>
-      <c r="D19" s="86">
+      <c r="D19" s="85">
         <v>7.2</v>
       </c>
-      <c r="E19" s="86">
+      <c r="E19" s="85">
         <v>8.4499999999999993</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="86">
+      <c r="A20" s="85">
         <v>18</v>
       </c>
-      <c r="B20" s="86">
+      <c r="B20" s="85">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C20" s="89">
+      <c r="C20" s="88">
         <v>2.105</v>
       </c>
-      <c r="D20" s="86">
+      <c r="D20" s="85">
         <v>7.2</v>
       </c>
-      <c r="E20" s="86">
+      <c r="E20" s="85">
         <v>14.25</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="86">
+      <c r="A21" s="85">
         <v>19</v>
       </c>
-      <c r="B21" s="86">
+      <c r="B21" s="85">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C21" s="89">
+      <c r="C21" s="88">
         <v>2.1070000000000002</v>
       </c>
-      <c r="D21" s="86">
+      <c r="D21" s="85">
         <v>7.2</v>
       </c>
-      <c r="E21" s="86">
+      <c r="E21" s="85">
         <v>8.14</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="86">
+      <c r="A22" s="85">
         <v>20</v>
       </c>
-      <c r="B22" s="86">
+      <c r="B22" s="85">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C22" s="89">
+      <c r="C22" s="88">
         <v>2.1080000000000001</v>
       </c>
-      <c r="D22" s="86">
+      <c r="D22" s="85">
         <v>7.2</v>
       </c>
-      <c r="E22" s="86">
+      <c r="E22" s="85">
         <v>16.28</v>
       </c>
     </row>
@@ -3356,7 +3355,7 @@
       <c r="D23" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="E23" s="72">
+      <c r="E23" s="71">
         <f>SUM(E3:E22)</f>
         <v>326.48</v>
       </c>
@@ -3382,28 +3381,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="123" t="s">
+      <c r="A1" s="122" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="124"/>
-      <c r="C1" s="124"/>
-      <c r="D1" s="124"/>
-      <c r="E1" s="125"/>
+      <c r="B1" s="123"/>
+      <c r="C1" s="123"/>
+      <c r="D1" s="123"/>
+      <c r="E1" s="124"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="77" t="s">
+      <c r="A2" s="76" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="65" t="s">
         <v>97</v>
       </c>
-      <c r="C2" s="78" t="s">
+      <c r="C2" s="77" t="s">
         <v>98</v>
       </c>
       <c r="D2" s="65" t="s">
         <v>93</v>
       </c>
-      <c r="E2" s="79" t="s">
+      <c r="E2" s="78" t="s">
         <v>51</v>
       </c>
     </row>
@@ -3420,7 +3419,7 @@
       <c r="D3" s="64">
         <v>6.1</v>
       </c>
-      <c r="E3" s="76">
+      <c r="E3" s="75">
         <v>13.62</v>
       </c>
     </row>
@@ -3437,7 +3436,7 @@
       <c r="D4" s="64">
         <v>6.1</v>
       </c>
-      <c r="E4" s="76">
+      <c r="E4" s="75">
         <v>15.07</v>
       </c>
     </row>
@@ -3454,7 +3453,7 @@
       <c r="D5" s="64">
         <v>7.2</v>
       </c>
-      <c r="E5" s="76">
+      <c r="E5" s="75">
         <v>17.21</v>
       </c>
     </row>
@@ -3471,7 +3470,7 @@
       <c r="D6" s="64">
         <v>7.2</v>
       </c>
-      <c r="E6" s="76">
+      <c r="E6" s="75">
         <v>21.12</v>
       </c>
     </row>
@@ -3488,7 +3487,7 @@
       <c r="D7" s="64">
         <v>7.2</v>
       </c>
-      <c r="E7" s="76">
+      <c r="E7" s="75">
         <v>5.0599999999999996</v>
       </c>
     </row>
@@ -3499,7 +3498,7 @@
       <c r="D8" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="E8" s="72">
+      <c r="E8" s="71">
         <f>SUM(E3:E7)</f>
         <v>72.08</v>
       </c>
@@ -3525,28 +3524,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="123" t="s">
+      <c r="A1" s="122" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="124"/>
-      <c r="C1" s="124"/>
-      <c r="D1" s="124"/>
-      <c r="E1" s="125"/>
+      <c r="B1" s="123"/>
+      <c r="C1" s="123"/>
+      <c r="D1" s="123"/>
+      <c r="E1" s="124"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="77" t="s">
+      <c r="A2" s="76" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="65" t="s">
         <v>97</v>
       </c>
-      <c r="C2" s="78" t="s">
+      <c r="C2" s="77" t="s">
         <v>98</v>
       </c>
       <c r="D2" s="65" t="s">
         <v>93</v>
       </c>
-      <c r="E2" s="85" t="s">
+      <c r="E2" s="84" t="s">
         <v>51</v>
       </c>
     </row>
@@ -3563,7 +3562,7 @@
       <c r="D3" s="64">
         <v>6</v>
       </c>
-      <c r="E3" s="76">
+      <c r="E3" s="75">
         <v>13.62</v>
       </c>
     </row>
@@ -3580,7 +3579,7 @@
       <c r="D4" s="64">
         <v>6</v>
       </c>
-      <c r="E4" s="76">
+      <c r="E4" s="75">
         <v>161.78</v>
       </c>
     </row>
@@ -3597,7 +3596,7 @@
       <c r="D5" s="64">
         <v>6</v>
       </c>
-      <c r="E5" s="76">
+      <c r="E5" s="75">
         <v>161.15</v>
       </c>
       <c r="G5">
@@ -3618,7 +3617,7 @@
       <c r="D6" s="64">
         <v>6</v>
       </c>
-      <c r="E6" s="76">
+      <c r="E6" s="75">
         <v>443.48</v>
       </c>
       <c r="G6" t="e">
@@ -3639,7 +3638,7 @@
       <c r="D7" s="64">
         <v>7</v>
       </c>
-      <c r="E7" s="76">
+      <c r="E7" s="75">
         <v>17.22</v>
       </c>
       <c r="G7" t="e">
@@ -3660,7 +3659,7 @@
       <c r="D8" s="64">
         <v>7</v>
       </c>
-      <c r="E8" s="76">
+      <c r="E8" s="75">
         <v>21.63</v>
       </c>
       <c r="G8" t="e">
@@ -3681,7 +3680,7 @@
       <c r="D9" s="64">
         <v>7</v>
       </c>
-      <c r="E9" s="76">
+      <c r="E9" s="75">
         <v>5.76</v>
       </c>
       <c r="G9" t="e">
@@ -3702,7 +3701,7 @@
       <c r="D10" s="64">
         <v>7</v>
       </c>
-      <c r="E10" s="76">
+      <c r="E10" s="75">
         <v>14.54</v>
       </c>
       <c r="G10" t="e">
@@ -3723,7 +3722,7 @@
       <c r="D11" s="64">
         <v>7.1</v>
       </c>
-      <c r="E11" s="76">
+      <c r="E11" s="75">
         <v>46.62</v>
       </c>
       <c r="G11" t="e">
@@ -3744,7 +3743,7 @@
       <c r="D12" s="64">
         <v>8.1</v>
       </c>
-      <c r="E12" s="76">
+      <c r="E12" s="75">
         <v>23.92</v>
       </c>
       <c r="G12" t="e">
@@ -3765,7 +3764,7 @@
       <c r="D13" s="64">
         <v>8.1999999999999993</v>
       </c>
-      <c r="E13" s="76">
+      <c r="E13" s="75">
         <v>3.34</v>
       </c>
       <c r="G13" t="e">
@@ -3786,7 +3785,7 @@
       <c r="D14" s="64">
         <v>8.1999999999999993</v>
       </c>
-      <c r="E14" s="76">
+      <c r="E14" s="75">
         <v>5.25</v>
       </c>
       <c r="G14" t="e">
@@ -3807,7 +3806,7 @@
       <c r="D15" s="64">
         <v>9</v>
       </c>
-      <c r="E15" s="76">
+      <c r="E15" s="75">
         <v>191.68</v>
       </c>
       <c r="G15" t="e">
@@ -3828,7 +3827,7 @@
       <c r="D16" s="64">
         <v>9</v>
       </c>
-      <c r="E16" s="76">
+      <c r="E16" s="75">
         <v>114.04</v>
       </c>
       <c r="G16" t="e">
@@ -3849,7 +3848,7 @@
       <c r="D17" s="64">
         <v>9</v>
       </c>
-      <c r="E17" s="76">
+      <c r="E17" s="75">
         <v>68.81</v>
       </c>
       <c r="G17" t="e">
@@ -3870,7 +3869,7 @@
       <c r="D18" s="64">
         <v>9</v>
       </c>
-      <c r="E18" s="76">
+      <c r="E18" s="75">
         <v>68.81</v>
       </c>
       <c r="G18" t="e">
@@ -3891,7 +3890,7 @@
       <c r="D19" s="64">
         <v>9</v>
       </c>
-      <c r="E19" s="76">
+      <c r="E19" s="75">
         <v>68.89</v>
       </c>
     </row>
@@ -3908,7 +3907,7 @@
       <c r="D20" s="64">
         <v>9</v>
       </c>
-      <c r="E20" s="76">
+      <c r="E20" s="75">
         <v>68.89</v>
       </c>
     </row>
@@ -3925,7 +3924,7 @@
       <c r="D21" s="64">
         <v>9</v>
       </c>
-      <c r="E21" s="76">
+      <c r="E21" s="75">
         <v>68.069999999999993</v>
       </c>
     </row>
@@ -3942,7 +3941,7 @@
       <c r="D22" s="64">
         <v>9</v>
       </c>
-      <c r="E22" s="76">
+      <c r="E22" s="75">
         <v>139.1</v>
       </c>
     </row>
@@ -3959,7 +3958,7 @@
       <c r="D23" s="64">
         <v>9</v>
       </c>
-      <c r="E23" s="76">
+      <c r="E23" s="75">
         <v>149.69999999999999</v>
       </c>
     </row>
@@ -3976,7 +3975,7 @@
       <c r="D24" s="64">
         <v>9</v>
       </c>
-      <c r="E24" s="76">
+      <c r="E24" s="75">
         <v>220.47</v>
       </c>
     </row>
@@ -3993,7 +3992,7 @@
       <c r="D25" s="64">
         <v>9</v>
       </c>
-      <c r="E25" s="76">
+      <c r="E25" s="75">
         <v>61.99</v>
       </c>
     </row>
@@ -4010,7 +4009,7 @@
       <c r="D26" s="64">
         <v>9</v>
       </c>
-      <c r="E26" s="76">
+      <c r="E26" s="75">
         <v>14.14</v>
       </c>
     </row>
@@ -4027,7 +4026,7 @@
       <c r="D27" s="64">
         <v>9</v>
       </c>
-      <c r="E27" s="76">
+      <c r="E27" s="75">
         <v>103.8</v>
       </c>
     </row>
@@ -4044,24 +4043,24 @@
       <c r="D28" s="64">
         <v>9</v>
       </c>
-      <c r="E28" s="76">
+      <c r="E28" s="75">
         <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="80">
+      <c r="A29" s="79">
         <v>27</v>
       </c>
-      <c r="B29" s="81">
+      <c r="B29" s="80">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C29" s="82">
+      <c r="C29" s="81">
         <v>1.0509999999999999</v>
       </c>
-      <c r="D29" s="81">
+      <c r="D29" s="80">
         <v>9</v>
       </c>
-      <c r="E29" s="83">
+      <c r="E29" s="82">
         <v>31.58</v>
       </c>
     </row>
@@ -4082,19 +4081,19 @@
       <c r="E31" s="60"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="77" t="s">
+      <c r="A32" s="76" t="s">
         <v>0</v>
       </c>
       <c r="B32" s="65" t="s">
         <v>97</v>
       </c>
-      <c r="C32" s="78" t="s">
+      <c r="C32" s="77" t="s">
         <v>98</v>
       </c>
       <c r="D32" s="65" t="s">
         <v>93</v>
       </c>
-      <c r="E32" s="79" t="s">
+      <c r="E32" s="78" t="s">
         <v>51</v>
       </c>
     </row>
@@ -4111,7 +4110,7 @@
       <c r="D33" s="64">
         <v>4.4000000000000004</v>
       </c>
-      <c r="E33" s="76">
+      <c r="E33" s="75">
         <v>72.64</v>
       </c>
     </row>
@@ -4128,7 +4127,7 @@
       <c r="D34" s="64">
         <v>6.1</v>
       </c>
-      <c r="E34" s="76">
+      <c r="E34" s="75">
         <v>13.62</v>
       </c>
       <c r="G34">
@@ -4148,7 +4147,7 @@
       <c r="D35" s="64">
         <v>6.1</v>
       </c>
-      <c r="E35" s="76">
+      <c r="E35" s="75">
         <v>16</v>
       </c>
       <c r="G35">
@@ -4156,7 +4155,7 @@
       </c>
     </row>
     <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="90">
+      <c r="A36" s="89">
         <v>4</v>
       </c>
       <c r="B36" s="64">
@@ -4168,7 +4167,7 @@
       <c r="D36" s="64">
         <v>6.1</v>
       </c>
-      <c r="E36" s="76">
+      <c r="E36" s="75">
         <v>19.46</v>
       </c>
       <c r="G36">
@@ -4188,7 +4187,7 @@
       <c r="D37" s="64">
         <v>6.1</v>
       </c>
-      <c r="E37" s="76">
+      <c r="E37" s="75">
         <v>33.049999999999997</v>
       </c>
       <c r="G37">
@@ -4208,7 +4207,7 @@
       <c r="D38" s="64">
         <v>6.1</v>
       </c>
-      <c r="E38" s="76">
+      <c r="E38" s="75">
         <v>8.02</v>
       </c>
     </row>
@@ -4225,7 +4224,7 @@
       <c r="D39" s="64">
         <v>7.2</v>
       </c>
-      <c r="E39" s="76">
+      <c r="E39" s="75">
         <v>17.22</v>
       </c>
       <c r="G39">
@@ -4245,7 +4244,7 @@
       <c r="D40" s="64">
         <v>7.2</v>
       </c>
-      <c r="E40" s="76">
+      <c r="E40" s="75">
         <v>21.87</v>
       </c>
       <c r="G40">
@@ -4265,7 +4264,7 @@
       <c r="D41" s="64">
         <v>7.2</v>
       </c>
-      <c r="E41" s="76">
+      <c r="E41" s="75">
         <v>5.0599999999999996</v>
       </c>
       <c r="G41">
@@ -4285,7 +4284,7 @@
       <c r="D42" s="64">
         <v>7.2</v>
       </c>
-      <c r="E42" s="76">
+      <c r="E42" s="75">
         <v>6.05</v>
       </c>
       <c r="G42">
@@ -4305,7 +4304,7 @@
       <c r="D43" s="64">
         <v>7.2</v>
       </c>
-      <c r="E43" s="76">
+      <c r="E43" s="75">
         <v>12.15</v>
       </c>
       <c r="G43">
@@ -4325,7 +4324,7 @@
       <c r="D44" s="64">
         <v>7.2</v>
       </c>
-      <c r="E44" s="76">
+      <c r="E44" s="75">
         <v>10.63</v>
       </c>
       <c r="G44">
@@ -4345,7 +4344,7 @@
       <c r="D45" s="64">
         <v>7.2</v>
       </c>
-      <c r="E45" s="76">
+      <c r="E45" s="75">
         <v>8.7899999999999991</v>
       </c>
       <c r="G45">
@@ -4365,7 +4364,7 @@
       <c r="D46" s="64">
         <v>7.2</v>
       </c>
-      <c r="E46" s="76">
+      <c r="E46" s="75">
         <v>14.39</v>
       </c>
     </row>
@@ -4382,7 +4381,7 @@
       <c r="D47" s="64">
         <v>7.2</v>
       </c>
-      <c r="E47" s="76">
+      <c r="E47" s="75">
         <v>8.19</v>
       </c>
     </row>
@@ -4399,7 +4398,7 @@
       <c r="D48" s="64">
         <v>7.2</v>
       </c>
-      <c r="E48" s="76">
+      <c r="E48" s="75">
         <v>12.22</v>
       </c>
     </row>
@@ -4416,7 +4415,7 @@
       <c r="D49" s="64">
         <v>7.2</v>
       </c>
-      <c r="E49" s="76">
+      <c r="E49" s="75">
         <v>8.4499999999999993</v>
       </c>
       <c r="G49">
@@ -4436,7 +4435,7 @@
       <c r="D50" s="64">
         <v>7.2</v>
       </c>
-      <c r="E50" s="76">
+      <c r="E50" s="75">
         <v>14.25</v>
       </c>
       <c r="G50">
@@ -4456,29 +4455,29 @@
       <c r="D51" s="64">
         <v>7.2</v>
       </c>
-      <c r="E51" s="84">
+      <c r="E51" s="83">
         <v>8.14</v>
       </c>
     </row>
     <row r="52" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="80">
+      <c r="A52" s="79">
         <v>20</v>
       </c>
-      <c r="B52" s="81">
+      <c r="B52" s="80">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C52" s="82">
+      <c r="C52" s="81">
         <v>2.1080000000000001</v>
       </c>
-      <c r="D52" s="81">
+      <c r="D52" s="80">
         <v>7.2</v>
       </c>
-      <c r="E52" s="87">
+      <c r="E52" s="86">
         <v>16.28</v>
       </c>
     </row>
     <row r="53" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="75">
+      <c r="A53" s="74">
         <v>21</v>
       </c>
       <c r="B53" s="64">
@@ -4490,12 +4489,12 @@
       <c r="D53" s="64">
         <v>8.3000000000000007</v>
       </c>
-      <c r="E53" s="76">
+      <c r="E53" s="75">
         <v>3.22</v>
       </c>
     </row>
     <row r="54" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="75">
+      <c r="A54" s="74">
         <v>22</v>
       </c>
       <c r="B54" s="64">
@@ -4507,12 +4506,12 @@
       <c r="D54" s="64">
         <v>8.3000000000000007</v>
       </c>
-      <c r="E54" s="76">
+      <c r="E54" s="75">
         <v>5.25</v>
       </c>
     </row>
     <row r="55" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="75">
+      <c r="A55" s="74">
         <v>23</v>
       </c>
       <c r="B55" s="64">
@@ -4524,12 +4523,12 @@
       <c r="D55" s="64">
         <v>8.3000000000000007</v>
       </c>
-      <c r="E55" s="76">
+      <c r="E55" s="75">
         <v>4.8499999999999996</v>
       </c>
     </row>
     <row r="56" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="75">
+      <c r="A56" s="74">
         <v>24</v>
       </c>
       <c r="B56" s="64">
@@ -4541,12 +4540,12 @@
       <c r="D56" s="64">
         <v>8.3000000000000007</v>
       </c>
-      <c r="E56" s="76">
+      <c r="E56" s="75">
         <v>4.76</v>
       </c>
     </row>
     <row r="57" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="75">
+      <c r="A57" s="74">
         <v>25</v>
       </c>
       <c r="B57" s="64">
@@ -4558,12 +4557,12 @@
       <c r="D57" s="64">
         <v>8.3000000000000007</v>
       </c>
-      <c r="E57" s="76">
+      <c r="E57" s="75">
         <v>9.24</v>
       </c>
     </row>
     <row r="58" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="75">
+      <c r="A58" s="74">
         <v>34</v>
       </c>
       <c r="B58" s="64">
@@ -4575,7 +4574,7 @@
       <c r="D58" s="64">
         <v>9.1999999999999993</v>
       </c>
-      <c r="E58" s="76">
+      <c r="E58" s="75">
         <v>73.55</v>
       </c>
       <c r="G58">
@@ -4583,7 +4582,7 @@
       </c>
     </row>
     <row r="59" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="75">
+      <c r="A59" s="74">
         <v>33</v>
       </c>
       <c r="B59" s="64">
@@ -4595,12 +4594,12 @@
       <c r="D59" s="64">
         <v>9.1999999999999993</v>
       </c>
-      <c r="E59" s="76">
+      <c r="E59" s="75">
         <v>72.239999999999995</v>
       </c>
     </row>
     <row r="60" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="75">
+      <c r="A60" s="74">
         <v>27</v>
       </c>
       <c r="B60" s="64">
@@ -4612,12 +4611,12 @@
       <c r="D60" s="64">
         <v>9.1999999999999993</v>
       </c>
-      <c r="E60" s="76">
+      <c r="E60" s="75">
         <v>68.260000000000005</v>
       </c>
     </row>
     <row r="61" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="75">
+      <c r="A61" s="74">
         <v>36</v>
       </c>
       <c r="B61" s="64">
@@ -4629,12 +4628,12 @@
       <c r="D61" s="64">
         <v>9.1999999999999993</v>
       </c>
-      <c r="E61" s="76">
+      <c r="E61" s="75">
         <v>158.71</v>
       </c>
     </row>
     <row r="62" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="75">
+      <c r="A62" s="74">
         <v>30</v>
       </c>
       <c r="B62" s="64">
@@ -4646,7 +4645,7 @@
       <c r="D62" s="64">
         <v>9.1999999999999993</v>
       </c>
-      <c r="E62" s="76">
+      <c r="E62" s="75">
         <v>68.3</v>
       </c>
       <c r="G62" t="s">
@@ -4657,7 +4656,7 @@
       </c>
     </row>
     <row r="63" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="75">
+      <c r="A63" s="74">
         <v>32</v>
       </c>
       <c r="B63" s="64">
@@ -4669,7 +4668,7 @@
       <c r="D63" s="64">
         <v>9.1999999999999993</v>
       </c>
-      <c r="E63" s="76">
+      <c r="E63" s="75">
         <v>68.459999999999994</v>
       </c>
       <c r="G63">
@@ -4678,7 +4677,7 @@
       </c>
     </row>
     <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="75">
+      <c r="A64" s="74">
         <v>31</v>
       </c>
       <c r="B64" s="64">
@@ -4690,7 +4689,7 @@
       <c r="D64" s="64">
         <v>9.1999999999999993</v>
       </c>
-      <c r="E64" s="76">
+      <c r="E64" s="75">
         <v>68.459999999999994</v>
       </c>
       <c r="G64">
@@ -4699,7 +4698,7 @@
       </c>
     </row>
     <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="75">
+      <c r="A65" s="74">
         <v>26</v>
       </c>
       <c r="B65" s="64">
@@ -4711,7 +4710,7 @@
       <c r="D65" s="64">
         <v>9.1999999999999993</v>
       </c>
-      <c r="E65" s="76">
+      <c r="E65" s="75">
         <v>67.64</v>
       </c>
       <c r="G65" t="e">
@@ -4723,7 +4722,7 @@
       </c>
     </row>
     <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="75">
+      <c r="A66" s="74">
         <v>28</v>
       </c>
       <c r="B66" s="64">
@@ -4735,7 +4734,7 @@
       <c r="D66" s="64">
         <v>9.1999999999999993</v>
       </c>
-      <c r="E66" s="76">
+      <c r="E66" s="75">
         <v>68.459999999999994</v>
       </c>
       <c r="G66" t="e">
@@ -4744,7 +4743,7 @@
       </c>
     </row>
     <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="75">
+      <c r="A67" s="74">
         <v>35</v>
       </c>
       <c r="B67" s="64">
@@ -4756,7 +4755,7 @@
       <c r="D67" s="64">
         <v>9.1999999999999993</v>
       </c>
-      <c r="E67" s="76">
+      <c r="E67" s="75">
         <v>149.25</v>
       </c>
       <c r="G67" t="e">
@@ -4765,7 +4764,7 @@
       </c>
     </row>
     <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="75">
+      <c r="A68" s="74">
         <v>29</v>
       </c>
       <c r="B68" s="64">
@@ -4777,7 +4776,7 @@
       <c r="D68" s="64">
         <v>9.1999999999999993</v>
       </c>
-      <c r="E68" s="76">
+      <c r="E68" s="75">
         <v>68.459999999999994</v>
       </c>
       <c r="G68" t="e">
@@ -4789,7 +4788,7 @@
       </c>
     </row>
     <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="75">
+      <c r="A69" s="74">
         <v>42</v>
       </c>
       <c r="B69" s="64">
@@ -4801,7 +4800,7 @@
       <c r="D69" s="64">
         <v>9.1999999999999993</v>
       </c>
-      <c r="E69" s="76">
+      <c r="E69" s="75">
         <v>79.790000000000006</v>
       </c>
       <c r="G69" t="e">
@@ -4810,7 +4809,7 @@
       </c>
     </row>
     <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="75">
+      <c r="A70" s="74">
         <v>43</v>
       </c>
       <c r="B70" s="64">
@@ -4822,7 +4821,7 @@
       <c r="D70" s="64">
         <v>9.1999999999999993</v>
       </c>
-      <c r="E70" s="76">
+      <c r="E70" s="75">
         <v>170.56</v>
       </c>
       <c r="G70" t="e">
@@ -4831,7 +4830,7 @@
       </c>
     </row>
     <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="75">
+      <c r="A71" s="74">
         <v>37</v>
       </c>
       <c r="B71" s="64">
@@ -4843,7 +4842,7 @@
       <c r="D71" s="64">
         <v>9.1999999999999993</v>
       </c>
-      <c r="E71" s="76">
+      <c r="E71" s="75">
         <v>10.24</v>
       </c>
       <c r="G71" t="e">
@@ -4855,7 +4854,7 @@
       </c>
     </row>
     <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="75">
+      <c r="A72" s="74">
         <v>41</v>
       </c>
       <c r="B72" s="64">
@@ -4867,7 +4866,7 @@
       <c r="D72" s="64">
         <v>9.1999999999999993</v>
       </c>
-      <c r="E72" s="76">
+      <c r="E72" s="75">
         <v>23.36</v>
       </c>
       <c r="G72" t="e">
@@ -4876,7 +4875,7 @@
       </c>
     </row>
     <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="90">
+      <c r="A73" s="89">
         <v>40</v>
       </c>
       <c r="B73" s="64">
@@ -4888,7 +4887,7 @@
       <c r="D73" s="64">
         <v>9.1999999999999993</v>
       </c>
-      <c r="E73" s="76">
+      <c r="E73" s="75">
         <v>21.09</v>
       </c>
       <c r="G73" t="e">
@@ -4897,7 +4896,7 @@
       </c>
     </row>
     <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="75">
+      <c r="A74" s="74">
         <v>39</v>
       </c>
       <c r="B74" s="64">
@@ -4909,7 +4908,7 @@
       <c r="D74" s="64">
         <v>9.1999999999999993</v>
       </c>
-      <c r="E74" s="76">
+      <c r="E74" s="75">
         <v>19.329999999999998</v>
       </c>
       <c r="G74" t="e">
@@ -4918,7 +4917,7 @@
       </c>
     </row>
     <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="75">
+      <c r="A75" s="74">
         <v>38</v>
       </c>
       <c r="B75" s="64">
@@ -4930,7 +4929,7 @@
       <c r="D75" s="64">
         <v>9.1999999999999993</v>
       </c>
-      <c r="E75" s="76">
+      <c r="E75" s="75">
         <v>19.36</v>
       </c>
       <c r="G75" t="e">
@@ -4939,7 +4938,7 @@
       </c>
     </row>
     <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="75">
+      <c r="A76" s="74">
         <v>44</v>
       </c>
       <c r="B76" s="64">
@@ -4951,7 +4950,7 @@
       <c r="D76" s="64">
         <v>11</v>
       </c>
-      <c r="E76" s="76">
+      <c r="E76" s="75">
         <v>298.27999999999997</v>
       </c>
       <c r="G76" t="e">
@@ -4963,19 +4962,19 @@
       </c>
     </row>
     <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="75">
+      <c r="A77" s="74">
         <v>45</v>
       </c>
-      <c r="B77" s="81">
+      <c r="B77" s="80">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C77" s="82">
+      <c r="C77" s="81">
         <v>2.085</v>
       </c>
-      <c r="D77" s="81">
+      <c r="D77" s="80">
         <v>11.1</v>
       </c>
-      <c r="E77" s="83">
+      <c r="E77" s="82">
         <v>168.62</v>
       </c>
       <c r="G77" t="e">
@@ -4987,7 +4986,7 @@
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A78" s="74"/>
+      <c r="A78" s="73"/>
       <c r="B78" s="34"/>
       <c r="C78" s="54"/>
       <c r="D78" s="34"/>
@@ -5017,19 +5016,19 @@
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A81" s="77" t="s">
+      <c r="A81" s="76" t="s">
         <v>0</v>
       </c>
       <c r="B81" s="65" t="s">
         <v>97</v>
       </c>
-      <c r="C81" s="78" t="s">
+      <c r="C81" s="77" t="s">
         <v>98</v>
       </c>
       <c r="D81" s="65" t="s">
         <v>93</v>
       </c>
-      <c r="E81" s="79" t="s">
+      <c r="E81" s="78" t="s">
         <v>51</v>
       </c>
     </row>
@@ -5046,7 +5045,7 @@
       <c r="D82" s="64">
         <v>6.1</v>
       </c>
-      <c r="E82" s="76">
+      <c r="E82" s="75">
         <v>13.62</v>
       </c>
       <c r="I82">
@@ -5066,7 +5065,7 @@
       <c r="D83" s="64">
         <v>6.1</v>
       </c>
-      <c r="E83" s="76">
+      <c r="E83" s="75">
         <v>15.07</v>
       </c>
       <c r="I83">
@@ -5086,7 +5085,7 @@
       <c r="D84" s="64">
         <v>7.2</v>
       </c>
-      <c r="E84" s="76">
+      <c r="E84" s="75">
         <v>17.21</v>
       </c>
       <c r="I84">
@@ -5106,7 +5105,7 @@
       <c r="D85" s="64">
         <v>7.2</v>
       </c>
-      <c r="E85" s="76">
+      <c r="E85" s="75">
         <v>21.12</v>
       </c>
       <c r="I85">
@@ -5126,7 +5125,7 @@
       <c r="D86" s="64">
         <v>7.2</v>
       </c>
-      <c r="E86" s="76">
+      <c r="E86" s="75">
         <v>5.0599999999999996</v>
       </c>
       <c r="I86">
@@ -5146,7 +5145,7 @@
       <c r="D87" s="64">
         <v>9.1999999999999993</v>
       </c>
-      <c r="E87" s="76">
+      <c r="E87" s="75">
         <v>129.68</v>
       </c>
       <c r="I87">
@@ -5166,7 +5165,7 @@
       <c r="D88" s="64">
         <v>9.1999999999999993</v>
       </c>
-      <c r="E88" s="76">
+      <c r="E88" s="75">
         <v>73.05</v>
       </c>
       <c r="I88">
@@ -5186,7 +5185,7 @@
       <c r="D89" s="64">
         <v>9.1999999999999993</v>
       </c>
-      <c r="E89" s="76">
+      <c r="E89" s="75">
         <v>71.709999999999994</v>
       </c>
       <c r="I89">
@@ -5206,7 +5205,7 @@
       <c r="D90" s="64">
         <v>9.1999999999999993</v>
       </c>
-      <c r="E90" s="76">
+      <c r="E90" s="75">
         <v>67.59</v>
       </c>
       <c r="I90">
@@ -5226,7 +5225,7 @@
       <c r="D91" s="64">
         <v>9.1999999999999993</v>
       </c>
-      <c r="E91" s="76">
+      <c r="E91" s="75">
         <v>239.62</v>
       </c>
       <c r="I91">
@@ -5246,7 +5245,7 @@
       <c r="D92" s="64">
         <v>9.1999999999999993</v>
       </c>
-      <c r="E92" s="76">
+      <c r="E92" s="75">
         <v>67.84</v>
       </c>
       <c r="I92">
@@ -5266,7 +5265,7 @@
       <c r="D93" s="64">
         <v>9.1999999999999993</v>
       </c>
-      <c r="E93" s="76">
+      <c r="E93" s="75">
         <v>68</v>
       </c>
       <c r="I93">
@@ -5286,7 +5285,7 @@
       <c r="D94" s="64">
         <v>9.1999999999999993</v>
       </c>
-      <c r="E94" s="76">
+      <c r="E94" s="75">
         <v>68</v>
       </c>
       <c r="I94">
@@ -5306,7 +5305,7 @@
       <c r="D95" s="64">
         <v>9.1999999999999993</v>
       </c>
-      <c r="E95" s="76">
+      <c r="E95" s="75">
         <v>67.14</v>
       </c>
       <c r="I95">
@@ -5326,7 +5325,7 @@
       <c r="D96" s="64">
         <v>9.1999999999999993</v>
       </c>
-      <c r="E96" s="76">
+      <c r="E96" s="75">
         <v>68</v>
       </c>
       <c r="I96">
@@ -5346,7 +5345,7 @@
       <c r="D97" s="64">
         <v>9.1999999999999993</v>
       </c>
-      <c r="E97" s="76">
+      <c r="E97" s="75">
         <v>68</v>
       </c>
       <c r="I97">
@@ -5366,7 +5365,7 @@
       <c r="D98" s="64">
         <v>8.3000000000000007</v>
       </c>
-      <c r="E98" s="76">
+      <c r="E98" s="75">
         <v>3.2</v>
       </c>
       <c r="I98">
@@ -5386,7 +5385,7 @@
       <c r="D99" s="64">
         <v>9.1999999999999993</v>
       </c>
-      <c r="E99" s="76">
+      <c r="E99" s="75">
         <v>148.61000000000001</v>
       </c>
       <c r="I99">
@@ -5406,7 +5405,7 @@
       <c r="D100" s="64">
         <v>9.1999999999999993</v>
       </c>
-      <c r="E100" s="76">
+      <c r="E100" s="75">
         <v>244.28</v>
       </c>
       <c r="I100">
@@ -5426,7 +5425,7 @@
       <c r="D101" s="64">
         <v>8.3000000000000007</v>
       </c>
-      <c r="E101" s="76">
+      <c r="E101" s="75">
         <v>15.62</v>
       </c>
       <c r="I101">
@@ -5446,7 +5445,7 @@
       <c r="D102" s="64">
         <v>9.1999999999999993</v>
       </c>
-      <c r="E102" s="76">
+      <c r="E102" s="75">
         <v>137.72999999999999</v>
       </c>
       <c r="I102">
@@ -5466,7 +5465,7 @@
       <c r="D103" s="64">
         <v>8.3000000000000007</v>
       </c>
-      <c r="E103" s="76">
+      <c r="E103" s="75">
         <v>5.24</v>
       </c>
     </row>
@@ -5483,24 +5482,24 @@
       <c r="D104" s="64">
         <v>9.1999999999999993</v>
       </c>
-      <c r="E104" s="76">
+      <c r="E104" s="75">
         <v>13.16</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A105" s="80">
+      <c r="A105" s="79">
         <v>24</v>
       </c>
-      <c r="B105" s="81">
+      <c r="B105" s="80">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C105" s="82" t="s">
+      <c r="C105" s="81" t="s">
         <v>94</v>
       </c>
-      <c r="D105" s="81">
+      <c r="D105" s="80">
         <v>9.1999999999999993</v>
       </c>
-      <c r="E105" s="83">
+      <c r="E105" s="82">
         <v>140.80000000000001</v>
       </c>
     </row>
@@ -5705,19 +5704,19 @@
       </c>
     </row>
     <row r="3" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="97">
-        <v>1</v>
-      </c>
-      <c r="B3" s="98" t="s">
+      <c r="A3" s="96">
+        <v>1</v>
+      </c>
+      <c r="B3" s="97" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="99" t="s">
+      <c r="C3" s="98" t="s">
         <v>116</v>
       </c>
-      <c r="D3" s="97" t="s">
+      <c r="D3" s="96" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="100">
+      <c r="E3" s="99">
         <v>1</v>
       </c>
       <c r="F3" s="50">
@@ -5726,14 +5725,14 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="74">
+      <c r="A4" s="73">
         <v>1.1000000000000001</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>22</v>
       </c>
       <c r="C4" s="9"/>
-      <c r="D4" s="74" t="s">
+      <c r="D4" s="73" t="s">
         <v>41</v>
       </c>
       <c r="E4" s="8">
@@ -5745,14 +5744,14 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="74">
+      <c r="A5" s="73">
         <v>1.2</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>23</v>
       </c>
       <c r="C5" s="9"/>
-      <c r="D5" s="74" t="s">
+      <c r="D5" s="73" t="s">
         <v>6</v>
       </c>
       <c r="E5" s="8">
@@ -5764,14 +5763,14 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="108">
+      <c r="A6" s="107">
         <v>1.3</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>24</v>
       </c>
       <c r="C6" s="9"/>
-      <c r="D6" s="74" t="s">
+      <c r="D6" s="73" t="s">
         <v>7</v>
       </c>
       <c r="E6" s="8">
@@ -5783,14 +5782,14 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="108">
+      <c r="A7" s="107">
         <v>1.4</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="9"/>
-      <c r="D7" s="74" t="s">
+      <c r="D7" s="73" t="s">
         <v>5</v>
       </c>
       <c r="E7" s="8">
@@ -5802,35 +5801,35 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A8" s="103">
+      <c r="A8" s="102">
         <v>2</v>
       </c>
-      <c r="B8" s="104" t="s">
+      <c r="B8" s="103" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="105" t="s">
+      <c r="C8" s="104" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="103" t="s">
+      <c r="D8" s="102" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="106">
-        <v>1</v>
-      </c>
-      <c r="F8" s="107">
+      <c r="E8" s="105">
+        <v>1</v>
+      </c>
+      <c r="F8" s="106">
         <f>'1эт'!E41</f>
         <v>2263.66</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="74">
+      <c r="A9" s="73">
         <v>2.1</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>22</v>
       </c>
       <c r="C9" s="9"/>
-      <c r="D9" s="74" t="s">
+      <c r="D9" s="73" t="s">
         <v>41</v>
       </c>
       <c r="E9" s="8">
@@ -5842,14 +5841,14 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="74">
+      <c r="A10" s="73">
         <v>2.2000000000000002</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>23</v>
       </c>
       <c r="C10" s="9"/>
-      <c r="D10" s="74" t="s">
+      <c r="D10" s="73" t="s">
         <v>6</v>
       </c>
       <c r="E10" s="8">
@@ -5861,14 +5860,14 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="108">
+      <c r="A11" s="107">
         <v>2.2999999999999998</v>
       </c>
       <c r="B11" s="9" t="s">
         <v>24</v>
       </c>
       <c r="C11" s="9"/>
-      <c r="D11" s="74" t="s">
+      <c r="D11" s="73" t="s">
         <v>7</v>
       </c>
       <c r="E11" s="8">
@@ -5880,14 +5879,14 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="108">
+      <c r="A12" s="107">
         <v>2.4</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C12" s="9"/>
-      <c r="D12" s="74" t="s">
+      <c r="D12" s="73" t="s">
         <v>5</v>
       </c>
       <c r="E12" s="8">
@@ -5899,19 +5898,19 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="109">
+      <c r="A13" s="108">
         <v>3</v>
       </c>
-      <c r="B13" s="110" t="s">
+      <c r="B13" s="109" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="111" t="s">
+      <c r="C13" s="110" t="s">
         <v>44</v>
       </c>
-      <c r="D13" s="109" t="s">
+      <c r="D13" s="108" t="s">
         <v>7</v>
       </c>
-      <c r="E13" s="112">
+      <c r="E13" s="111">
         <v>1</v>
       </c>
       <c r="F13" s="44">
@@ -5920,14 +5919,14 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="74">
+      <c r="A14" s="73">
         <v>3.1</v>
       </c>
       <c r="B14" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="9"/>
-      <c r="D14" s="74" t="s">
+      <c r="D14" s="73" t="s">
         <v>6</v>
       </c>
       <c r="E14" s="8">
@@ -5939,14 +5938,14 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="74">
+      <c r="A15" s="73">
         <v>3.2</v>
       </c>
       <c r="B15" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C15" s="9"/>
-      <c r="D15" s="74" t="s">
+      <c r="D15" s="73" t="s">
         <v>5</v>
       </c>
       <c r="E15" s="8">
@@ -5958,14 +5957,14 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="108">
+      <c r="A16" s="107">
         <v>3.3</v>
       </c>
       <c r="B16" s="9" t="s">
         <v>24</v>
       </c>
       <c r="C16" s="9"/>
-      <c r="D16" s="74" t="s">
+      <c r="D16" s="73" t="s">
         <v>7</v>
       </c>
       <c r="E16" s="8">
@@ -5977,14 +5976,14 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="108">
+      <c r="A17" s="107">
         <v>3.4</v>
       </c>
       <c r="B17" s="9" t="s">
         <v>23</v>
       </c>
       <c r="C17" s="9"/>
-      <c r="D17" s="74" t="s">
+      <c r="D17" s="73" t="s">
         <v>6</v>
       </c>
       <c r="E17" s="8">
@@ -5996,13 +5995,13 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="108">
+      <c r="A18" s="107">
         <v>3.5</v>
       </c>
-      <c r="B18" s="73" t="s">
+      <c r="B18" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="91"/>
+      <c r="C18" s="90"/>
       <c r="D18" s="67" t="s">
         <v>41</v>
       </c>
@@ -6015,35 +6014,35 @@
       </c>
     </row>
     <row r="19" spans="1:6" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A19" s="117">
+      <c r="A19" s="116">
         <v>4</v>
       </c>
-      <c r="B19" s="118" t="s">
+      <c r="B19" s="117" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="118" t="s">
+      <c r="C19" s="117" t="s">
         <v>45</v>
       </c>
-      <c r="D19" s="117" t="s">
+      <c r="D19" s="116" t="s">
         <v>7</v>
       </c>
-      <c r="E19" s="119">
-        <v>1</v>
-      </c>
-      <c r="F19" s="120">
+      <c r="E19" s="118">
+        <v>1</v>
+      </c>
+      <c r="F19" s="119">
         <f>'1эт'!E11</f>
         <v>19.420000000000002</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="74">
+      <c r="A20" s="73">
         <v>4.0999999999999996</v>
       </c>
       <c r="B20" s="9" t="s">
         <v>22</v>
       </c>
       <c r="C20" s="9"/>
-      <c r="D20" s="74" t="s">
+      <c r="D20" s="73" t="s">
         <v>41</v>
       </c>
       <c r="E20" s="8">
@@ -6055,14 +6054,14 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="74">
+      <c r="A21" s="73">
         <v>4.2</v>
       </c>
       <c r="B21" s="9" t="s">
         <v>27</v>
       </c>
       <c r="C21" s="9"/>
-      <c r="D21" s="74" t="s">
+      <c r="D21" s="73" t="s">
         <v>6</v>
       </c>
       <c r="E21" s="8">
@@ -6074,14 +6073,14 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="108">
+      <c r="A22" s="107">
         <v>4.3</v>
       </c>
       <c r="B22" s="9" t="s">
         <v>28</v>
       </c>
       <c r="C22" s="9"/>
-      <c r="D22" s="74" t="s">
+      <c r="D22" s="73" t="s">
         <v>7</v>
       </c>
       <c r="E22" s="8">
@@ -6093,14 +6092,14 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="108">
+      <c r="A23" s="107">
         <v>4.4000000000000004</v>
       </c>
       <c r="B23" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C23" s="9"/>
-      <c r="D23" s="74" t="s">
+      <c r="D23" s="73" t="s">
         <v>5</v>
       </c>
       <c r="E23" s="8">
@@ -6112,35 +6111,35 @@
       </c>
     </row>
     <row r="24" spans="1:6" ht="26.25" x14ac:dyDescent="0.25">
-      <c r="A24" s="113">
+      <c r="A24" s="112">
         <v>5</v>
       </c>
-      <c r="B24" s="114" t="s">
+      <c r="B24" s="113" t="s">
         <v>26</v>
       </c>
-      <c r="C24" s="114" t="s">
+      <c r="C24" s="113" t="s">
         <v>46</v>
       </c>
-      <c r="D24" s="113" t="s">
+      <c r="D24" s="112" t="s">
         <v>7</v>
       </c>
-      <c r="E24" s="115">
-        <v>1</v>
-      </c>
-      <c r="F24" s="116">
+      <c r="E24" s="114">
+        <v>1</v>
+      </c>
+      <c r="F24" s="115">
         <f>'2эт'!E12+'3эт'!E10</f>
-        <v>100.99</v>
+        <v>101.29</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="74">
+      <c r="A25" s="73">
         <v>5.0999999999999996</v>
       </c>
       <c r="B25" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C25" s="9"/>
-      <c r="D25" s="74" t="s">
+      <c r="D25" s="73" t="s">
         <v>5</v>
       </c>
       <c r="E25" s="8">
@@ -6148,18 +6147,18 @@
       </c>
       <c r="F25" s="25">
         <f>F24*E25</f>
-        <v>100.99</v>
+        <v>101.29</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="74">
+      <c r="A26" s="73">
         <v>5.2</v>
       </c>
       <c r="B26" s="9" t="s">
         <v>28</v>
       </c>
       <c r="C26" s="9"/>
-      <c r="D26" s="74" t="s">
+      <c r="D26" s="73" t="s">
         <v>7</v>
       </c>
       <c r="E26" s="8">
@@ -6167,18 +6166,18 @@
       </c>
       <c r="F26" s="25">
         <f>E26*F24</f>
-        <v>111.089</v>
+        <v>111.41900000000001</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="108">
+      <c r="A27" s="107">
         <v>5.3</v>
       </c>
       <c r="B27" s="9" t="s">
         <v>27</v>
       </c>
       <c r="C27" s="9"/>
-      <c r="D27" s="74" t="s">
+      <c r="D27" s="73" t="s">
         <v>6</v>
       </c>
       <c r="E27" s="8">
@@ -6186,18 +6185,18 @@
       </c>
       <c r="F27" s="25">
         <f>E27*F24*80</f>
-        <v>14542.559999999998</v>
+        <v>14585.76</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="108">
+      <c r="A28" s="107">
         <v>5.4</v>
       </c>
       <c r="B28" s="9" t="s">
         <v>22</v>
       </c>
       <c r="C28" s="9"/>
-      <c r="D28" s="74" t="s">
+      <c r="D28" s="73" t="s">
         <v>41</v>
       </c>
       <c r="E28" s="8">
@@ -6205,7 +6204,7 @@
       </c>
       <c r="F28" s="25">
         <f>ROUNDDOWN(E28*F24,0)</f>
-        <v>807</v>
+        <v>810</v>
       </c>
     </row>
   </sheetData>
@@ -6221,624 +6220,624 @@
   <dimension ref="A1:E41"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="102"/>
+    <col min="1" max="16384" width="9.140625" style="101"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" s="126" t="s">
+      <c r="A1" s="125" t="s">
         <v>110</v>
       </c>
-      <c r="B1" s="127"/>
-      <c r="C1" s="127"/>
-      <c r="D1" s="127"/>
-      <c r="E1" s="128"/>
+      <c r="B1" s="126"/>
+      <c r="C1" s="126"/>
+      <c r="D1" s="126"/>
+      <c r="E1" s="127"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="86" t="s">
+      <c r="A2" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="86" t="s">
+      <c r="B2" s="85" t="s">
         <v>97</v>
       </c>
-      <c r="C2" s="86" t="s">
+      <c r="C2" s="85" t="s">
         <v>98</v>
       </c>
-      <c r="D2" s="86" t="s">
+      <c r="D2" s="85" t="s">
         <v>93</v>
       </c>
-      <c r="E2" s="86" t="s">
+      <c r="E2" s="85" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="86">
-        <v>1</v>
-      </c>
-      <c r="B3" s="86">
-        <v>1</v>
-      </c>
-      <c r="C3" s="86" t="s">
+      <c r="A3" s="85">
+        <v>1</v>
+      </c>
+      <c r="B3" s="85">
+        <v>1</v>
+      </c>
+      <c r="C3" s="85" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="86">
+      <c r="D3" s="85">
         <v>9.1</v>
       </c>
-      <c r="E3" s="101">
+      <c r="E3" s="100">
         <f>37.5-2.48</f>
         <v>35.020000000000003</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="86">
+      <c r="A4" s="85">
         <v>2</v>
       </c>
-      <c r="B4" s="86">
+      <c r="B4" s="85">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C4" s="86" t="s">
+      <c r="C4" s="85" t="s">
         <v>113</v>
       </c>
-      <c r="D4" s="86">
+      <c r="D4" s="85">
         <v>9.1</v>
       </c>
-      <c r="E4" s="101">
+      <c r="E4" s="100">
         <v>4.2</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D5" s="102" t="s">
+      <c r="D5" s="101" t="s">
         <v>114</v>
       </c>
-      <c r="E5" s="102">
+      <c r="E5" s="101">
         <f>SUM(E3:E4)</f>
         <v>39.220000000000006</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="126" t="s">
+      <c r="A7" s="125" t="s">
         <v>110</v>
       </c>
-      <c r="B7" s="127"/>
-      <c r="C7" s="127"/>
-      <c r="D7" s="127"/>
-      <c r="E7" s="128"/>
+      <c r="B7" s="126"/>
+      <c r="C7" s="126"/>
+      <c r="D7" s="126"/>
+      <c r="E7" s="127"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="86" t="s">
+      <c r="A8" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="86" t="s">
+      <c r="B8" s="85" t="s">
         <v>97</v>
       </c>
-      <c r="C8" s="86" t="s">
+      <c r="C8" s="85" t="s">
         <v>98</v>
       </c>
-      <c r="D8" s="86" t="s">
+      <c r="D8" s="85" t="s">
         <v>93</v>
       </c>
-      <c r="E8" s="86" t="s">
+      <c r="E8" s="85" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="86">
-        <v>1</v>
-      </c>
-      <c r="B9" s="86">
-        <v>1</v>
-      </c>
-      <c r="C9" s="86" t="s">
+      <c r="A9" s="85">
+        <v>1</v>
+      </c>
+      <c r="B9" s="85">
+        <v>1</v>
+      </c>
+      <c r="C9" s="85" t="s">
         <v>113</v>
       </c>
-      <c r="D9" s="86">
+      <c r="D9" s="85">
         <v>5</v>
       </c>
-      <c r="E9" s="101">
+      <c r="E9" s="100">
         <v>11.69</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="86">
+      <c r="A10" s="85">
         <v>2</v>
       </c>
-      <c r="B10" s="86">
+      <c r="B10" s="85">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C10" s="86" t="s">
+      <c r="C10" s="85" t="s">
         <v>113</v>
       </c>
-      <c r="D10" s="86">
+      <c r="D10" s="85">
         <v>5</v>
       </c>
-      <c r="E10" s="101">
+      <c r="E10" s="100">
         <v>7.73</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D11" s="102" t="s">
+      <c r="D11" s="101" t="s">
         <v>114</v>
       </c>
-      <c r="E11" s="102">
+      <c r="E11" s="101">
         <f>SUM(E9:E10)</f>
         <v>19.420000000000002</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" s="126" t="s">
+      <c r="A13" s="125" t="s">
         <v>48</v>
       </c>
-      <c r="B13" s="127"/>
-      <c r="C13" s="127"/>
-      <c r="D13" s="127"/>
-      <c r="E13" s="128"/>
+      <c r="B13" s="126"/>
+      <c r="C13" s="126"/>
+      <c r="D13" s="126"/>
+      <c r="E13" s="127"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" s="86" t="s">
+      <c r="A14" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="B14" s="86" t="s">
+      <c r="B14" s="85" t="s">
         <v>97</v>
       </c>
-      <c r="C14" s="86" t="s">
+      <c r="C14" s="85" t="s">
         <v>98</v>
       </c>
-      <c r="D14" s="86" t="s">
+      <c r="D14" s="85" t="s">
         <v>93</v>
       </c>
-      <c r="E14" s="86" t="s">
+      <c r="E14" s="85" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" s="86">
-        <v>1</v>
-      </c>
-      <c r="B15" s="86">
-        <v>1</v>
-      </c>
-      <c r="C15" s="86">
+      <c r="A15" s="85">
+        <v>1</v>
+      </c>
+      <c r="B15" s="85">
+        <v>1</v>
+      </c>
+      <c r="C15" s="85">
         <v>1.024</v>
       </c>
-      <c r="D15" s="86">
+      <c r="D15" s="85">
         <v>6</v>
       </c>
-      <c r="E15" s="86">
+      <c r="E15" s="85">
         <v>13.62</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A16" s="86">
+      <c r="A16" s="85">
         <v>2</v>
       </c>
-      <c r="B16" s="86">
+      <c r="B16" s="85">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C16" s="86">
+      <c r="C16" s="85">
         <v>1.0449999999999999</v>
       </c>
-      <c r="D16" s="86">
+      <c r="D16" s="85">
         <v>6</v>
       </c>
-      <c r="E16" s="86">
+      <c r="E16" s="85">
         <v>161.78</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" s="86">
+      <c r="A17" s="85">
         <v>3</v>
       </c>
-      <c r="B17" s="86">
+      <c r="B17" s="85">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C17" s="86">
+      <c r="C17" s="85">
         <v>1.046</v>
       </c>
-      <c r="D17" s="86">
+      <c r="D17" s="85">
         <v>6</v>
       </c>
-      <c r="E17" s="86">
+      <c r="E17" s="85">
         <v>161.15</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18" s="86">
+      <c r="A18" s="85">
         <v>4</v>
       </c>
-      <c r="B18" s="86">
+      <c r="B18" s="85">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C18" s="86">
+      <c r="C18" s="85">
         <v>1.0529999999999999</v>
       </c>
-      <c r="D18" s="86">
+      <c r="D18" s="85">
         <v>6</v>
       </c>
-      <c r="E18" s="86">
+      <c r="E18" s="85">
         <v>443.48</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19" s="86">
+      <c r="A19" s="85">
         <v>5</v>
       </c>
-      <c r="B19" s="86">
-        <v>1</v>
-      </c>
-      <c r="C19" s="86">
+      <c r="B19" s="85">
+        <v>1</v>
+      </c>
+      <c r="C19" s="85">
         <v>1.034</v>
       </c>
-      <c r="D19" s="86">
+      <c r="D19" s="85">
         <v>7</v>
       </c>
-      <c r="E19" s="86">
+      <c r="E19" s="85">
         <v>17.22</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A20" s="86">
+      <c r="A20" s="85">
         <v>6</v>
       </c>
-      <c r="B20" s="86">
-        <v>1</v>
-      </c>
-      <c r="C20" s="86">
+      <c r="B20" s="85">
+        <v>1</v>
+      </c>
+      <c r="C20" s="85">
         <v>1.0349999999999999</v>
       </c>
-      <c r="D20" s="86">
+      <c r="D20" s="85">
         <v>7</v>
       </c>
-      <c r="E20" s="86">
+      <c r="E20" s="85">
         <v>21.63</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A21" s="86">
+      <c r="A21" s="85">
         <v>7</v>
       </c>
-      <c r="B21" s="86">
-        <v>1</v>
-      </c>
-      <c r="C21" s="86">
+      <c r="B21" s="85">
+        <v>1</v>
+      </c>
+      <c r="C21" s="85">
         <v>1.036</v>
       </c>
-      <c r="D21" s="86">
+      <c r="D21" s="85">
         <v>7</v>
       </c>
-      <c r="E21" s="86">
+      <c r="E21" s="85">
         <v>5.76</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A22" s="86">
+      <c r="A22" s="85">
         <v>8</v>
       </c>
-      <c r="B22" s="86">
+      <c r="B22" s="85">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C22" s="86">
+      <c r="C22" s="85">
         <v>1.054</v>
       </c>
-      <c r="D22" s="86">
+      <c r="D22" s="85">
         <v>7</v>
       </c>
-      <c r="E22" s="86">
+      <c r="E22" s="85">
         <v>14.54</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23" s="86">
+      <c r="A23" s="85">
         <v>9</v>
       </c>
-      <c r="B23" s="86">
+      <c r="B23" s="85">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C23" s="86">
+      <c r="C23" s="85">
         <v>1.048</v>
       </c>
-      <c r="D23" s="86">
+      <c r="D23" s="85">
         <v>8.1</v>
       </c>
-      <c r="E23" s="86">
+      <c r="E23" s="85">
         <v>23.92</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A24" s="86">
+      <c r="A24" s="85">
         <v>10</v>
       </c>
-      <c r="B24" s="86">
-        <v>1</v>
-      </c>
-      <c r="C24" s="86">
+      <c r="B24" s="85">
+        <v>1</v>
+      </c>
+      <c r="C24" s="85">
         <v>1.0369999999999999</v>
       </c>
-      <c r="D24" s="86">
+      <c r="D24" s="85">
         <v>8.1999999999999993</v>
       </c>
-      <c r="E24" s="86">
+      <c r="E24" s="85">
         <v>3.34</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A25" s="86">
+      <c r="A25" s="85">
         <v>11</v>
       </c>
-      <c r="B25" s="86">
-        <v>1</v>
-      </c>
-      <c r="C25" s="86">
+      <c r="B25" s="85">
+        <v>1</v>
+      </c>
+      <c r="C25" s="85">
         <v>1.038</v>
       </c>
-      <c r="D25" s="86">
+      <c r="D25" s="85">
         <v>8.1999999999999993</v>
       </c>
-      <c r="E25" s="86">
+      <c r="E25" s="85">
         <v>5.25</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A26" s="86">
+      <c r="A26" s="85">
         <v>12</v>
       </c>
-      <c r="B26" s="86">
-        <v>1</v>
-      </c>
-      <c r="C26" s="86">
+      <c r="B26" s="85">
+        <v>1</v>
+      </c>
+      <c r="C26" s="85">
         <v>1.026</v>
       </c>
-      <c r="D26" s="86">
+      <c r="D26" s="85">
         <v>9</v>
       </c>
-      <c r="E26" s="86">
+      <c r="E26" s="85">
         <v>191.68</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A27" s="86">
+      <c r="A27" s="85">
         <v>13</v>
       </c>
-      <c r="B27" s="86">
-        <v>1</v>
-      </c>
-      <c r="C27" s="86">
+      <c r="B27" s="85">
+        <v>1</v>
+      </c>
+      <c r="C27" s="85">
         <v>1.0269999999999999</v>
       </c>
-      <c r="D27" s="86">
+      <c r="D27" s="85">
         <v>9</v>
       </c>
-      <c r="E27" s="86">
+      <c r="E27" s="85">
         <v>114.04</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A28" s="86">
+      <c r="A28" s="85">
         <v>14</v>
       </c>
-      <c r="B28" s="86">
-        <v>1</v>
-      </c>
-      <c r="C28" s="86">
+      <c r="B28" s="85">
+        <v>1</v>
+      </c>
+      <c r="C28" s="85">
         <v>1.028</v>
       </c>
-      <c r="D28" s="86">
+      <c r="D28" s="85">
         <v>9</v>
       </c>
-      <c r="E28" s="86">
+      <c r="E28" s="85">
         <v>68.81</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A29" s="86">
+      <c r="A29" s="85">
         <v>15</v>
       </c>
-      <c r="B29" s="86">
-        <v>1</v>
-      </c>
-      <c r="C29" s="86">
+      <c r="B29" s="85">
+        <v>1</v>
+      </c>
+      <c r="C29" s="85">
         <v>1.0289999999999999</v>
       </c>
-      <c r="D29" s="86">
+      <c r="D29" s="85">
         <v>9</v>
       </c>
-      <c r="E29" s="86">
+      <c r="E29" s="85">
         <v>68.81</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A30" s="86">
+      <c r="A30" s="85">
         <v>16</v>
       </c>
-      <c r="B30" s="86">
-        <v>1</v>
-      </c>
-      <c r="C30" s="86">
+      <c r="B30" s="85">
+        <v>1</v>
+      </c>
+      <c r="C30" s="85">
         <v>1.03</v>
       </c>
-      <c r="D30" s="86">
+      <c r="D30" s="85">
         <v>9</v>
       </c>
-      <c r="E30" s="86">
+      <c r="E30" s="85">
         <v>68.89</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A31" s="86">
+      <c r="A31" s="85">
         <v>17</v>
       </c>
-      <c r="B31" s="86">
-        <v>1</v>
-      </c>
-      <c r="C31" s="86">
+      <c r="B31" s="85">
+        <v>1</v>
+      </c>
+      <c r="C31" s="85">
         <v>1.0309999999999999</v>
       </c>
-      <c r="D31" s="86">
+      <c r="D31" s="85">
         <v>9</v>
       </c>
-      <c r="E31" s="86">
+      <c r="E31" s="85">
         <v>68.89</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A32" s="86">
+      <c r="A32" s="85">
         <v>18</v>
       </c>
-      <c r="B32" s="86">
-        <v>1</v>
-      </c>
-      <c r="C32" s="86">
+      <c r="B32" s="85">
+        <v>1</v>
+      </c>
+      <c r="C32" s="85">
         <v>1.032</v>
       </c>
-      <c r="D32" s="86">
+      <c r="D32" s="85">
         <v>9</v>
       </c>
-      <c r="E32" s="86">
+      <c r="E32" s="85">
         <v>68.069999999999993</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A33" s="86">
+      <c r="A33" s="85">
         <v>19</v>
       </c>
-      <c r="B33" s="86">
-        <v>1</v>
-      </c>
-      <c r="C33" s="86">
+      <c r="B33" s="85">
+        <v>1</v>
+      </c>
+      <c r="C33" s="85">
         <v>1.0329999999999999</v>
       </c>
-      <c r="D33" s="86">
+      <c r="D33" s="85">
         <v>9</v>
       </c>
-      <c r="E33" s="86">
+      <c r="E33" s="85">
         <v>139.1</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A34" s="86">
+      <c r="A34" s="85">
         <v>20</v>
       </c>
-      <c r="B34" s="86">
-        <v>1</v>
-      </c>
-      <c r="C34" s="86">
+      <c r="B34" s="85">
+        <v>1</v>
+      </c>
+      <c r="C34" s="85">
         <v>1.0389999999999999</v>
       </c>
-      <c r="D34" s="86">
+      <c r="D34" s="85">
         <v>9</v>
       </c>
-      <c r="E34" s="86">
+      <c r="E34" s="85">
         <v>149.69999999999999</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A35" s="86">
+      <c r="A35" s="85">
         <v>21</v>
       </c>
-      <c r="B35" s="86">
+      <c r="B35" s="85">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C35" s="86">
+      <c r="C35" s="85">
         <v>1.04</v>
       </c>
-      <c r="D35" s="86">
+      <c r="D35" s="85">
         <v>9</v>
       </c>
-      <c r="E35" s="86">
+      <c r="E35" s="85">
         <v>220.47</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A36" s="86">
+      <c r="A36" s="85">
         <v>22</v>
       </c>
-      <c r="B36" s="86">
+      <c r="B36" s="85">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C36" s="86">
+      <c r="C36" s="85">
         <v>1.0429999999999999</v>
       </c>
-      <c r="D36" s="86">
+      <c r="D36" s="85">
         <v>9</v>
       </c>
-      <c r="E36" s="86">
+      <c r="E36" s="85">
         <v>61.99</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A37" s="86">
+      <c r="A37" s="85">
         <v>23</v>
       </c>
-      <c r="B37" s="86">
+      <c r="B37" s="85">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C37" s="86">
+      <c r="C37" s="85">
         <v>1.044</v>
       </c>
-      <c r="D37" s="86">
+      <c r="D37" s="85">
         <v>9</v>
       </c>
-      <c r="E37" s="86">
+      <c r="E37" s="85">
         <v>14.14</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A38" s="86">
+      <c r="A38" s="85">
         <v>24</v>
       </c>
-      <c r="B38" s="86">
+      <c r="B38" s="85">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C38" s="86">
+      <c r="C38" s="85">
         <v>1.0489999999999999</v>
       </c>
-      <c r="D38" s="86">
+      <c r="D38" s="85">
         <v>9</v>
       </c>
-      <c r="E38" s="86">
+      <c r="E38" s="85">
         <v>103.8</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A39" s="86">
+      <c r="A39" s="85">
         <v>25</v>
       </c>
-      <c r="B39" s="86">
+      <c r="B39" s="85">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C39" s="86">
+      <c r="C39" s="85">
         <v>1.05</v>
       </c>
-      <c r="D39" s="86">
+      <c r="D39" s="85">
         <v>9</v>
       </c>
-      <c r="E39" s="86">
+      <c r="E39" s="85">
         <v>22</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A40" s="86">
+      <c r="A40" s="85">
         <v>26</v>
       </c>
-      <c r="B40" s="86">
+      <c r="B40" s="85">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C40" s="86">
+      <c r="C40" s="85">
         <v>1.0509999999999999</v>
       </c>
-      <c r="D40" s="86">
+      <c r="D40" s="85">
         <v>9</v>
       </c>
-      <c r="E40" s="86">
+      <c r="E40" s="85">
         <v>31.58</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A41" s="86"/>
-      <c r="B41" s="86"/>
-      <c r="C41" s="86"/>
-      <c r="D41" s="86" t="s">
+      <c r="A41" s="85"/>
+      <c r="B41" s="85"/>
+      <c r="C41" s="85"/>
+      <c r="D41" s="85" t="s">
         <v>114</v>
       </c>
-      <c r="E41" s="86">
+      <c r="E41" s="85">
         <f>SUM(E15:E40)</f>
         <v>2263.66</v>
       </c>
@@ -6861,201 +6860,201 @@
   <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="102"/>
+    <col min="1" max="16384" width="9.140625" style="101"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" s="129" t="s">
+      <c r="A1" s="128" t="s">
         <v>111</v>
       </c>
-      <c r="B1" s="129"/>
-      <c r="C1" s="129"/>
-      <c r="D1" s="129"/>
-      <c r="E1" s="129"/>
+      <c r="B1" s="128"/>
+      <c r="C1" s="128"/>
+      <c r="D1" s="128"/>
+      <c r="E1" s="128"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="86" t="s">
+      <c r="A2" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="86" t="s">
+      <c r="B2" s="85" t="s">
         <v>97</v>
       </c>
-      <c r="C2" s="86" t="s">
+      <c r="C2" s="85" t="s">
         <v>98</v>
       </c>
-      <c r="D2" s="86" t="s">
+      <c r="D2" s="85" t="s">
         <v>93</v>
       </c>
-      <c r="E2" s="86" t="s">
+      <c r="E2" s="85" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="86">
-        <v>1</v>
-      </c>
-      <c r="B3" s="86">
-        <v>1</v>
-      </c>
-      <c r="C3" s="86" t="s">
+      <c r="A3" s="85">
+        <v>1</v>
+      </c>
+      <c r="B3" s="85">
+        <v>1</v>
+      </c>
+      <c r="C3" s="85" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="86">
+      <c r="D3" s="85">
         <v>9.3000000000000007</v>
       </c>
-      <c r="E3" s="101">
+      <c r="E3" s="100">
         <v>14.5</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="86">
+      <c r="A4" s="85">
         <v>2</v>
       </c>
-      <c r="B4" s="86">
+      <c r="B4" s="85">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C4" s="86" t="s">
+      <c r="C4" s="85" t="s">
         <v>113</v>
       </c>
-      <c r="D4" s="86">
+      <c r="D4" s="85">
         <v>9.3000000000000007</v>
       </c>
-      <c r="E4" s="101">
+      <c r="E4" s="100">
         <v>0.5</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="86"/>
-      <c r="B5" s="86"/>
-      <c r="C5" s="86"/>
-      <c r="D5" s="86" t="s">
+      <c r="A5" s="85"/>
+      <c r="B5" s="85"/>
+      <c r="C5" s="85"/>
+      <c r="D5" s="85" t="s">
         <v>114</v>
       </c>
-      <c r="E5" s="121">
+      <c r="E5" s="120">
         <f>SUM(E3:E4)</f>
         <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="129" t="s">
+      <c r="A7" s="128" t="s">
         <v>111</v>
       </c>
-      <c r="B7" s="129"/>
-      <c r="C7" s="129"/>
-      <c r="D7" s="129"/>
-      <c r="E7" s="129"/>
+      <c r="B7" s="128"/>
+      <c r="C7" s="128"/>
+      <c r="D7" s="128"/>
+      <c r="E7" s="128"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="86" t="s">
+      <c r="A8" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="86" t="s">
+      <c r="B8" s="85" t="s">
         <v>97</v>
       </c>
-      <c r="C8" s="86" t="s">
+      <c r="C8" s="85" t="s">
         <v>98</v>
       </c>
-      <c r="D8" s="86" t="s">
+      <c r="D8" s="85" t="s">
         <v>93</v>
       </c>
-      <c r="E8" s="86" t="s">
+      <c r="E8" s="85" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="86">
-        <v>1</v>
-      </c>
-      <c r="B9" s="86">
-        <v>1</v>
-      </c>
-      <c r="C9" s="86" t="s">
+      <c r="A9" s="85">
+        <v>1</v>
+      </c>
+      <c r="B9" s="85">
+        <v>1</v>
+      </c>
+      <c r="C9" s="85" t="s">
         <v>113</v>
       </c>
-      <c r="D9" s="86">
+      <c r="D9" s="85">
         <v>5.0999999999999996</v>
       </c>
-      <c r="E9" s="86">
+      <c r="E9" s="85">
         <v>8.2799999999999994</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="86">
+      <c r="A10" s="85">
         <v>2</v>
       </c>
-      <c r="B10" s="86">
+      <c r="B10" s="85">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C10" s="86" t="s">
+      <c r="C10" s="85" t="s">
         <v>113</v>
       </c>
-      <c r="D10" s="86">
+      <c r="D10" s="85">
         <v>5.0999999999999996</v>
       </c>
-      <c r="E10" s="86">
-        <v>8.09</v>
+      <c r="E10" s="85">
+        <v>8.39</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="86">
+      <c r="A11" s="85">
         <v>3</v>
       </c>
-      <c r="B11" s="86">
+      <c r="B11" s="85">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C11" s="86">
+      <c r="C11" s="85">
         <v>2.16</v>
       </c>
-      <c r="D11" s="86">
+      <c r="D11" s="85">
         <v>4.4000000000000004</v>
       </c>
-      <c r="E11" s="86">
+      <c r="E11" s="85">
         <v>72.64</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="86"/>
-      <c r="B12" s="86"/>
-      <c r="C12" s="86"/>
-      <c r="D12" s="86" t="s">
+      <c r="A12" s="85"/>
+      <c r="B12" s="85"/>
+      <c r="C12" s="85"/>
+      <c r="D12" s="85" t="s">
         <v>114</v>
       </c>
-      <c r="E12" s="86">
+      <c r="E12" s="85">
         <f>SUM(E9:E11)</f>
-        <v>89.009999999999991</v>
+        <v>89.31</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" s="129" t="s">
+      <c r="A14" s="128" t="s">
         <v>111</v>
       </c>
-      <c r="B14" s="129"/>
-      <c r="C14" s="129"/>
-      <c r="D14" s="129"/>
-      <c r="E14" s="129"/>
+      <c r="B14" s="128"/>
+      <c r="C14" s="128"/>
+      <c r="D14" s="128"/>
+      <c r="E14" s="128"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" s="86">
-        <v>1</v>
-      </c>
-      <c r="B15" s="86">
+      <c r="A15" s="85">
+        <v>1</v>
+      </c>
+      <c r="B15" s="85">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C15" s="86">
+      <c r="C15" s="85">
         <v>2.085</v>
       </c>
-      <c r="D15" s="86">
+      <c r="D15" s="85">
         <v>11.1</v>
       </c>
-      <c r="E15" s="86">
+      <c r="E15" s="85">
         <v>168.62</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D16" s="86" t="s">
+      <c r="D16" s="85" t="s">
         <v>114</v>
       </c>
-      <c r="E16" s="86">
+      <c r="E16" s="85">
         <f>SUM(E15:E15)</f>
         <v>168.62</v>
       </c>
@@ -7080,129 +7079,129 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="129" t="s">
+      <c r="A1" s="128" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="129"/>
-      <c r="C1" s="129"/>
-      <c r="D1" s="129"/>
-      <c r="E1" s="129"/>
+      <c r="B1" s="128"/>
+      <c r="C1" s="128"/>
+      <c r="D1" s="128"/>
+      <c r="E1" s="128"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="86" t="s">
+      <c r="A2" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="86" t="s">
+      <c r="B2" s="85" t="s">
         <v>97</v>
       </c>
-      <c r="C2" s="86" t="s">
+      <c r="C2" s="85" t="s">
         <v>98</v>
       </c>
-      <c r="D2" s="86" t="s">
+      <c r="D2" s="85" t="s">
         <v>93</v>
       </c>
-      <c r="E2" s="86" t="s">
+      <c r="E2" s="85" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="86">
+      <c r="A3" s="85">
         <v>4</v>
       </c>
-      <c r="B3" s="86">
-        <v>1</v>
-      </c>
-      <c r="C3" s="86" t="s">
+      <c r="B3" s="85">
+        <v>1</v>
+      </c>
+      <c r="C3" s="85" t="s">
         <v>113</v>
       </c>
-      <c r="D3" s="86">
+      <c r="D3" s="85">
         <v>9.3000000000000007</v>
       </c>
-      <c r="E3" s="101">
+      <c r="E3" s="100">
         <v>14.79</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="86"/>
-      <c r="B4" s="86"/>
-      <c r="C4" s="86"/>
-      <c r="D4" s="86" t="s">
+      <c r="A4" s="85"/>
+      <c r="B4" s="85"/>
+      <c r="C4" s="85"/>
+      <c r="D4" s="85" t="s">
         <v>114</v>
       </c>
-      <c r="E4" s="86">
+      <c r="E4" s="85">
         <f>SUM(E3:E3)</f>
         <v>14.79</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="129" t="s">
+      <c r="A6" s="128" t="s">
         <v>109</v>
       </c>
-      <c r="B6" s="129"/>
-      <c r="C6" s="129"/>
-      <c r="D6" s="129"/>
-      <c r="E6" s="129"/>
+      <c r="B6" s="128"/>
+      <c r="C6" s="128"/>
+      <c r="D6" s="128"/>
+      <c r="E6" s="128"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="86" t="s">
+      <c r="A7" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="86" t="s">
+      <c r="B7" s="85" t="s">
         <v>97</v>
       </c>
-      <c r="C7" s="86" t="s">
+      <c r="C7" s="85" t="s">
         <v>98</v>
       </c>
-      <c r="D7" s="86" t="s">
+      <c r="D7" s="85" t="s">
         <v>93</v>
       </c>
-      <c r="E7" s="86" t="s">
+      <c r="E7" s="85" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="86">
-        <v>1</v>
-      </c>
-      <c r="B8" s="86">
-        <v>1</v>
-      </c>
-      <c r="C8" s="86" t="s">
+      <c r="A8" s="85">
+        <v>1</v>
+      </c>
+      <c r="B8" s="85">
+        <v>1</v>
+      </c>
+      <c r="C8" s="85" t="s">
         <v>113</v>
       </c>
-      <c r="D8" s="86">
+      <c r="D8" s="85">
         <v>5.0999999999999996</v>
       </c>
-      <c r="E8" s="86">
+      <c r="E8" s="85">
         <v>6.03</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="86">
+      <c r="A9" s="85">
         <v>2</v>
       </c>
-      <c r="B9" s="86">
+      <c r="B9" s="85">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C9" s="86" t="s">
+      <c r="C9" s="85" t="s">
         <v>113</v>
       </c>
-      <c r="D9" s="86">
+      <c r="D9" s="85">
         <v>5.0999999999999996</v>
       </c>
-      <c r="E9" s="86">
+      <c r="E9" s="85">
         <v>5.95</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="86"/>
-      <c r="B10" s="86"/>
-      <c r="C10" s="86"/>
-      <c r="D10" s="86" t="s">
+      <c r="A10" s="85"/>
+      <c r="B10" s="85"/>
+      <c r="C10" s="85"/>
+      <c r="D10" s="85" t="s">
         <v>114</v>
       </c>
-      <c r="E10" s="86">
+      <c r="E10" s="85">
         <f>SUM(E8:E9)</f>
         <v>11.98</v>
       </c>
@@ -7566,15 +7565,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="122" t="s">
+      <c r="A1" s="121" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
-      <c r="E1" s="122"/>
-      <c r="F1" s="122"/>
-      <c r="G1" s="122"/>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="121"/>
+      <c r="F1" s="121"/>
+      <c r="G1" s="121"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="10"/>
@@ -8783,15 +8782,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="122" t="s">
+      <c r="A1" s="121" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
-      <c r="E1" s="122"/>
-      <c r="F1" s="122"/>
-      <c r="G1" s="122"/>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="121"/>
+      <c r="F1" s="121"/>
+      <c r="G1" s="121"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="10"/>
@@ -8860,7 +8859,7 @@
       <c r="E4" s="41"/>
       <c r="F4" s="47"/>
       <c r="G4" s="25">
-        <f>SUM(C4:F4)</f>
+        <f t="shared" ref="G4:G23" si="0">SUM(C4:F4)</f>
         <v>13.62</v>
       </c>
       <c r="K4">
@@ -8881,7 +8880,7 @@
       <c r="E5" s="41"/>
       <c r="F5" s="47"/>
       <c r="G5" s="25">
-        <f>SUM(C5:F5)</f>
+        <f t="shared" si="0"/>
         <v>15.07</v>
       </c>
       <c r="K5">
@@ -8902,7 +8901,7 @@
       <c r="E6" s="41"/>
       <c r="F6" s="47"/>
       <c r="G6" s="25">
-        <f>SUM(C6:F6)</f>
+        <f t="shared" si="0"/>
         <v>17.21</v>
       </c>
       <c r="K6">
@@ -8923,7 +8922,7 @@
       <c r="E7" s="41"/>
       <c r="F7" s="47"/>
       <c r="G7" s="25">
-        <f>SUM(C7:F7)</f>
+        <f t="shared" si="0"/>
         <v>21.12</v>
       </c>
       <c r="K7">
@@ -8944,7 +8943,7 @@
       <c r="E8" s="41"/>
       <c r="F8" s="47"/>
       <c r="G8" s="25">
-        <f>SUM(C8:F8)</f>
+        <f t="shared" si="0"/>
         <v>5.0599999999999996</v>
       </c>
       <c r="K8">
@@ -8965,7 +8964,7 @@
       </c>
       <c r="F9" s="47"/>
       <c r="G9" s="25">
-        <f>SUM(C9:F9)</f>
+        <f t="shared" si="0"/>
         <v>5.0599999999999996</v>
       </c>
       <c r="K9">
@@ -8986,7 +8985,7 @@
       </c>
       <c r="F10" s="47"/>
       <c r="G10" s="25">
-        <f>SUM(C10:F10)</f>
+        <f t="shared" si="0"/>
         <v>5.24</v>
       </c>
       <c r="K10">
@@ -9007,7 +9006,7 @@
       </c>
       <c r="F11" s="47"/>
       <c r="G11" s="25">
-        <f>SUM(C11:F11)</f>
+        <f t="shared" si="0"/>
         <v>15.62</v>
       </c>
       <c r="K11">
@@ -9015,7 +9014,7 @@
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="108">
+      <c r="A12" s="107">
         <v>9</v>
       </c>
       <c r="B12" s="54">
@@ -9028,7 +9027,7 @@
         <v>67.59</v>
       </c>
       <c r="G12" s="25">
-        <f>SUM(C12:F12)</f>
+        <f t="shared" si="0"/>
         <v>67.59</v>
       </c>
       <c r="K12">
@@ -9036,7 +9035,7 @@
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="108">
+      <c r="A13" s="107">
         <v>10</v>
       </c>
       <c r="B13" s="54">
@@ -9049,7 +9048,7 @@
         <v>67.84</v>
       </c>
       <c r="G13" s="25">
-        <f>SUM(C13:F13)</f>
+        <f t="shared" si="0"/>
         <v>67.84</v>
       </c>
       <c r="K13">
@@ -9057,7 +9056,7 @@
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="108">
+      <c r="A14" s="107">
         <v>11</v>
       </c>
       <c r="B14" s="54">
@@ -9070,7 +9069,7 @@
         <v>68</v>
       </c>
       <c r="G14" s="25">
-        <f>SUM(C14:F14)</f>
+        <f t="shared" si="0"/>
         <v>68</v>
       </c>
       <c r="K14">
@@ -9078,7 +9077,7 @@
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="108">
+      <c r="A15" s="107">
         <v>12</v>
       </c>
       <c r="B15" s="54">
@@ -9091,7 +9090,7 @@
         <v>68</v>
       </c>
       <c r="G15" s="25">
-        <f>SUM(C15:F15)</f>
+        <f t="shared" si="0"/>
         <v>68</v>
       </c>
       <c r="K15">
@@ -9099,7 +9098,7 @@
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="108">
+      <c r="A16" s="107">
         <v>13</v>
       </c>
       <c r="B16" s="54">
@@ -9112,7 +9111,7 @@
         <v>67.14</v>
       </c>
       <c r="G16" s="25">
-        <f>SUM(C16:F16)</f>
+        <f t="shared" si="0"/>
         <v>67.14</v>
       </c>
       <c r="K16">
@@ -9120,7 +9119,7 @@
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="108">
+      <c r="A17" s="107">
         <v>14</v>
       </c>
       <c r="B17" s="54">
@@ -9133,7 +9132,7 @@
         <v>68</v>
       </c>
       <c r="G17" s="25">
-        <f>SUM(C17:F17)</f>
+        <f t="shared" si="0"/>
         <v>68</v>
       </c>
       <c r="K17">
@@ -9141,7 +9140,7 @@
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="108">
+      <c r="A18" s="107">
         <v>15</v>
       </c>
       <c r="B18" s="54">
@@ -9154,7 +9153,7 @@
         <v>68</v>
       </c>
       <c r="G18" s="25">
-        <f>SUM(C18:F18)</f>
+        <f t="shared" si="0"/>
         <v>68</v>
       </c>
       <c r="K18">
@@ -9162,7 +9161,7 @@
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="108">
+      <c r="A19" s="107">
         <v>16</v>
       </c>
       <c r="B19" s="54">
@@ -9175,7 +9174,7 @@
         <v>148.61000000000001</v>
       </c>
       <c r="G19" s="25">
-        <f>SUM(C19:F19)</f>
+        <f t="shared" si="0"/>
         <v>148.61000000000001</v>
       </c>
       <c r="K19">
@@ -9183,7 +9182,7 @@
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="108">
+      <c r="A20" s="107">
         <v>17</v>
       </c>
       <c r="B20" s="8">
@@ -9196,7 +9195,7 @@
         <v>244.28</v>
       </c>
       <c r="G20" s="25">
-        <f>SUM(C20:F20)</f>
+        <f t="shared" si="0"/>
         <v>244.28</v>
       </c>
       <c r="K20">
@@ -9204,7 +9203,7 @@
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="108">
+      <c r="A21" s="107">
         <v>18</v>
       </c>
       <c r="B21" s="54">
@@ -9217,7 +9216,7 @@
         <v>137.72999999999999</v>
       </c>
       <c r="G21" s="25">
-        <f>SUM(C21:F21)</f>
+        <f t="shared" si="0"/>
         <v>137.72999999999999</v>
       </c>
       <c r="K21">
@@ -9225,7 +9224,7 @@
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="108">
+      <c r="A22" s="107">
         <v>19</v>
       </c>
       <c r="B22" s="54">
@@ -9238,7 +9237,7 @@
         <v>13.16</v>
       </c>
       <c r="G22" s="25">
-        <f>SUM(C22:F22)</f>
+        <f t="shared" si="0"/>
         <v>13.16</v>
       </c>
       <c r="K22">
@@ -9246,7 +9245,7 @@
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="108">
+      <c r="A23" s="107">
         <v>20</v>
       </c>
       <c r="B23" s="54" t="s">
@@ -9259,7 +9258,7 @@
         <v>140.80000000000001</v>
       </c>
       <c r="G23" s="25">
-        <f>SUM(C23:F23)</f>
+        <f t="shared" si="0"/>
         <v>140.80000000000001</v>
       </c>
       <c r="K23">
@@ -10445,35 +10444,35 @@
     <col min="7" max="9" width="0" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="92">
-        <v>1</v>
-      </c>
-      <c r="B1" s="93" t="s">
+    <row r="1" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="91">
+        <v>1</v>
+      </c>
+      <c r="B1" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="94" t="s">
+      <c r="C1" s="93" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="92" t="s">
+      <c r="D1" s="91" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="95">
-        <v>1</v>
-      </c>
-      <c r="F1" s="96">
+      <c r="E1" s="94">
+        <v>1</v>
+      </c>
+      <c r="F1" s="95">
         <v>46.62</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="51.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="74">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="73">
         <v>1.1000000000000001</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>22</v>
       </c>
       <c r="C2" s="9"/>
-      <c r="D2" s="74" t="s">
+      <c r="D2" s="73" t="s">
         <v>41</v>
       </c>
       <c r="E2" s="8">
@@ -10483,15 +10482,15 @@
         <v>372</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="51.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="74">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="73">
         <v>1.2</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>23</v>
       </c>
       <c r="C3" s="9"/>
-      <c r="D3" s="74" t="s">
+      <c r="D3" s="73" t="s">
         <v>6</v>
       </c>
       <c r="E3" s="8">
@@ -10501,15 +10500,15 @@
         <v>3356.64</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="39" x14ac:dyDescent="0.25">
-      <c r="A4" s="74">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="73">
         <v>1.3</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>24</v>
       </c>
       <c r="C4" s="9"/>
-      <c r="D4" s="74" t="s">
+      <c r="D4" s="73" t="s">
         <v>7</v>
       </c>
       <c r="E4" s="8">
@@ -10519,15 +10518,15 @@
         <v>51.281999999999996</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="51.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="74">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="73">
         <v>1.4</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="9"/>
-      <c r="D5" s="74" t="s">
+      <c r="D5" s="73" t="s">
         <v>5</v>
       </c>
       <c r="E5" s="8">
@@ -10537,20 +10536,20 @@
         <v>46.62</v>
       </c>
     </row>
-    <row r="7" spans="1:11" s="102" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="86">
-        <v>1</v>
-      </c>
-      <c r="B7" s="86">
+    <row r="7" spans="1:11" s="101" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="85">
+        <v>1</v>
+      </c>
+      <c r="B7" s="85">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C7" s="86">
+      <c r="C7" s="85">
         <v>2.081</v>
       </c>
-      <c r="D7" s="86">
+      <c r="D7" s="85">
         <v>11</v>
       </c>
-      <c r="E7" s="86">
+      <c r="E7" s="85">
         <v>298.27999999999997</v>
       </c>
     </row>
@@ -10583,14 +10582,14 @@
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="108">
+      <c r="A9" s="107">
         <v>2.1</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>22</v>
       </c>
       <c r="C9" s="9"/>
-      <c r="D9" s="108" t="s">
+      <c r="D9" s="107" t="s">
         <v>41</v>
       </c>
       <c r="E9" s="8">
@@ -10609,14 +10608,14 @@
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="108">
+      <c r="A10" s="107">
         <v>2.2000000000000002</v>
       </c>
       <c r="B10" s="30" t="s">
         <v>23</v>
       </c>
       <c r="C10" s="30"/>
-      <c r="D10" s="108" t="s">
+      <c r="D10" s="107" t="s">
         <v>6</v>
       </c>
       <c r="E10" s="8">
@@ -10639,14 +10638,14 @@
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="108">
+      <c r="A11" s="107">
         <v>2.2999999999999998</v>
       </c>
       <c r="B11" s="30" t="s">
         <v>24</v>
       </c>
       <c r="C11" s="30"/>
-      <c r="D11" s="108" t="s">
+      <c r="D11" s="107" t="s">
         <v>7</v>
       </c>
       <c r="E11" s="8">
@@ -10665,14 +10664,14 @@
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="108">
+      <c r="A12" s="107">
         <v>2.4</v>
       </c>
       <c r="B12" s="30" t="s">
         <v>12</v>
       </c>
       <c r="C12" s="30"/>
-      <c r="D12" s="108" t="s">
+      <c r="D12" s="107" t="s">
         <v>5</v>
       </c>
       <c r="E12" s="8">
@@ -10829,7 +10828,7 @@
       <c r="A3" s="67">
         <v>1</v>
       </c>
-      <c r="B3" s="73" t="s">
+      <c r="B3" s="72" t="s">
         <v>102</v>
       </c>
       <c r="C3" s="69" t="s">
@@ -10842,8 +10841,8 @@
         <v>1</v>
       </c>
       <c r="F3" s="60">
-        <f>Из1эт!E29+Из2эт!E17</f>
-        <v>2427.35</v>
+        <f>Из1эт!E29</f>
+        <v>2263.66</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -10862,7 +10861,7 @@
       </c>
       <c r="F4" s="25">
         <f>E4*F3*50/1000</f>
-        <v>125.00852500000001</v>
+        <v>116.57848999999999</v>
       </c>
     </row>
   </sheetData>
@@ -10883,13 +10882,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="123" t="s">
+      <c r="A1" s="122" t="s">
         <v>108</v>
       </c>
-      <c r="B1" s="124"/>
-      <c r="C1" s="124"/>
-      <c r="D1" s="124"/>
-      <c r="E1" s="125"/>
+      <c r="B1" s="123"/>
+      <c r="C1" s="123"/>
+      <c r="D1" s="123"/>
+      <c r="E1" s="124"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="56" t="s">
